--- a/output/Data and Chart Outputs/brazil_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/brazil_power_capacity.xlsx
@@ -377,7 +377,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="9A9A9A"/>
+              <a:srgbClr val="E34948"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -947,29 +947,29 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Solar</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Wind</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Oil</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
         <is>
           <t>Bioenergy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Gas</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Oil</t>
-        </is>
-      </c>
       <c r="H1" t="inlineStr">
         <is>
           <t>Coal</t>
@@ -977,7 +977,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Nuclear &amp; other</t>
         </is>
       </c>
     </row>
@@ -989,19 +989,19 @@
         <v>109.2893</v>
       </c>
       <c r="C2" t="n">
-        <v>9.463200000000001</v>
+        <v>13.982</v>
       </c>
       <c r="D2" t="n">
         <v>17.3511</v>
       </c>
       <c r="E2" t="n">
+        <v>9.463200000000001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>6.8934</v>
+      </c>
+      <c r="G2" t="n">
         <v>15.4085</v>
-      </c>
-      <c r="F2" t="n">
-        <v>13.982</v>
-      </c>
-      <c r="G2" t="n">
-        <v>6.8934</v>
       </c>
       <c r="H2" t="n">
         <v>3.9137</v>
@@ -1018,19 +1018,19 @@
         <v>109.2992</v>
       </c>
       <c r="C3" t="n">
-        <v>9.786100000000001</v>
+        <v>13.982</v>
       </c>
       <c r="D3" t="n">
         <v>17.4718</v>
       </c>
       <c r="E3" t="n">
+        <v>9.786100000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>6.9028</v>
+      </c>
+      <c r="G3" t="n">
         <v>15.426</v>
-      </c>
-      <c r="F3" t="n">
-        <v>13.982</v>
-      </c>
-      <c r="G3" t="n">
-        <v>6.9028</v>
       </c>
       <c r="H3" t="n">
         <v>3.9137</v>
@@ -1047,19 +1047,19 @@
         <v>109.3056</v>
       </c>
       <c r="C4" t="n">
-        <v>10.2781</v>
+        <v>13.982</v>
       </c>
       <c r="D4" t="n">
         <v>17.8043</v>
       </c>
       <c r="E4" t="n">
+        <v>10.2781</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6.9315</v>
+      </c>
+      <c r="G4" t="n">
         <v>15.4351</v>
-      </c>
-      <c r="F4" t="n">
-        <v>13.982</v>
-      </c>
-      <c r="G4" t="n">
-        <v>6.9315</v>
       </c>
       <c r="H4" t="n">
         <v>3.9137</v>
@@ -1076,19 +1076,19 @@
         <v>109.3056</v>
       </c>
       <c r="C5" t="n">
-        <v>10.6506</v>
+        <v>13.982</v>
       </c>
       <c r="D5" t="n">
         <v>18.0124</v>
       </c>
       <c r="E5" t="n">
+        <v>10.6506</v>
+      </c>
+      <c r="F5" t="n">
+        <v>6.9739</v>
+      </c>
+      <c r="G5" t="n">
         <v>15.4904</v>
-      </c>
-      <c r="F5" t="n">
-        <v>13.982</v>
-      </c>
-      <c r="G5" t="n">
-        <v>6.9739</v>
       </c>
       <c r="H5" t="n">
         <v>3.9137</v>
@@ -1105,19 +1105,19 @@
         <v>109.315</v>
       </c>
       <c r="C6" t="n">
-        <v>11.0853</v>
+        <v>13.982</v>
       </c>
       <c r="D6" t="n">
         <v>18.263</v>
       </c>
       <c r="E6" t="n">
+        <v>11.0853</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6.9739</v>
+      </c>
+      <c r="G6" t="n">
         <v>15.5156</v>
-      </c>
-      <c r="F6" t="n">
-        <v>13.982</v>
-      </c>
-      <c r="G6" t="n">
-        <v>6.9739</v>
       </c>
       <c r="H6" t="n">
         <v>3.9137</v>
@@ -1134,19 +1134,19 @@
         <v>109.3481</v>
       </c>
       <c r="C7" t="n">
-        <v>11.5629</v>
+        <v>13.982</v>
       </c>
       <c r="D7" t="n">
         <v>18.6021</v>
       </c>
       <c r="E7" t="n">
+        <v>11.5629</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6.9739</v>
+      </c>
+      <c r="G7" t="n">
         <v>15.5595</v>
-      </c>
-      <c r="F7" t="n">
-        <v>13.982</v>
-      </c>
-      <c r="G7" t="n">
-        <v>6.9739</v>
       </c>
       <c r="H7" t="n">
         <v>3.9137</v>
@@ -1163,19 +1163,19 @@
         <v>109.3481</v>
       </c>
       <c r="C8" t="n">
-        <v>12.0824</v>
+        <v>14.1591</v>
       </c>
       <c r="D8" t="n">
         <v>18.8737</v>
       </c>
       <c r="E8" t="n">
+        <v>12.0824</v>
+      </c>
+      <c r="F8" t="n">
+        <v>6.9739</v>
+      </c>
+      <c r="G8" t="n">
         <v>15.5602</v>
-      </c>
-      <c r="F8" t="n">
-        <v>14.1591</v>
-      </c>
-      <c r="G8" t="n">
-        <v>6.9739</v>
       </c>
       <c r="H8" t="n">
         <v>3.9137</v>
@@ -1192,19 +1192,19 @@
         <v>109.3628</v>
       </c>
       <c r="C9" t="n">
-        <v>12.8917</v>
+        <v>14.1591</v>
       </c>
       <c r="D9" t="n">
         <v>19.3076</v>
       </c>
       <c r="E9" t="n">
+        <v>12.8917</v>
+      </c>
+      <c r="F9" t="n">
+        <v>6.9757</v>
+      </c>
+      <c r="G9" t="n">
         <v>15.6108</v>
-      </c>
-      <c r="F9" t="n">
-        <v>14.1591</v>
-      </c>
-      <c r="G9" t="n">
-        <v>6.9757</v>
       </c>
       <c r="H9" t="n">
         <v>3.9137</v>
@@ -1221,19 +1221,19 @@
         <v>109.3644</v>
       </c>
       <c r="C10" t="n">
-        <v>13.4677</v>
+        <v>15.4974</v>
       </c>
       <c r="D10" t="n">
         <v>19.586</v>
       </c>
       <c r="E10" t="n">
+        <v>13.4677</v>
+      </c>
+      <c r="F10" t="n">
+        <v>6.9785</v>
+      </c>
+      <c r="G10" t="n">
         <v>15.6138</v>
-      </c>
-      <c r="F10" t="n">
-        <v>15.4974</v>
-      </c>
-      <c r="G10" t="n">
-        <v>6.9785</v>
       </c>
       <c r="H10" t="n">
         <v>3.9137</v>
@@ -1250,19 +1250,19 @@
         <v>109.367</v>
       </c>
       <c r="C11" t="n">
-        <v>14.5823</v>
+        <v>15.5269</v>
       </c>
       <c r="D11" t="n">
         <v>19.8684</v>
       </c>
       <c r="E11" t="n">
+        <v>14.5823</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6.9808</v>
+      </c>
+      <c r="G11" t="n">
         <v>15.6465</v>
-      </c>
-      <c r="F11" t="n">
-        <v>15.5269</v>
-      </c>
-      <c r="G11" t="n">
-        <v>6.9808</v>
       </c>
       <c r="H11" t="n">
         <v>3.9137</v>
@@ -1279,19 +1279,19 @@
         <v>109.3766</v>
       </c>
       <c r="C12" t="n">
-        <v>15.3061</v>
+        <v>15.5269</v>
       </c>
       <c r="D12" t="n">
         <v>20.2385</v>
       </c>
       <c r="E12" t="n">
+        <v>15.3061</v>
+      </c>
+      <c r="F12" t="n">
+        <v>6.9808</v>
+      </c>
+      <c r="G12" t="n">
         <v>15.6605</v>
-      </c>
-      <c r="F12" t="n">
-        <v>15.5269</v>
-      </c>
-      <c r="G12" t="n">
-        <v>6.9808</v>
       </c>
       <c r="H12" t="n">
         <v>3.9137</v>
@@ -1308,19 +1308,19 @@
         <v>109.4045</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1104</v>
+        <v>15.5269</v>
       </c>
       <c r="D13" t="n">
         <v>20.9293</v>
       </c>
       <c r="E13" t="n">
+        <v>16.1104</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6.9808</v>
+      </c>
+      <c r="G13" t="n">
         <v>16.0793</v>
-      </c>
-      <c r="F13" t="n">
-        <v>15.5269</v>
-      </c>
-      <c r="G13" t="n">
-        <v>6.9808</v>
       </c>
       <c r="H13" t="n">
         <v>3.9137</v>
@@ -1337,19 +1337,19 @@
         <v>109.4053</v>
       </c>
       <c r="C14" t="n">
-        <v>16.594</v>
+        <v>15.5269</v>
       </c>
       <c r="D14" t="n">
         <v>21.1966</v>
       </c>
       <c r="E14" t="n">
+        <v>16.594</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6.984</v>
+      </c>
+      <c r="G14" t="n">
         <v>16.2173</v>
-      </c>
-      <c r="F14" t="n">
-        <v>15.5269</v>
-      </c>
-      <c r="G14" t="n">
-        <v>6.984</v>
       </c>
       <c r="H14" t="n">
         <v>3.9137</v>
@@ -1366,19 +1366,19 @@
         <v>109.4252</v>
       </c>
       <c r="C15" t="n">
-        <v>17.2675</v>
+        <v>15.6532</v>
       </c>
       <c r="D15" t="n">
         <v>21.5646</v>
       </c>
       <c r="E15" t="n">
+        <v>17.2675</v>
+      </c>
+      <c r="F15" t="n">
+        <v>6.984</v>
+      </c>
+      <c r="G15" t="n">
         <v>16.2188</v>
-      </c>
-      <c r="F15" t="n">
-        <v>15.6532</v>
-      </c>
-      <c r="G15" t="n">
-        <v>6.984</v>
       </c>
       <c r="H15" t="n">
         <v>3.9137</v>
@@ -1395,19 +1395,19 @@
         <v>109.4733</v>
       </c>
       <c r="C16" t="n">
-        <v>18.0986</v>
+        <v>15.6532</v>
       </c>
       <c r="D16" t="n">
         <v>21.5995</v>
       </c>
       <c r="E16" t="n">
+        <v>18.0986</v>
+      </c>
+      <c r="F16" t="n">
+        <v>6.9902</v>
+      </c>
+      <c r="G16" t="n">
         <v>16.2954</v>
-      </c>
-      <c r="F16" t="n">
-        <v>15.6532</v>
-      </c>
-      <c r="G16" t="n">
-        <v>6.9902</v>
       </c>
       <c r="H16" t="n">
         <v>3.9137</v>
@@ -1424,19 +1424,19 @@
         <v>109.4743</v>
       </c>
       <c r="C17" t="n">
-        <v>18.883</v>
+        <v>15.6532</v>
       </c>
       <c r="D17" t="n">
         <v>21.6583</v>
       </c>
       <c r="E17" t="n">
+        <v>18.883</v>
+      </c>
+      <c r="F17" t="n">
+        <v>6.9905</v>
+      </c>
+      <c r="G17" t="n">
         <v>16.3329</v>
-      </c>
-      <c r="F17" t="n">
-        <v>15.6532</v>
-      </c>
-      <c r="G17" t="n">
-        <v>6.9905</v>
       </c>
       <c r="H17" t="n">
         <v>3.9137</v>
@@ -1453,19 +1453,19 @@
         <v>109.5038</v>
       </c>
       <c r="C18" t="n">
-        <v>19.765</v>
+        <v>15.6532</v>
       </c>
       <c r="D18" t="n">
         <v>21.8023</v>
       </c>
       <c r="E18" t="n">
+        <v>19.765</v>
+      </c>
+      <c r="F18" t="n">
+        <v>6.9905</v>
+      </c>
+      <c r="G18" t="n">
         <v>16.6857</v>
-      </c>
-      <c r="F18" t="n">
-        <v>15.6532</v>
-      </c>
-      <c r="G18" t="n">
-        <v>6.9905</v>
       </c>
       <c r="H18" t="n">
         <v>3.9137</v>
@@ -1482,19 +1482,19 @@
         <v>109.505</v>
       </c>
       <c r="C19" t="n">
-        <v>20.6052</v>
+        <v>15.6769</v>
       </c>
       <c r="D19" t="n">
         <v>21.9049</v>
       </c>
       <c r="E19" t="n">
+        <v>20.6052</v>
+      </c>
+      <c r="F19" t="n">
+        <v>6.994800000000001</v>
+      </c>
+      <c r="G19" t="n">
         <v>16.7093</v>
-      </c>
-      <c r="F19" t="n">
-        <v>15.6769</v>
-      </c>
-      <c r="G19" t="n">
-        <v>6.994800000000001</v>
       </c>
       <c r="H19" t="n">
         <v>3.9137</v>
@@ -1511,19 +1511,19 @@
         <v>109.6489</v>
       </c>
       <c r="C20" t="n">
-        <v>21.7337</v>
+        <v>15.7895</v>
       </c>
       <c r="D20" t="n">
         <v>22.2287</v>
       </c>
       <c r="E20" t="n">
+        <v>21.7337</v>
+      </c>
+      <c r="F20" t="n">
+        <v>6.994800000000001</v>
+      </c>
+      <c r="G20" t="n">
         <v>16.7208</v>
-      </c>
-      <c r="F20" t="n">
-        <v>15.7895</v>
-      </c>
-      <c r="G20" t="n">
-        <v>6.994800000000001</v>
       </c>
       <c r="H20" t="n">
         <v>3.9137</v>
@@ -1540,19 +1540,19 @@
         <v>109.6505</v>
       </c>
       <c r="C21" t="n">
-        <v>22.8731</v>
+        <v>15.8018</v>
       </c>
       <c r="D21" t="n">
         <v>22.4249</v>
       </c>
       <c r="E21" t="n">
+        <v>22.8731</v>
+      </c>
+      <c r="F21" t="n">
+        <v>6.994800000000001</v>
+      </c>
+      <c r="G21" t="n">
         <v>16.722</v>
-      </c>
-      <c r="F21" t="n">
-        <v>15.8018</v>
-      </c>
-      <c r="G21" t="n">
-        <v>6.994800000000001</v>
       </c>
       <c r="H21" t="n">
         <v>3.9137</v>
@@ -1569,19 +1569,19 @@
         <v>109.6827</v>
       </c>
       <c r="C22" t="n">
-        <v>24.2095</v>
+        <v>16.0337</v>
       </c>
       <c r="D22" t="n">
         <v>22.6648</v>
       </c>
       <c r="E22" t="n">
+        <v>24.2095</v>
+      </c>
+      <c r="F22" t="n">
+        <v>6.9962</v>
+      </c>
+      <c r="G22" t="n">
         <v>16.9133</v>
-      </c>
-      <c r="F22" t="n">
-        <v>16.0337</v>
-      </c>
-      <c r="G22" t="n">
-        <v>6.9962</v>
       </c>
       <c r="H22" t="n">
         <v>3.9137</v>
@@ -1598,19 +1598,19 @@
         <v>109.6929</v>
       </c>
       <c r="C23" t="n">
-        <v>25.186</v>
+        <v>16.3706</v>
       </c>
       <c r="D23" t="n">
         <v>23.3259</v>
       </c>
       <c r="E23" t="n">
+        <v>25.186</v>
+      </c>
+      <c r="F23" t="n">
+        <v>7.0082</v>
+      </c>
+      <c r="G23" t="n">
         <v>16.9138</v>
-      </c>
-      <c r="F23" t="n">
-        <v>16.3706</v>
-      </c>
-      <c r="G23" t="n">
-        <v>7.0082</v>
       </c>
       <c r="H23" t="n">
         <v>3.9137</v>
@@ -1627,19 +1627,19 @@
         <v>109.7486</v>
       </c>
       <c r="C24" t="n">
-        <v>26.2962</v>
+        <v>16.7359</v>
       </c>
       <c r="D24" t="n">
         <v>23.6406</v>
       </c>
       <c r="E24" t="n">
+        <v>26.2962</v>
+      </c>
+      <c r="F24" t="n">
+        <v>7.014399999999999</v>
+      </c>
+      <c r="G24" t="n">
         <v>16.9314</v>
-      </c>
-      <c r="F24" t="n">
-        <v>16.7359</v>
-      </c>
-      <c r="G24" t="n">
-        <v>7.014399999999999</v>
       </c>
       <c r="H24" t="n">
         <v>3.9137</v>
@@ -1656,19 +1656,19 @@
         <v>109.7587</v>
       </c>
       <c r="C25" t="n">
-        <v>27.7044</v>
+        <v>16.7359</v>
       </c>
       <c r="D25" t="n">
         <v>24.1145</v>
       </c>
       <c r="E25" t="n">
+        <v>27.7044</v>
+      </c>
+      <c r="F25" t="n">
+        <v>7.0615</v>
+      </c>
+      <c r="G25" t="n">
         <v>16.957</v>
-      </c>
-      <c r="F25" t="n">
-        <v>16.7359</v>
-      </c>
-      <c r="G25" t="n">
-        <v>7.0615</v>
       </c>
       <c r="H25" t="n">
         <v>3.9137</v>
@@ -1685,19 +1685,19 @@
         <v>109.7836</v>
       </c>
       <c r="C26" t="n">
-        <v>29.1641</v>
+        <v>16.7359</v>
       </c>
       <c r="D26" t="n">
         <v>24.9878</v>
       </c>
       <c r="E26" t="n">
+        <v>29.1641</v>
+      </c>
+      <c r="F26" t="n">
+        <v>7.063800000000001</v>
+      </c>
+      <c r="G26" t="n">
         <v>16.957</v>
-      </c>
-      <c r="F26" t="n">
-        <v>16.7359</v>
-      </c>
-      <c r="G26" t="n">
-        <v>7.063800000000001</v>
       </c>
       <c r="H26" t="n">
         <v>3.9137</v>
@@ -1714,19 +1714,19 @@
         <v>109.7839</v>
       </c>
       <c r="C27" t="n">
-        <v>30.3054</v>
+        <v>16.7359</v>
       </c>
       <c r="D27" t="n">
         <v>25.1758</v>
       </c>
       <c r="E27" t="n">
+        <v>30.3054</v>
+      </c>
+      <c r="F27" t="n">
+        <v>7.1373</v>
+      </c>
+      <c r="G27" t="n">
         <v>16.9983</v>
-      </c>
-      <c r="F27" t="n">
-        <v>16.7359</v>
-      </c>
-      <c r="G27" t="n">
-        <v>7.1373</v>
       </c>
       <c r="H27" t="n">
         <v>3.9137</v>
@@ -1743,19 +1743,19 @@
         <v>109.8056</v>
       </c>
       <c r="C28" t="n">
-        <v>31.6648</v>
+        <v>16.7359</v>
       </c>
       <c r="D28" t="n">
         <v>25.36</v>
       </c>
       <c r="E28" t="n">
+        <v>31.6648</v>
+      </c>
+      <c r="F28" t="n">
+        <v>7.1456</v>
+      </c>
+      <c r="G28" t="n">
         <v>17.0024</v>
-      </c>
-      <c r="F28" t="n">
-        <v>16.7359</v>
-      </c>
-      <c r="G28" t="n">
-        <v>7.1456</v>
       </c>
       <c r="H28" t="n">
         <v>3.9137</v>
@@ -1772,19 +1772,19 @@
         <v>109.836</v>
       </c>
       <c r="C29" t="n">
-        <v>32.742</v>
+        <v>16.7359</v>
       </c>
       <c r="D29" t="n">
         <v>25.6176</v>
       </c>
       <c r="E29" t="n">
+        <v>32.742</v>
+      </c>
+      <c r="F29" t="n">
+        <v>7.1525</v>
+      </c>
+      <c r="G29" t="n">
         <v>17.0823</v>
-      </c>
-      <c r="F29" t="n">
-        <v>16.7359</v>
-      </c>
-      <c r="G29" t="n">
-        <v>7.1525</v>
       </c>
       <c r="H29" t="n">
         <v>3.9137</v>
@@ -1801,19 +1801,19 @@
         <v>109.8373</v>
       </c>
       <c r="C30" t="n">
-        <v>34.4225</v>
+        <v>16.8387</v>
       </c>
       <c r="D30" t="n">
         <v>25.9833</v>
       </c>
       <c r="E30" t="n">
+        <v>34.4225</v>
+      </c>
+      <c r="F30" t="n">
+        <v>7.1778</v>
+      </c>
+      <c r="G30" t="n">
         <v>17.0864</v>
-      </c>
-      <c r="F30" t="n">
-        <v>16.8387</v>
-      </c>
-      <c r="G30" t="n">
-        <v>7.1778</v>
       </c>
       <c r="H30" t="n">
         <v>3.9137</v>
@@ -1830,19 +1830,19 @@
         <v>109.8765</v>
       </c>
       <c r="C31" t="n">
-        <v>35.1515</v>
+        <v>16.8387</v>
       </c>
       <c r="D31" t="n">
         <v>26.2352</v>
       </c>
       <c r="E31" t="n">
+        <v>35.1515</v>
+      </c>
+      <c r="F31" t="n">
+        <v>7.1915</v>
+      </c>
+      <c r="G31" t="n">
         <v>17.1049</v>
-      </c>
-      <c r="F31" t="n">
-        <v>16.8387</v>
-      </c>
-      <c r="G31" t="n">
-        <v>7.1915</v>
       </c>
       <c r="H31" t="n">
         <v>3.9137</v>
@@ -1859,19 +1859,19 @@
         <v>109.8827</v>
       </c>
       <c r="C32" t="n">
-        <v>35.7495</v>
+        <v>16.8387</v>
       </c>
       <c r="D32" t="n">
         <v>26.6768</v>
       </c>
       <c r="E32" t="n">
+        <v>35.7495</v>
+      </c>
+      <c r="F32" t="n">
+        <v>7.1933</v>
+      </c>
+      <c r="G32" t="n">
         <v>17.1107</v>
-      </c>
-      <c r="F32" t="n">
-        <v>16.8387</v>
-      </c>
-      <c r="G32" t="n">
-        <v>7.1933</v>
       </c>
       <c r="H32" t="n">
         <v>3.9137</v>
@@ -1888,19 +1888,19 @@
         <v>109.9037</v>
       </c>
       <c r="C33" t="n">
-        <v>37.0375</v>
+        <v>16.8387</v>
       </c>
       <c r="D33" t="n">
         <v>27.023</v>
       </c>
       <c r="E33" t="n">
+        <v>37.0375</v>
+      </c>
+      <c r="F33" t="n">
+        <v>7.2017</v>
+      </c>
+      <c r="G33" t="n">
         <v>17.1267</v>
-      </c>
-      <c r="F33" t="n">
-        <v>16.8387</v>
-      </c>
-      <c r="G33" t="n">
-        <v>7.2017</v>
       </c>
       <c r="H33" t="n">
         <v>3.9137</v>
@@ -1917,19 +1917,19 @@
         <v>109.9052</v>
       </c>
       <c r="C34" t="n">
-        <v>37.5747</v>
+        <v>16.8387</v>
       </c>
       <c r="D34" t="n">
         <v>27.1876</v>
       </c>
       <c r="E34" t="n">
+        <v>37.5747</v>
+      </c>
+      <c r="F34" t="n">
+        <v>7.2418</v>
+      </c>
+      <c r="G34" t="n">
         <v>17.1678</v>
-      </c>
-      <c r="F34" t="n">
-        <v>16.8387</v>
-      </c>
-      <c r="G34" t="n">
-        <v>7.2418</v>
       </c>
       <c r="H34" t="n">
         <v>3.9137</v>
@@ -1946,19 +1946,19 @@
         <v>109.9082</v>
       </c>
       <c r="C35" t="n">
-        <v>38.4571</v>
+        <v>16.8387</v>
       </c>
       <c r="D35" t="n">
         <v>27.696</v>
       </c>
       <c r="E35" t="n">
+        <v>38.4571</v>
+      </c>
+      <c r="F35" t="n">
+        <v>7.2518</v>
+      </c>
+      <c r="G35" t="n">
         <v>17.1918</v>
-      </c>
-      <c r="F35" t="n">
-        <v>16.8387</v>
-      </c>
-      <c r="G35" t="n">
-        <v>7.2518</v>
       </c>
       <c r="H35" t="n">
         <v>3.9137</v>
@@ -1975,19 +1975,19 @@
         <v>109.9212</v>
       </c>
       <c r="C36" t="n">
-        <v>39.4366</v>
+        <v>16.8387</v>
       </c>
       <c r="D36" t="n">
         <v>27.9834</v>
       </c>
       <c r="E36" t="n">
+        <v>39.4366</v>
+      </c>
+      <c r="F36" t="n">
+        <v>7.2518</v>
+      </c>
+      <c r="G36" t="n">
         <v>17.1953</v>
-      </c>
-      <c r="F36" t="n">
-        <v>16.8387</v>
-      </c>
-      <c r="G36" t="n">
-        <v>7.2518</v>
       </c>
       <c r="H36" t="n">
         <v>3.9137</v>
@@ -2004,19 +2004,19 @@
         <v>109.9314</v>
       </c>
       <c r="C37" t="n">
-        <v>40.5277</v>
+        <v>17.4042</v>
       </c>
       <c r="D37" t="n">
         <v>29.0403</v>
       </c>
       <c r="E37" t="n">
+        <v>40.5277</v>
+      </c>
+      <c r="F37" t="n">
+        <v>7.2518</v>
+      </c>
+      <c r="G37" t="n">
         <v>17.1959</v>
-      </c>
-      <c r="F37" t="n">
-        <v>17.4042</v>
-      </c>
-      <c r="G37" t="n">
-        <v>7.2518</v>
       </c>
       <c r="H37" t="n">
         <v>3.9137</v>
@@ -2033,19 +2033,19 @@
         <v>109.9321</v>
       </c>
       <c r="C38" t="n">
-        <v>41.5382</v>
+        <v>17.4042</v>
       </c>
       <c r="D38" t="n">
         <v>29.5172</v>
       </c>
       <c r="E38" t="n">
+        <v>41.5382</v>
+      </c>
+      <c r="F38" t="n">
+        <v>7.2518</v>
+      </c>
+      <c r="G38" t="n">
         <v>17.196</v>
-      </c>
-      <c r="F38" t="n">
-        <v>17.4042</v>
-      </c>
-      <c r="G38" t="n">
-        <v>7.2518</v>
       </c>
       <c r="H38" t="n">
         <v>3.9137</v>
@@ -2062,19 +2062,19 @@
         <v>109.9321</v>
       </c>
       <c r="C39" t="n">
-        <v>42.8823</v>
+        <v>17.4042</v>
       </c>
       <c r="D39" t="n">
         <v>29.893</v>
       </c>
       <c r="E39" t="n">
+        <v>42.8823</v>
+      </c>
+      <c r="F39" t="n">
+        <v>7.2518</v>
+      </c>
+      <c r="G39" t="n">
         <v>17.1985</v>
-      </c>
-      <c r="F39" t="n">
-        <v>17.4042</v>
-      </c>
-      <c r="G39" t="n">
-        <v>7.2518</v>
       </c>
       <c r="H39" t="n">
         <v>3.9137</v>
@@ -2091,19 +2091,19 @@
         <v>109.9518</v>
       </c>
       <c r="C40" t="n">
-        <v>44.3004</v>
+        <v>17.4042</v>
       </c>
       <c r="D40" t="n">
         <v>30.2145</v>
       </c>
       <c r="E40" t="n">
+        <v>44.3004</v>
+      </c>
+      <c r="F40" t="n">
+        <v>7.2518</v>
+      </c>
+      <c r="G40" t="n">
         <v>17.199</v>
-      </c>
-      <c r="F40" t="n">
-        <v>17.4042</v>
-      </c>
-      <c r="G40" t="n">
-        <v>7.2518</v>
       </c>
       <c r="H40" t="n">
         <v>3.9137</v>
@@ -2120,19 +2120,19 @@
         <v>109.9548</v>
       </c>
       <c r="C41" t="n">
-        <v>45.929</v>
+        <v>17.4042</v>
       </c>
       <c r="D41" t="n">
         <v>30.6802</v>
       </c>
       <c r="E41" t="n">
+        <v>45.929</v>
+      </c>
+      <c r="F41" t="n">
+        <v>7.2518</v>
+      </c>
+      <c r="G41" t="n">
         <v>17.3457</v>
-      </c>
-      <c r="F41" t="n">
-        <v>17.4042</v>
-      </c>
-      <c r="G41" t="n">
-        <v>7.2518</v>
       </c>
       <c r="H41" t="n">
         <v>3.9137</v>
@@ -2149,19 +2149,19 @@
         <v>109.9548</v>
       </c>
       <c r="C42" t="n">
-        <v>47.1933</v>
+        <v>17.4042</v>
       </c>
       <c r="D42" t="n">
         <v>30.9016</v>
       </c>
       <c r="E42" t="n">
+        <v>47.1933</v>
+      </c>
+      <c r="F42" t="n">
+        <v>7.2518</v>
+      </c>
+      <c r="G42" t="n">
         <v>17.3462</v>
-      </c>
-      <c r="F42" t="n">
-        <v>17.4042</v>
-      </c>
-      <c r="G42" t="n">
-        <v>7.2518</v>
       </c>
       <c r="H42" t="n">
         <v>3.9137</v>
@@ -2178,19 +2178,19 @@
         <v>109.9595</v>
       </c>
       <c r="C43" t="n">
-        <v>48.4345</v>
+        <v>17.4042</v>
       </c>
       <c r="D43" t="n">
         <v>31.1283</v>
       </c>
       <c r="E43" t="n">
+        <v>48.4345</v>
+      </c>
+      <c r="F43" t="n">
+        <v>7.2818</v>
+      </c>
+      <c r="G43" t="n">
         <v>17.3868</v>
-      </c>
-      <c r="F43" t="n">
-        <v>17.4042</v>
-      </c>
-      <c r="G43" t="n">
-        <v>7.2818</v>
       </c>
       <c r="H43" t="n">
         <v>3.9137</v>
@@ -2207,19 +2207,19 @@
         <v>109.9595</v>
       </c>
       <c r="C44" t="n">
-        <v>49.962</v>
+        <v>17.4042</v>
       </c>
       <c r="D44" t="n">
         <v>31.5212</v>
       </c>
       <c r="E44" t="n">
+        <v>49.962</v>
+      </c>
+      <c r="F44" t="n">
+        <v>7.2824</v>
+      </c>
+      <c r="G44" t="n">
         <v>17.3881</v>
-      </c>
-      <c r="F44" t="n">
-        <v>17.4042</v>
-      </c>
-      <c r="G44" t="n">
-        <v>7.2824</v>
       </c>
       <c r="H44" t="n">
         <v>3.9137</v>
@@ -2236,19 +2236,19 @@
         <v>109.9764</v>
       </c>
       <c r="C45" t="n">
-        <v>51.1059</v>
+        <v>17.4042</v>
       </c>
       <c r="D45" t="n">
         <v>31.8485</v>
       </c>
       <c r="E45" t="n">
+        <v>51.1059</v>
+      </c>
+      <c r="F45" t="n">
+        <v>7.2824</v>
+      </c>
+      <c r="G45" t="n">
         <v>17.3902</v>
-      </c>
-      <c r="F45" t="n">
-        <v>17.4042</v>
-      </c>
-      <c r="G45" t="n">
-        <v>7.2824</v>
       </c>
       <c r="H45" t="n">
         <v>3.9137</v>
@@ -2265,19 +2265,19 @@
         <v>109.9764</v>
       </c>
       <c r="C46" t="n">
-        <v>52.4351</v>
+        <v>17.4042</v>
       </c>
       <c r="D46" t="n">
         <v>32.0042</v>
       </c>
       <c r="E46" t="n">
+        <v>52.4351</v>
+      </c>
+      <c r="F46" t="n">
+        <v>7.2824</v>
+      </c>
+      <c r="G46" t="n">
         <v>17.46</v>
-      </c>
-      <c r="F46" t="n">
-        <v>17.4042</v>
-      </c>
-      <c r="G46" t="n">
-        <v>7.2824</v>
       </c>
       <c r="H46" t="n">
         <v>3.9137</v>
@@ -2294,19 +2294,19 @@
         <v>109.9815</v>
       </c>
       <c r="C47" t="n">
-        <v>53.8829</v>
+        <v>17.4042</v>
       </c>
       <c r="D47" t="n">
         <v>32.4956</v>
       </c>
       <c r="E47" t="n">
+        <v>53.8829</v>
+      </c>
+      <c r="F47" t="n">
+        <v>7.5723</v>
+      </c>
+      <c r="G47" t="n">
         <v>17.4963</v>
-      </c>
-      <c r="F47" t="n">
-        <v>17.4042</v>
-      </c>
-      <c r="G47" t="n">
-        <v>7.5723</v>
       </c>
       <c r="H47" t="n">
         <v>3.9137</v>
@@ -2323,19 +2323,19 @@
         <v>110.0103</v>
       </c>
       <c r="C48" t="n">
-        <v>55.4687</v>
+        <v>17.4042</v>
       </c>
       <c r="D48" t="n">
         <v>32.6441</v>
       </c>
       <c r="E48" t="n">
+        <v>55.4687</v>
+      </c>
+      <c r="F48" t="n">
+        <v>7.5723</v>
+      </c>
+      <c r="G48" t="n">
         <v>17.4963</v>
-      </c>
-      <c r="F48" t="n">
-        <v>17.4042</v>
-      </c>
-      <c r="G48" t="n">
-        <v>7.5723</v>
       </c>
       <c r="H48" t="n">
         <v>3.9137</v>
@@ -2352,19 +2352,19 @@
         <v>110.0133</v>
       </c>
       <c r="C49" t="n">
-        <v>56.851</v>
+        <v>17.4042</v>
       </c>
       <c r="D49" t="n">
         <v>32.8931</v>
       </c>
       <c r="E49" t="n">
+        <v>56.851</v>
+      </c>
+      <c r="F49" t="n">
+        <v>7.5723</v>
+      </c>
+      <c r="G49" t="n">
         <v>17.4963</v>
-      </c>
-      <c r="F49" t="n">
-        <v>17.4042</v>
-      </c>
-      <c r="G49" t="n">
-        <v>7.5723</v>
       </c>
       <c r="H49" t="n">
         <v>3.9137</v>
@@ -2381,19 +2381,19 @@
         <v>110.0133</v>
       </c>
       <c r="C50" t="n">
-        <v>58.424</v>
+        <v>17.4042</v>
       </c>
       <c r="D50" t="n">
         <v>33.22069999999999</v>
       </c>
       <c r="E50" t="n">
+        <v>58.424</v>
+      </c>
+      <c r="F50" t="n">
+        <v>7.573600000000001</v>
+      </c>
+      <c r="G50" t="n">
         <v>17.8819</v>
-      </c>
-      <c r="F50" t="n">
-        <v>17.4042</v>
-      </c>
-      <c r="G50" t="n">
-        <v>7.573600000000001</v>
       </c>
       <c r="H50" t="n">
         <v>3.9137</v>
@@ -2410,19 +2410,19 @@
         <v>110.0607</v>
       </c>
       <c r="C51" t="n">
-        <v>59.3316</v>
+        <v>17.4042</v>
       </c>
       <c r="D51" t="n">
         <v>33.4106</v>
       </c>
       <c r="E51" t="n">
+        <v>59.3316</v>
+      </c>
+      <c r="F51" t="n">
+        <v>7.573600000000001</v>
+      </c>
+      <c r="G51" t="n">
         <v>17.9351</v>
-      </c>
-      <c r="F51" t="n">
-        <v>17.4042</v>
-      </c>
-      <c r="G51" t="n">
-        <v>7.573600000000001</v>
       </c>
       <c r="H51" t="n">
         <v>3.9137</v>
@@ -2439,19 +2439,19 @@
         <v>110.0923</v>
       </c>
       <c r="C52" t="n">
-        <v>60.2548</v>
+        <v>17.4042</v>
       </c>
       <c r="D52" t="n">
         <v>33.6086</v>
       </c>
       <c r="E52" t="n">
+        <v>60.2548</v>
+      </c>
+      <c r="F52" t="n">
+        <v>7.573600000000001</v>
+      </c>
+      <c r="G52" t="n">
         <v>17.9663</v>
-      </c>
-      <c r="F52" t="n">
-        <v>17.4042</v>
-      </c>
-      <c r="G52" t="n">
-        <v>7.573600000000001</v>
       </c>
       <c r="H52" t="n">
         <v>3.9137</v>
@@ -2468,19 +2468,19 @@
         <v>110.1037</v>
       </c>
       <c r="C53" t="n">
-        <v>61.1996</v>
+        <v>17.4042</v>
       </c>
       <c r="D53" t="n">
         <v>33.6356</v>
       </c>
       <c r="E53" t="n">
+        <v>61.1996</v>
+      </c>
+      <c r="F53" t="n">
+        <v>7.573600000000001</v>
+      </c>
+      <c r="G53" t="n">
         <v>18.0116</v>
-      </c>
-      <c r="F53" t="n">
-        <v>17.4042</v>
-      </c>
-      <c r="G53" t="n">
-        <v>7.573600000000001</v>
       </c>
       <c r="H53" t="n">
         <v>3.9137</v>
@@ -2497,19 +2497,19 @@
         <v>110.1082</v>
       </c>
       <c r="C54" t="n">
-        <v>62.003</v>
+        <v>19.0768</v>
       </c>
       <c r="D54" t="n">
         <v>33.6356</v>
       </c>
       <c r="E54" t="n">
+        <v>62.003</v>
+      </c>
+      <c r="F54" t="n">
+        <v>7.573600000000001</v>
+      </c>
+      <c r="G54" t="n">
         <v>18.0596</v>
-      </c>
-      <c r="F54" t="n">
-        <v>19.0768</v>
-      </c>
-      <c r="G54" t="n">
-        <v>7.573600000000001</v>
       </c>
       <c r="H54" t="n">
         <v>3.9137</v>
@@ -2526,19 +2526,19 @@
         <v>110.1122</v>
       </c>
       <c r="C55" t="n">
-        <v>62.788</v>
+        <v>19.0768</v>
       </c>
       <c r="D55" t="n">
         <v>33.8471</v>
       </c>
       <c r="E55" t="n">
+        <v>62.788</v>
+      </c>
+      <c r="F55" t="n">
+        <v>7.573600000000001</v>
+      </c>
+      <c r="G55" t="n">
         <v>18.0618</v>
-      </c>
-      <c r="F55" t="n">
-        <v>19.0768</v>
-      </c>
-      <c r="G55" t="n">
-        <v>7.573600000000001</v>
       </c>
       <c r="H55" t="n">
         <v>3.9137</v>
@@ -2555,19 +2555,19 @@
         <v>110.1122</v>
       </c>
       <c r="C56" t="n">
-        <v>63.6554</v>
+        <v>19.0768</v>
       </c>
       <c r="D56" t="n">
         <v>33.8876</v>
       </c>
       <c r="E56" t="n">
+        <v>63.6554</v>
+      </c>
+      <c r="F56" t="n">
+        <v>7.573600000000001</v>
+      </c>
+      <c r="G56" t="n">
         <v>18.0646</v>
-      </c>
-      <c r="F56" t="n">
-        <v>19.0768</v>
-      </c>
-      <c r="G56" t="n">
-        <v>7.573600000000001</v>
       </c>
       <c r="H56" t="n">
         <v>3.9137</v>
@@ -2584,19 +2584,19 @@
         <v>110.1662</v>
       </c>
       <c r="C57" t="n">
-        <v>64.3811</v>
+        <v>19.0768</v>
       </c>
       <c r="D57" t="n">
         <v>34.1037</v>
       </c>
       <c r="E57" t="n">
+        <v>64.3811</v>
+      </c>
+      <c r="F57" t="n">
+        <v>7.573600000000001</v>
+      </c>
+      <c r="G57" t="n">
         <v>18.1046</v>
-      </c>
-      <c r="F57" t="n">
-        <v>19.0768</v>
-      </c>
-      <c r="G57" t="n">
-        <v>7.573600000000001</v>
       </c>
       <c r="H57" t="n">
         <v>3.9137</v>
@@ -2613,19 +2613,19 @@
         <v>110.2405</v>
       </c>
       <c r="C58" t="n">
-        <v>65.989</v>
+        <v>19.0768</v>
       </c>
       <c r="D58" t="n">
         <v>34.41869999999999</v>
       </c>
       <c r="E58" t="n">
+        <v>65.989</v>
+      </c>
+      <c r="F58" t="n">
+        <v>7.573600000000001</v>
+      </c>
+      <c r="G58" t="n">
         <v>18.1067</v>
-      </c>
-      <c r="F58" t="n">
-        <v>19.0768</v>
-      </c>
-      <c r="G58" t="n">
-        <v>7.573600000000001</v>
       </c>
       <c r="H58" t="n">
         <v>3.9137</v>
@@ -2642,19 +2642,19 @@
         <v>110.2734</v>
       </c>
       <c r="C59" t="n">
-        <v>67.35510000000001</v>
+        <v>19.0768</v>
       </c>
       <c r="D59" t="n">
         <v>34.41869999999999</v>
       </c>
       <c r="E59" t="n">
+        <v>67.35510000000001</v>
+      </c>
+      <c r="F59" t="n">
+        <v>7.573600000000001</v>
+      </c>
+      <c r="G59" t="n">
         <v>18.1365</v>
-      </c>
-      <c r="F59" t="n">
-        <v>19.0768</v>
-      </c>
-      <c r="G59" t="n">
-        <v>7.573600000000001</v>
       </c>
       <c r="H59" t="n">
         <v>3.9137</v>
@@ -2671,19 +2671,19 @@
         <v>110.2734</v>
       </c>
       <c r="C60" t="n">
-        <v>68.26310000000001</v>
+        <v>19.0768</v>
       </c>
       <c r="D60" t="n">
         <v>34.41869999999999</v>
       </c>
       <c r="E60" t="n">
+        <v>68.26310000000001</v>
+      </c>
+      <c r="F60" t="n">
+        <v>7.573600000000001</v>
+      </c>
+      <c r="G60" t="n">
         <v>18.1365</v>
-      </c>
-      <c r="F60" t="n">
-        <v>19.0768</v>
-      </c>
-      <c r="G60" t="n">
-        <v>7.573600000000001</v>
       </c>
       <c r="H60" t="n">
         <v>3.9137</v>
@@ -2700,19 +2700,19 @@
         <v>110.2734</v>
       </c>
       <c r="C61" t="n">
-        <v>69.3095</v>
+        <v>19.0768</v>
       </c>
       <c r="D61" t="n">
         <v>34.7697</v>
       </c>
       <c r="E61" t="n">
+        <v>69.3095</v>
+      </c>
+      <c r="F61" t="n">
+        <v>7.573600000000001</v>
+      </c>
+      <c r="G61" t="n">
         <v>18.145</v>
-      </c>
-      <c r="F61" t="n">
-        <v>19.0768</v>
-      </c>
-      <c r="G61" t="n">
-        <v>7.573600000000001</v>
       </c>
       <c r="H61" t="n">
         <v>3.9137</v>
@@ -2729,19 +2729,19 @@
         <v>110.2946</v>
       </c>
       <c r="C62" t="n">
-        <v>70.5573</v>
+        <v>19.0768</v>
       </c>
       <c r="D62" t="n">
         <v>34.7697</v>
       </c>
       <c r="E62" t="n">
+        <v>70.5573</v>
+      </c>
+      <c r="F62" t="n">
+        <v>7.573600000000001</v>
+      </c>
+      <c r="G62" t="n">
         <v>18.1451</v>
-      </c>
-      <c r="F62" t="n">
-        <v>19.0768</v>
-      </c>
-      <c r="G62" t="n">
-        <v>7.573600000000001</v>
       </c>
       <c r="H62" t="n">
         <v>3.9137</v>
@@ -2758,19 +2758,19 @@
         <v>110.2946</v>
       </c>
       <c r="C63" t="n">
-        <v>71.9028</v>
+        <v>19.0768</v>
       </c>
       <c r="D63" t="n">
         <v>34.8282</v>
       </c>
       <c r="E63" t="n">
+        <v>71.9028</v>
+      </c>
+      <c r="F63" t="n">
+        <v>7.573600000000001</v>
+      </c>
+      <c r="G63" t="n">
         <v>18.1451</v>
-      </c>
-      <c r="F63" t="n">
-        <v>19.0768</v>
-      </c>
-      <c r="G63" t="n">
-        <v>7.573600000000001</v>
       </c>
       <c r="H63" t="n">
         <v>3.9137</v>
@@ -2787,19 +2787,19 @@
         <v>110.2998</v>
       </c>
       <c r="C64" t="n">
-        <v>73.7351</v>
+        <v>19.0768</v>
       </c>
       <c r="D64" t="n">
         <v>34.8282</v>
       </c>
       <c r="E64" t="n">
+        <v>73.7351</v>
+      </c>
+      <c r="F64" t="n">
+        <v>7.5747</v>
+      </c>
+      <c r="G64" t="n">
         <v>18.1715</v>
-      </c>
-      <c r="F64" t="n">
-        <v>19.0768</v>
-      </c>
-      <c r="G64" t="n">
-        <v>7.5747</v>
       </c>
       <c r="H64" t="n">
         <v>3.9137</v>
@@ -2816,19 +2816,19 @@
         <v>110.2999</v>
       </c>
       <c r="C65" t="n">
-        <v>74.60850000000001</v>
+        <v>19.0768</v>
       </c>
       <c r="D65" t="n">
         <v>34.8282</v>
       </c>
       <c r="E65" t="n">
+        <v>74.60850000000001</v>
+      </c>
+      <c r="F65" t="n">
+        <v>7.5747</v>
+      </c>
+      <c r="G65" t="n">
         <v>18.2115</v>
-      </c>
-      <c r="F65" t="n">
-        <v>19.0768</v>
-      </c>
-      <c r="G65" t="n">
-        <v>7.5747</v>
       </c>
       <c r="H65" t="n">
         <v>3.9137</v>
@@ -2845,19 +2845,19 @@
         <v>110.3043</v>
       </c>
       <c r="C66" t="n">
-        <v>75.3052</v>
+        <v>19.0768</v>
       </c>
       <c r="D66" t="n">
         <v>34.8282</v>
       </c>
       <c r="E66" t="n">
+        <v>75.3052</v>
+      </c>
+      <c r="F66" t="n">
+        <v>7.5747</v>
+      </c>
+      <c r="G66" t="n">
         <v>18.2115</v>
-      </c>
-      <c r="F66" t="n">
-        <v>19.0768</v>
-      </c>
-      <c r="G66" t="n">
-        <v>7.5747</v>
       </c>
       <c r="H66" t="n">
         <v>3.9137</v>
@@ -2874,19 +2874,19 @@
         <v>110.327</v>
       </c>
       <c r="C67" t="n">
-        <v>75.9914</v>
+        <v>19.0768</v>
       </c>
       <c r="D67" t="n">
         <v>34.8282</v>
       </c>
       <c r="E67" t="n">
+        <v>75.9914</v>
+      </c>
+      <c r="F67" t="n">
+        <v>7.5747</v>
+      </c>
+      <c r="G67" t="n">
         <v>18.2115</v>
-      </c>
-      <c r="F67" t="n">
-        <v>19.0768</v>
-      </c>
-      <c r="G67" t="n">
-        <v>7.5747</v>
       </c>
       <c r="H67" t="n">
         <v>3.9137</v>
@@ -2903,19 +2903,19 @@
         <v>110.334</v>
       </c>
       <c r="C68" t="n">
-        <v>76.3515</v>
+        <v>19.0768</v>
       </c>
       <c r="D68" t="n">
         <v>34.8912</v>
       </c>
       <c r="E68" t="n">
+        <v>76.3515</v>
+      </c>
+      <c r="F68" t="n">
+        <v>7.5747</v>
+      </c>
+      <c r="G68" t="n">
         <v>18.2157</v>
-      </c>
-      <c r="F68" t="n">
-        <v>19.0768</v>
-      </c>
-      <c r="G68" t="n">
-        <v>7.5747</v>
       </c>
       <c r="H68" t="n">
         <v>3.9137</v>
@@ -2932,19 +2932,19 @@
         <v>110.334</v>
       </c>
       <c r="C69" t="n">
-        <v>77.2662</v>
+        <v>20.0677</v>
       </c>
       <c r="D69" t="n">
         <v>34.9542</v>
       </c>
       <c r="E69" t="n">
+        <v>77.2662</v>
+      </c>
+      <c r="F69" t="n">
+        <v>7.5796</v>
+      </c>
+      <c r="G69" t="n">
         <v>18.2257</v>
-      </c>
-      <c r="F69" t="n">
-        <v>20.0677</v>
-      </c>
-      <c r="G69" t="n">
-        <v>7.5796</v>
       </c>
       <c r="H69" t="n">
         <v>3.9137</v>
@@ -2961,19 +2961,19 @@
         <v>110.334</v>
       </c>
       <c r="C70" t="n">
-        <v>77.2662</v>
+        <v>20.1825</v>
       </c>
       <c r="D70" t="n">
         <v>34.9542</v>
       </c>
       <c r="E70" t="n">
+        <v>77.2662</v>
+      </c>
+      <c r="F70" t="n">
+        <v>7.5796</v>
+      </c>
+      <c r="G70" t="n">
         <v>18.2507</v>
-      </c>
-      <c r="F70" t="n">
-        <v>20.1825</v>
-      </c>
-      <c r="G70" t="n">
-        <v>7.5796</v>
       </c>
       <c r="H70" t="n">
         <v>3.9137</v>

--- a/output/Data and Chart Outputs/brazil_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/brazil_power_capacity.xlsx
@@ -25,8 +25,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -66,12 +66,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -822,7 +823,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -851,7 +851,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
@@ -866,7 +865,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
@@ -902,7 +900,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
@@ -982,7 +979,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -1011,7 +1008,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -1040,7 +1037,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -1069,7 +1066,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -1098,7 +1095,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -1127,7 +1124,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -1156,7 +1153,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -1185,7 +1182,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -1214,7 +1211,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -1243,7 +1240,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -1272,7 +1269,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -1301,7 +1298,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -1330,7 +1327,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -1359,7 +1356,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -1388,7 +1385,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -1417,7 +1414,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -1446,7 +1443,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -1475,7 +1472,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -1504,7 +1501,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -1533,7 +1530,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -1562,7 +1559,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -1591,7 +1588,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -1620,7 +1617,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -1649,7 +1646,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -1678,7 +1675,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -1707,7 +1704,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -1736,7 +1733,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -1765,7 +1762,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -1794,7 +1791,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -1823,7 +1820,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -1852,7 +1849,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -1881,7 +1878,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -1910,7 +1907,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -1939,7 +1936,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -1968,7 +1965,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -1997,7 +1994,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -2026,7 +2023,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -2055,7 +2052,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -2084,7 +2081,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -2113,7 +2110,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -2142,7 +2139,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -2171,7 +2168,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -2200,7 +2197,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -2229,7 +2226,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -2258,7 +2255,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -2287,7 +2284,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -2316,7 +2313,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -2345,7 +2342,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -2374,7 +2371,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -2403,7 +2400,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -2432,7 +2429,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -2461,7 +2458,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -2490,7 +2487,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -2519,7 +2516,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -2548,7 +2545,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -2577,7 +2574,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -2606,7 +2603,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -2635,7 +2632,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -2664,7 +2661,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -2693,7 +2690,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -2722,7 +2719,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2751,7 +2748,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -2780,7 +2777,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -2809,7 +2806,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -2838,7 +2835,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -2867,7 +2864,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -2896,7 +2893,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -2925,7 +2922,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n">
+      <c r="A69" s="5" t="n">
         <v>46235</v>
       </c>
       <c r="B69" t="n">
@@ -2954,7 +2951,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="n">
+      <c r="A70" s="5" t="n">
         <v>46266</v>
       </c>
       <c r="B70" t="n">

--- a/output/Data and Chart Outputs/brazil_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/brazil_power_capacity.xlsx
@@ -25,8 +25,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="mmm/yy"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -66,13 +66,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -823,6 +822,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RETIREMENTS: neither register has a decommissioning date. Retired plants are removed from SIGA, so months back-filled on the first run (2021 to Sep 2026) count only plants still registered today; capacity retired since 2021 (mainly old oil/diesel units) is missing from them. Each later run keeps the months already saved and recomputes only the latest two, so retirements from then on show up.</t>
+          <t>RETIREMENTS: neither register has a decommissioning date. Retired plants are removed from SIGA, so a rebuild from today's register misses capacity retired since 2021 (mainly old oil/diesel thermal units). Back-filled months (Jan 2021 to Sep 2026) are therefore recomputed on every run and topped up to ANEEL's own published thermal (UTE) totals: the gap at each published date (2.2 GW end-2021, 1.5 GW end-2022, ...) is interpolated between dates, tapered to 0 at the latest month and added to Oil_MW. From Oct 2026 each saved month is kept as computed (only the latest two are recomputed), so later retirements show up directly.</t>
         </is>
       </c>
     </row>
@@ -851,6 +851,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
@@ -865,6 +866,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
@@ -900,6 +902,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
@@ -979,7 +982,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -995,7 +998,7 @@
         <v>9.463200000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>6.8934</v>
+        <v>9.134399999999999</v>
       </c>
       <c r="G2" t="n">
         <v>15.4085</v>
@@ -1008,7 +1011,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -1024,7 +1027,7 @@
         <v>9.786100000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>6.9028</v>
+        <v>9.143799999999999</v>
       </c>
       <c r="G3" t="n">
         <v>15.426</v>
@@ -1037,7 +1040,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -1053,7 +1056,7 @@
         <v>10.2781</v>
       </c>
       <c r="F4" t="n">
-        <v>6.9315</v>
+        <v>9.172499999999999</v>
       </c>
       <c r="G4" t="n">
         <v>15.4351</v>
@@ -1066,7 +1069,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -1082,7 +1085,7 @@
         <v>10.6506</v>
       </c>
       <c r="F5" t="n">
-        <v>6.9739</v>
+        <v>9.2149</v>
       </c>
       <c r="G5" t="n">
         <v>15.4904</v>
@@ -1095,7 +1098,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -1111,7 +1114,7 @@
         <v>11.0853</v>
       </c>
       <c r="F6" t="n">
-        <v>6.9739</v>
+        <v>9.2149</v>
       </c>
       <c r="G6" t="n">
         <v>15.5156</v>
@@ -1124,7 +1127,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -1140,7 +1143,7 @@
         <v>11.5629</v>
       </c>
       <c r="F7" t="n">
-        <v>6.9739</v>
+        <v>9.2149</v>
       </c>
       <c r="G7" t="n">
         <v>15.5595</v>
@@ -1153,7 +1156,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -1169,7 +1172,7 @@
         <v>12.0824</v>
       </c>
       <c r="F8" t="n">
-        <v>6.9739</v>
+        <v>9.2149</v>
       </c>
       <c r="G8" t="n">
         <v>15.5602</v>
@@ -1182,7 +1185,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -1198,7 +1201,7 @@
         <v>12.8917</v>
       </c>
       <c r="F9" t="n">
-        <v>6.9757</v>
+        <v>9.216700000000001</v>
       </c>
       <c r="G9" t="n">
         <v>15.6108</v>
@@ -1211,7 +1214,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -1227,7 +1230,7 @@
         <v>13.4677</v>
       </c>
       <c r="F10" t="n">
-        <v>6.9785</v>
+        <v>9.2195</v>
       </c>
       <c r="G10" t="n">
         <v>15.6138</v>
@@ -1240,7 +1243,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -1256,7 +1259,7 @@
         <v>14.5823</v>
       </c>
       <c r="F11" t="n">
-        <v>6.9808</v>
+        <v>9.2218</v>
       </c>
       <c r="G11" t="n">
         <v>15.6465</v>
@@ -1269,7 +1272,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -1285,7 +1288,7 @@
         <v>15.3061</v>
       </c>
       <c r="F12" t="n">
-        <v>6.9808</v>
+        <v>9.2218</v>
       </c>
       <c r="G12" t="n">
         <v>15.6605</v>
@@ -1298,7 +1301,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -1314,7 +1317,7 @@
         <v>16.1104</v>
       </c>
       <c r="F13" t="n">
-        <v>6.9808</v>
+        <v>9.2218</v>
       </c>
       <c r="G13" t="n">
         <v>16.0793</v>
@@ -1327,7 +1330,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -1343,7 +1346,7 @@
         <v>16.594</v>
       </c>
       <c r="F14" t="n">
-        <v>6.984</v>
+        <v>9.1655</v>
       </c>
       <c r="G14" t="n">
         <v>16.2173</v>
@@ -1356,7 +1359,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -1372,7 +1375,7 @@
         <v>17.2675</v>
       </c>
       <c r="F15" t="n">
-        <v>6.984</v>
+        <v>9.106</v>
       </c>
       <c r="G15" t="n">
         <v>16.2188</v>
@@ -1385,7 +1388,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -1401,7 +1404,7 @@
         <v>18.0986</v>
       </c>
       <c r="F16" t="n">
-        <v>6.9902</v>
+        <v>9.052700000000002</v>
       </c>
       <c r="G16" t="n">
         <v>16.2954</v>
@@ -1414,7 +1417,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -1430,7 +1433,7 @@
         <v>18.883</v>
       </c>
       <c r="F17" t="n">
-        <v>6.9905</v>
+        <v>8.993600000000001</v>
       </c>
       <c r="G17" t="n">
         <v>16.3329</v>
@@ -1443,7 +1446,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -1459,7 +1462,7 @@
         <v>19.765</v>
       </c>
       <c r="F18" t="n">
-        <v>6.9905</v>
+        <v>8.934100000000001</v>
       </c>
       <c r="G18" t="n">
         <v>16.6857</v>
@@ -1472,7 +1475,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -1488,7 +1491,7 @@
         <v>20.6052</v>
       </c>
       <c r="F19" t="n">
-        <v>6.994800000000001</v>
+        <v>8.879</v>
       </c>
       <c r="G19" t="n">
         <v>16.7093</v>
@@ -1501,7 +1504,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -1517,7 +1520,7 @@
         <v>21.7337</v>
       </c>
       <c r="F20" t="n">
-        <v>6.994800000000001</v>
+        <v>8.8195</v>
       </c>
       <c r="G20" t="n">
         <v>16.7208</v>
@@ -1530,7 +1533,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -1546,7 +1549,7 @@
         <v>22.8731</v>
       </c>
       <c r="F21" t="n">
-        <v>6.994800000000001</v>
+        <v>8.76</v>
       </c>
       <c r="G21" t="n">
         <v>16.722</v>
@@ -1559,7 +1562,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -1575,7 +1578,7 @@
         <v>24.2095</v>
       </c>
       <c r="F22" t="n">
-        <v>6.9962</v>
+        <v>8.702</v>
       </c>
       <c r="G22" t="n">
         <v>16.9133</v>
@@ -1588,7 +1591,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -1604,7 +1607,7 @@
         <v>25.186</v>
       </c>
       <c r="F23" t="n">
-        <v>7.0082</v>
+        <v>8.654399999999999</v>
       </c>
       <c r="G23" t="n">
         <v>16.9138</v>
@@ -1617,7 +1620,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -1633,7 +1636,7 @@
         <v>26.2962</v>
       </c>
       <c r="F24" t="n">
-        <v>7.014399999999999</v>
+        <v>8.601100000000001</v>
       </c>
       <c r="G24" t="n">
         <v>16.9314</v>
@@ -1646,7 +1649,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -1662,7 +1665,7 @@
         <v>27.7044</v>
       </c>
       <c r="F25" t="n">
-        <v>7.0615</v>
+        <v>8.588799999999999</v>
       </c>
       <c r="G25" t="n">
         <v>16.957</v>
@@ -1675,7 +1678,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -1691,7 +1694,7 @@
         <v>29.1641</v>
       </c>
       <c r="F26" t="n">
-        <v>7.063800000000001</v>
+        <v>8.5733</v>
       </c>
       <c r="G26" t="n">
         <v>16.957</v>
@@ -1704,7 +1707,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -1720,7 +1723,7 @@
         <v>30.3054</v>
       </c>
       <c r="F27" t="n">
-        <v>7.1373</v>
+        <v>8.629</v>
       </c>
       <c r="G27" t="n">
         <v>16.9983</v>
@@ -1733,7 +1736,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -1749,7 +1752,7 @@
         <v>31.6648</v>
       </c>
       <c r="F28" t="n">
-        <v>7.1456</v>
+        <v>8.6195</v>
       </c>
       <c r="G28" t="n">
         <v>17.0024</v>
@@ -1762,7 +1765,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -1778,7 +1781,7 @@
         <v>32.742</v>
       </c>
       <c r="F29" t="n">
-        <v>7.1525</v>
+        <v>8.608499999999999</v>
       </c>
       <c r="G29" t="n">
         <v>17.0823</v>
@@ -1791,7 +1794,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -1807,7 +1810,7 @@
         <v>34.4225</v>
       </c>
       <c r="F30" t="n">
-        <v>7.1778</v>
+        <v>8.616</v>
       </c>
       <c r="G30" t="n">
         <v>17.0864</v>
@@ -1820,7 +1823,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -1836,7 +1839,7 @@
         <v>35.1515</v>
       </c>
       <c r="F31" t="n">
-        <v>7.1915</v>
+        <v>8.612</v>
       </c>
       <c r="G31" t="n">
         <v>17.1049</v>
@@ -1849,7 +1852,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -1865,7 +1868,7 @@
         <v>35.7495</v>
       </c>
       <c r="F32" t="n">
-        <v>7.1933</v>
+        <v>8.5959</v>
       </c>
       <c r="G32" t="n">
         <v>17.1107</v>
@@ -1878,7 +1881,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -1894,7 +1897,7 @@
         <v>37.0375</v>
       </c>
       <c r="F33" t="n">
-        <v>7.2017</v>
+        <v>8.586600000000001</v>
       </c>
       <c r="G33" t="n">
         <v>17.1267</v>
@@ -1907,7 +1910,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -1923,7 +1926,7 @@
         <v>37.5747</v>
       </c>
       <c r="F34" t="n">
-        <v>7.2418</v>
+        <v>8.6089</v>
       </c>
       <c r="G34" t="n">
         <v>17.1678</v>
@@ -1936,7 +1939,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -1952,7 +1955,7 @@
         <v>38.4571</v>
       </c>
       <c r="F35" t="n">
-        <v>7.2518</v>
+        <v>8.601100000000001</v>
       </c>
       <c r="G35" t="n">
         <v>17.1918</v>
@@ -1965,7 +1968,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -1981,7 +1984,7 @@
         <v>39.4366</v>
       </c>
       <c r="F36" t="n">
-        <v>7.2518</v>
+        <v>8.583299999999999</v>
       </c>
       <c r="G36" t="n">
         <v>17.1953</v>
@@ -1994,7 +1997,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -2010,7 +2013,7 @@
         <v>40.5277</v>
       </c>
       <c r="F37" t="n">
-        <v>7.2518</v>
+        <v>8.494999999999999</v>
       </c>
       <c r="G37" t="n">
         <v>17.1959</v>
@@ -2023,7 +2026,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -2039,7 +2042,7 @@
         <v>41.5382</v>
       </c>
       <c r="F38" t="n">
-        <v>7.2518</v>
+        <v>8.406799999999999</v>
       </c>
       <c r="G38" t="n">
         <v>17.196</v>
@@ -2052,7 +2055,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -2068,7 +2071,7 @@
         <v>42.8823</v>
       </c>
       <c r="F39" t="n">
-        <v>7.2518</v>
+        <v>8.3185</v>
       </c>
       <c r="G39" t="n">
         <v>17.1985</v>
@@ -2081,7 +2084,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -2097,7 +2100,7 @@
         <v>44.3004</v>
       </c>
       <c r="F40" t="n">
-        <v>7.2518</v>
+        <v>8.2302</v>
       </c>
       <c r="G40" t="n">
         <v>17.199</v>
@@ -2110,7 +2113,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -2126,7 +2129,7 @@
         <v>45.929</v>
       </c>
       <c r="F41" t="n">
-        <v>7.2518</v>
+        <v>8.1419</v>
       </c>
       <c r="G41" t="n">
         <v>17.3457</v>
@@ -2139,7 +2142,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -2155,7 +2158,7 @@
         <v>47.1933</v>
       </c>
       <c r="F42" t="n">
-        <v>7.2518</v>
+        <v>8.053699999999999</v>
       </c>
       <c r="G42" t="n">
         <v>17.3462</v>
@@ -2168,7 +2171,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -2184,7 +2187,7 @@
         <v>48.4345</v>
       </c>
       <c r="F43" t="n">
-        <v>7.2818</v>
+        <v>7.9954</v>
       </c>
       <c r="G43" t="n">
         <v>17.3868</v>
@@ -2197,7 +2200,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -2213,7 +2216,7 @@
         <v>49.962</v>
       </c>
       <c r="F44" t="n">
-        <v>7.2824</v>
+        <v>7.9077</v>
       </c>
       <c r="G44" t="n">
         <v>17.3881</v>
@@ -2226,7 +2229,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -2242,7 +2245,7 @@
         <v>51.1059</v>
       </c>
       <c r="F45" t="n">
-        <v>7.2824</v>
+        <v>7.8194</v>
       </c>
       <c r="G45" t="n">
         <v>17.3902</v>
@@ -2255,7 +2258,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -2271,7 +2274,7 @@
         <v>52.4351</v>
       </c>
       <c r="F46" t="n">
-        <v>7.2824</v>
+        <v>7.731100000000001</v>
       </c>
       <c r="G46" t="n">
         <v>17.46</v>
@@ -2284,7 +2287,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -2300,7 +2303,7 @@
         <v>53.8829</v>
       </c>
       <c r="F47" t="n">
-        <v>7.5723</v>
+        <v>7.9327</v>
       </c>
       <c r="G47" t="n">
         <v>17.4963</v>
@@ -2313,7 +2316,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -2329,7 +2332,7 @@
         <v>55.4687</v>
       </c>
       <c r="F48" t="n">
-        <v>7.5723</v>
+        <v>7.844399999999999</v>
       </c>
       <c r="G48" t="n">
         <v>17.4963</v>
@@ -2342,7 +2345,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -2358,7 +2361,7 @@
         <v>56.851</v>
       </c>
       <c r="F49" t="n">
-        <v>7.5723</v>
+        <v>7.8522</v>
       </c>
       <c r="G49" t="n">
         <v>17.4963</v>
@@ -2371,7 +2374,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -2387,7 +2390,7 @@
         <v>58.424</v>
       </c>
       <c r="F50" t="n">
-        <v>7.573600000000001</v>
+        <v>7.8597</v>
       </c>
       <c r="G50" t="n">
         <v>17.8819</v>
@@ -2400,7 +2403,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -2416,7 +2419,7 @@
         <v>59.3316</v>
       </c>
       <c r="F51" t="n">
-        <v>7.573600000000001</v>
+        <v>7.8658</v>
       </c>
       <c r="G51" t="n">
         <v>17.9351</v>
@@ -2429,7 +2432,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -2445,7 +2448,7 @@
         <v>60.2548</v>
       </c>
       <c r="F52" t="n">
-        <v>7.573600000000001</v>
+        <v>7.872</v>
       </c>
       <c r="G52" t="n">
         <v>17.9663</v>
@@ -2458,7 +2461,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -2474,7 +2477,7 @@
         <v>61.1996</v>
       </c>
       <c r="F53" t="n">
-        <v>7.573600000000001</v>
+        <v>7.8782</v>
       </c>
       <c r="G53" t="n">
         <v>18.0116</v>
@@ -2487,7 +2490,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -2503,7 +2506,7 @@
         <v>62.003</v>
       </c>
       <c r="F54" t="n">
-        <v>7.573600000000001</v>
+        <v>7.884399999999999</v>
       </c>
       <c r="G54" t="n">
         <v>18.0596</v>
@@ -2516,7 +2519,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -2532,7 +2535,7 @@
         <v>62.788</v>
       </c>
       <c r="F55" t="n">
-        <v>7.573600000000001</v>
+        <v>7.8905</v>
       </c>
       <c r="G55" t="n">
         <v>18.0618</v>
@@ -2545,7 +2548,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -2561,7 +2564,7 @@
         <v>63.6554</v>
       </c>
       <c r="F56" t="n">
-        <v>7.573600000000001</v>
+        <v>7.8967</v>
       </c>
       <c r="G56" t="n">
         <v>18.0646</v>
@@ -2574,7 +2577,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -2590,7 +2593,7 @@
         <v>64.3811</v>
       </c>
       <c r="F57" t="n">
-        <v>7.573600000000001</v>
+        <v>7.9029</v>
       </c>
       <c r="G57" t="n">
         <v>18.1046</v>
@@ -2603,7 +2606,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n">
+      <c r="A58" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -2619,7 +2622,7 @@
         <v>65.989</v>
       </c>
       <c r="F58" t="n">
-        <v>7.573600000000001</v>
+        <v>7.9091</v>
       </c>
       <c r="G58" t="n">
         <v>18.1067</v>
@@ -2632,7 +2635,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -2648,7 +2651,7 @@
         <v>67.35510000000001</v>
       </c>
       <c r="F59" t="n">
-        <v>7.573600000000001</v>
+        <v>7.9152</v>
       </c>
       <c r="G59" t="n">
         <v>18.1365</v>
@@ -2661,7 +2664,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -2677,7 +2680,7 @@
         <v>68.26310000000001</v>
       </c>
       <c r="F60" t="n">
-        <v>7.573600000000001</v>
+        <v>7.921399999999999</v>
       </c>
       <c r="G60" t="n">
         <v>18.1365</v>
@@ -2690,7 +2693,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -2706,7 +2709,7 @@
         <v>69.3095</v>
       </c>
       <c r="F61" t="n">
-        <v>7.573600000000001</v>
+        <v>7.9276</v>
       </c>
       <c r="G61" t="n">
         <v>18.145</v>
@@ -2719,7 +2722,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
+      <c r="A62" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2735,7 +2738,7 @@
         <v>70.5573</v>
       </c>
       <c r="F62" t="n">
-        <v>7.573600000000001</v>
+        <v>7.8883</v>
       </c>
       <c r="G62" t="n">
         <v>18.1451</v>
@@ -2748,7 +2751,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -2764,7 +2767,7 @@
         <v>71.9028</v>
       </c>
       <c r="F63" t="n">
-        <v>7.573600000000001</v>
+        <v>7.8489</v>
       </c>
       <c r="G63" t="n">
         <v>18.1451</v>
@@ -2777,7 +2780,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n">
+      <c r="A64" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -2793,7 +2796,7 @@
         <v>73.7351</v>
       </c>
       <c r="F64" t="n">
-        <v>7.5747</v>
+        <v>7.8107</v>
       </c>
       <c r="G64" t="n">
         <v>18.1715</v>
@@ -2806,7 +2809,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -2822,7 +2825,7 @@
         <v>74.60850000000001</v>
       </c>
       <c r="F65" t="n">
-        <v>7.5747</v>
+        <v>7.7714</v>
       </c>
       <c r="G65" t="n">
         <v>18.2115</v>
@@ -2835,7 +2838,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="n">
+      <c r="A66" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -2851,7 +2854,7 @@
         <v>75.3052</v>
       </c>
       <c r="F66" t="n">
-        <v>7.5747</v>
+        <v>7.732</v>
       </c>
       <c r="G66" t="n">
         <v>18.2115</v>
@@ -2864,7 +2867,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="n">
+      <c r="A67" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -2880,7 +2883,7 @@
         <v>75.9914</v>
       </c>
       <c r="F67" t="n">
-        <v>7.5747</v>
+        <v>7.692699999999999</v>
       </c>
       <c r="G67" t="n">
         <v>18.2115</v>
@@ -2893,7 +2896,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="n">
+      <c r="A68" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -2909,7 +2912,7 @@
         <v>76.3515</v>
       </c>
       <c r="F68" t="n">
-        <v>7.5747</v>
+        <v>7.6534</v>
       </c>
       <c r="G68" t="n">
         <v>18.2157</v>
@@ -2922,7 +2925,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="n">
+      <c r="A69" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B69" t="n">
@@ -2938,7 +2941,7 @@
         <v>77.2662</v>
       </c>
       <c r="F69" t="n">
-        <v>7.5796</v>
+        <v>7.619</v>
       </c>
       <c r="G69" t="n">
         <v>18.2257</v>
@@ -2951,7 +2954,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="n">
+      <c r="A70" s="3" t="n">
         <v>46266</v>
       </c>
       <c r="B70" t="n">
@@ -3074,7 +3077,7 @@
         <v>1990</v>
       </c>
       <c r="H2" t="n">
-        <v>6893.4</v>
+        <v>9134.4</v>
       </c>
       <c r="I2" t="n">
         <v>15408.5</v>
@@ -3083,7 +3086,7 @@
         <v>166</v>
       </c>
       <c r="K2" t="n">
-        <v>178457.2</v>
+        <v>180698.2</v>
       </c>
     </row>
     <row r="3">
@@ -3109,7 +3112,7 @@
         <v>1990</v>
       </c>
       <c r="H3" t="n">
-        <v>6902.8</v>
+        <v>9143.799999999999</v>
       </c>
       <c r="I3" t="n">
         <v>15426</v>
@@ -3118,7 +3121,7 @@
         <v>166</v>
       </c>
       <c r="K3" t="n">
-        <v>178937.5</v>
+        <v>181178.5</v>
       </c>
     </row>
     <row r="4">
@@ -3144,7 +3147,7 @@
         <v>1990</v>
       </c>
       <c r="H4" t="n">
-        <v>6931.5</v>
+        <v>9172.5</v>
       </c>
       <c r="I4" t="n">
         <v>15435.1</v>
@@ -3153,7 +3156,7 @@
         <v>166</v>
       </c>
       <c r="K4" t="n">
-        <v>179806.3</v>
+        <v>182047.3</v>
       </c>
     </row>
     <row r="5">
@@ -3179,7 +3182,7 @@
         <v>1990</v>
       </c>
       <c r="H5" t="n">
-        <v>6973.9</v>
+        <v>9214.9</v>
       </c>
       <c r="I5" t="n">
         <v>15490.4</v>
@@ -3188,7 +3191,7 @@
         <v>166</v>
       </c>
       <c r="K5" t="n">
-        <v>180484.6</v>
+        <v>182725.6</v>
       </c>
     </row>
     <row r="6">
@@ -3214,7 +3217,7 @@
         <v>1990</v>
       </c>
       <c r="H6" t="n">
-        <v>6973.9</v>
+        <v>9214.9</v>
       </c>
       <c r="I6" t="n">
         <v>15515.6</v>
@@ -3223,7 +3226,7 @@
         <v>166</v>
       </c>
       <c r="K6" t="n">
-        <v>181204.5</v>
+        <v>183445.5</v>
       </c>
     </row>
     <row r="7">
@@ -3249,7 +3252,7 @@
         <v>1990</v>
       </c>
       <c r="H7" t="n">
-        <v>6973.9</v>
+        <v>9214.9</v>
       </c>
       <c r="I7" t="n">
         <v>15559.5</v>
@@ -3258,7 +3261,7 @@
         <v>168.9</v>
       </c>
       <c r="K7" t="n">
-        <v>182101</v>
+        <v>184342</v>
       </c>
     </row>
     <row r="8">
@@ -3284,7 +3287,7 @@
         <v>1990</v>
       </c>
       <c r="H8" t="n">
-        <v>6973.9</v>
+        <v>9214.9</v>
       </c>
       <c r="I8" t="n">
         <v>15560.2</v>
@@ -3293,7 +3296,7 @@
         <v>168.9</v>
       </c>
       <c r="K8" t="n">
-        <v>183069.9</v>
+        <v>185310.9</v>
       </c>
     </row>
     <row r="9">
@@ -3319,7 +3322,7 @@
         <v>1990</v>
       </c>
       <c r="H9" t="n">
-        <v>6975.7</v>
+        <v>9216.700000000001</v>
       </c>
       <c r="I9" t="n">
         <v>15610.8</v>
@@ -3328,7 +3331,7 @@
         <v>168.9</v>
       </c>
       <c r="K9" t="n">
-        <v>184380.3</v>
+        <v>186621.3</v>
       </c>
     </row>
     <row r="10">
@@ -3354,7 +3357,7 @@
         <v>1990</v>
       </c>
       <c r="H10" t="n">
-        <v>6978.5</v>
+        <v>9219.5</v>
       </c>
       <c r="I10" t="n">
         <v>15613.8</v>
@@ -3363,7 +3366,7 @@
         <v>168.9</v>
       </c>
       <c r="K10" t="n">
-        <v>186580.5</v>
+        <v>188821.5</v>
       </c>
     </row>
     <row r="11">
@@ -3389,7 +3392,7 @@
         <v>1990</v>
       </c>
       <c r="H11" t="n">
-        <v>6980.8</v>
+        <v>9221.799999999999</v>
       </c>
       <c r="I11" t="n">
         <v>15646.5</v>
@@ -3398,7 +3401,7 @@
         <v>170.5</v>
       </c>
       <c r="K11" t="n">
-        <v>188046.2</v>
+        <v>190287.2</v>
       </c>
     </row>
     <row r="12">
@@ -3424,7 +3427,7 @@
         <v>1990</v>
       </c>
       <c r="H12" t="n">
-        <v>6980.8</v>
+        <v>9221.799999999999</v>
       </c>
       <c r="I12" t="n">
         <v>15660.5</v>
@@ -3433,7 +3436,7 @@
         <v>170.5</v>
       </c>
       <c r="K12" t="n">
-        <v>189163.6</v>
+        <v>191404.6</v>
       </c>
     </row>
     <row r="13">
@@ -3459,7 +3462,7 @@
         <v>1990</v>
       </c>
       <c r="H13" t="n">
-        <v>6980.8</v>
+        <v>9221.799999999999</v>
       </c>
       <c r="I13" t="n">
         <v>16079.3</v>
@@ -3468,7 +3471,7 @@
         <v>170.5</v>
       </c>
       <c r="K13" t="n">
-        <v>191105.4</v>
+        <v>193346.4</v>
       </c>
     </row>
     <row r="14">
@@ -3494,7 +3497,7 @@
         <v>1990</v>
       </c>
       <c r="H14" t="n">
-        <v>6984</v>
+        <v>9165.5</v>
       </c>
       <c r="I14" t="n">
         <v>16217.3</v>
@@ -3503,7 +3506,7 @@
         <v>170.5</v>
       </c>
       <c r="K14" t="n">
-        <v>191998.3</v>
+        <v>194179.8</v>
       </c>
     </row>
     <row r="15">
@@ -3529,7 +3532,7 @@
         <v>1990</v>
       </c>
       <c r="H15" t="n">
-        <v>6984</v>
+        <v>9106</v>
       </c>
       <c r="I15" t="n">
         <v>16218.8</v>
@@ -3538,7 +3541,7 @@
         <v>172.2</v>
       </c>
       <c r="K15" t="n">
-        <v>193189.2</v>
+        <v>195311.2</v>
       </c>
     </row>
     <row r="16">
@@ -3564,7 +3567,7 @@
         <v>1990</v>
       </c>
       <c r="H16" t="n">
-        <v>6990.2</v>
+        <v>9052.700000000001</v>
       </c>
       <c r="I16" t="n">
         <v>16295.4</v>
@@ -3573,7 +3576,7 @@
         <v>172.2</v>
       </c>
       <c r="K16" t="n">
-        <v>194186</v>
+        <v>196248.6</v>
       </c>
     </row>
     <row r="17">
@@ -3599,7 +3602,7 @@
         <v>1990</v>
       </c>
       <c r="H17" t="n">
-        <v>6990.5</v>
+        <v>8993.6</v>
       </c>
       <c r="I17" t="n">
         <v>16332.9</v>
@@ -3608,7 +3611,7 @@
         <v>173.1</v>
       </c>
       <c r="K17" t="n">
-        <v>195069</v>
+        <v>197072.1</v>
       </c>
     </row>
     <row r="18">
@@ -3634,7 +3637,7 @@
         <v>1990</v>
       </c>
       <c r="H18" t="n">
-        <v>6990.5</v>
+        <v>8934.1</v>
       </c>
       <c r="I18" t="n">
         <v>16685.7</v>
@@ -3643,7 +3646,7 @@
         <v>173.1</v>
       </c>
       <c r="K18" t="n">
-        <v>196477.3</v>
+        <v>198420.9</v>
       </c>
     </row>
     <row r="19">
@@ -3669,7 +3672,7 @@
         <v>1990</v>
       </c>
       <c r="H19" t="n">
-        <v>6994.8</v>
+        <v>8879</v>
       </c>
       <c r="I19" t="n">
         <v>16709.3</v>
@@ -3678,7 +3681,7 @@
         <v>173.1</v>
       </c>
       <c r="K19" t="n">
-        <v>197472.9</v>
+        <v>199357</v>
       </c>
     </row>
     <row r="20">
@@ -3704,7 +3707,7 @@
         <v>1990</v>
       </c>
       <c r="H20" t="n">
-        <v>6994.8</v>
+        <v>8819.5</v>
       </c>
       <c r="I20" t="n">
         <v>16720.8</v>
@@ -3713,7 +3716,7 @@
         <v>173.1</v>
       </c>
       <c r="K20" t="n">
-        <v>199193.2</v>
+        <v>201017.9</v>
       </c>
     </row>
     <row r="21">
@@ -3739,7 +3742,7 @@
         <v>1990</v>
       </c>
       <c r="H21" t="n">
-        <v>6994.8</v>
+        <v>8760</v>
       </c>
       <c r="I21" t="n">
         <v>16722</v>
@@ -3748,7 +3751,7 @@
         <v>173.1</v>
       </c>
       <c r="K21" t="n">
-        <v>200543.9</v>
+        <v>202309</v>
       </c>
     </row>
     <row r="22">
@@ -3774,7 +3777,7 @@
         <v>1990</v>
       </c>
       <c r="H22" t="n">
-        <v>6996.2</v>
+        <v>8702</v>
       </c>
       <c r="I22" t="n">
         <v>16913.3</v>
@@ -3783,7 +3786,7 @@
         <v>173.1</v>
       </c>
       <c r="K22" t="n">
-        <v>202576.9</v>
+        <v>204282.6</v>
       </c>
     </row>
     <row r="23">
@@ -3809,7 +3812,7 @@
         <v>1990</v>
       </c>
       <c r="H23" t="n">
-        <v>7008.2</v>
+        <v>8654.4</v>
       </c>
       <c r="I23" t="n">
         <v>16913.8</v>
@@ -3818,7 +3821,7 @@
         <v>173.1</v>
       </c>
       <c r="K23" t="n">
-        <v>204574.1</v>
+        <v>206220.3</v>
       </c>
     </row>
     <row r="24">
@@ -3844,7 +3847,7 @@
         <v>1990</v>
       </c>
       <c r="H24" t="n">
-        <v>7014.4</v>
+        <v>8601.1</v>
       </c>
       <c r="I24" t="n">
         <v>16931.4</v>
@@ -3853,7 +3856,7 @@
         <v>173.1</v>
       </c>
       <c r="K24" t="n">
-        <v>206443.9</v>
+        <v>208030.6</v>
       </c>
     </row>
     <row r="25">
@@ -3879,7 +3882,7 @@
         <v>1990</v>
       </c>
       <c r="H25" t="n">
-        <v>7061.5</v>
+        <v>8588.799999999999</v>
       </c>
       <c r="I25" t="n">
         <v>16957</v>
@@ -3888,7 +3891,7 @@
         <v>173.1</v>
       </c>
       <c r="K25" t="n">
-        <v>208408.8</v>
+        <v>209936</v>
       </c>
     </row>
     <row r="26">
@@ -3914,7 +3917,7 @@
         <v>1990</v>
       </c>
       <c r="H26" t="n">
-        <v>7063.8</v>
+        <v>8573.299999999999</v>
       </c>
       <c r="I26" t="n">
         <v>16957</v>
@@ -3923,7 +3926,7 @@
         <v>173.1</v>
       </c>
       <c r="K26" t="n">
-        <v>210769</v>
+        <v>212278.5</v>
       </c>
     </row>
     <row r="27">
@@ -3949,7 +3952,7 @@
         <v>1990</v>
       </c>
       <c r="H27" t="n">
-        <v>7137.3</v>
+        <v>8629</v>
       </c>
       <c r="I27" t="n">
         <v>16998.3</v>
@@ -3958,7 +3961,7 @@
         <v>173.1</v>
       </c>
       <c r="K27" t="n">
-        <v>212213.4</v>
+        <v>213705.1</v>
       </c>
     </row>
     <row r="28">
@@ -3984,7 +3987,7 @@
         <v>1990</v>
       </c>
       <c r="H28" t="n">
-        <v>7145.6</v>
+        <v>8619.5</v>
       </c>
       <c r="I28" t="n">
         <v>17002.4</v>
@@ -3993,7 +3996,7 @@
         <v>173.1</v>
       </c>
       <c r="K28" t="n">
-        <v>213791.1</v>
+        <v>215265</v>
       </c>
     </row>
     <row r="29">
@@ -4019,7 +4022,7 @@
         <v>1990</v>
       </c>
       <c r="H29" t="n">
-        <v>7152.5</v>
+        <v>8608.5</v>
       </c>
       <c r="I29" t="n">
         <v>17082.3</v>
@@ -4028,7 +4031,7 @@
         <v>173.1</v>
       </c>
       <c r="K29" t="n">
-        <v>215243.1</v>
+        <v>216699.2</v>
       </c>
     </row>
     <row r="30">
@@ -4054,7 +4057,7 @@
         <v>1990</v>
       </c>
       <c r="H30" t="n">
-        <v>7177.8</v>
+        <v>8616</v>
       </c>
       <c r="I30" t="n">
         <v>17086.4</v>
@@ -4063,7 +4066,7 @@
         <v>173.1</v>
       </c>
       <c r="K30" t="n">
-        <v>217422.8</v>
+        <v>218861</v>
       </c>
     </row>
     <row r="31">
@@ -4089,7 +4092,7 @@
         <v>1990</v>
       </c>
       <c r="H31" t="n">
-        <v>7191.5</v>
+        <v>8612</v>
       </c>
       <c r="I31" t="n">
         <v>17104.9</v>
@@ -4098,7 +4101,7 @@
         <v>173.1</v>
       </c>
       <c r="K31" t="n">
-        <v>218475.2</v>
+        <v>219895.7</v>
       </c>
     </row>
     <row r="32">
@@ -4124,7 +4127,7 @@
         <v>1990</v>
       </c>
       <c r="H32" t="n">
-        <v>7193.3</v>
+        <v>8595.9</v>
       </c>
       <c r="I32" t="n">
         <v>17110.7</v>
@@ -4133,7 +4136,7 @@
         <v>173.1</v>
       </c>
       <c r="K32" t="n">
-        <v>219528.5</v>
+        <v>220931.1</v>
       </c>
     </row>
     <row r="33">
@@ -4159,7 +4162,7 @@
         <v>1990</v>
       </c>
       <c r="H33" t="n">
-        <v>7201.7</v>
+        <v>8586.6</v>
       </c>
       <c r="I33" t="n">
         <v>17126.7</v>
@@ -4168,7 +4171,7 @@
         <v>173.1</v>
       </c>
       <c r="K33" t="n">
-        <v>221208.1</v>
+        <v>222593</v>
       </c>
     </row>
     <row r="34">
@@ -4194,7 +4197,7 @@
         <v>1990</v>
       </c>
       <c r="H34" t="n">
-        <v>7241.8</v>
+        <v>8608.9</v>
       </c>
       <c r="I34" t="n">
         <v>17167.8</v>
@@ -4203,7 +4206,7 @@
         <v>173.1</v>
       </c>
       <c r="K34" t="n">
-        <v>221992.6</v>
+        <v>223359.7</v>
       </c>
     </row>
     <row r="35">
@@ -4229,7 +4232,7 @@
         <v>1990</v>
       </c>
       <c r="H35" t="n">
-        <v>7251.8</v>
+        <v>8601.1</v>
       </c>
       <c r="I35" t="n">
         <v>17191.8</v>
@@ -4238,7 +4241,7 @@
         <v>174.2</v>
       </c>
       <c r="K35" t="n">
-        <v>223421.5</v>
+        <v>224770.8</v>
       </c>
     </row>
     <row r="36">
@@ -4264,7 +4267,7 @@
         <v>1990</v>
       </c>
       <c r="H36" t="n">
-        <v>7251.8</v>
+        <v>8583.299999999999</v>
       </c>
       <c r="I36" t="n">
         <v>17195.3</v>
@@ -4273,7 +4276,7 @@
         <v>174.2</v>
       </c>
       <c r="K36" t="n">
-        <v>224704.9</v>
+        <v>226036.4</v>
       </c>
     </row>
     <row r="37">
@@ -4299,7 +4302,7 @@
         <v>1990</v>
       </c>
       <c r="H37" t="n">
-        <v>7251.8</v>
+        <v>8495</v>
       </c>
       <c r="I37" t="n">
         <v>17195.9</v>
@@ -4308,7 +4311,7 @@
         <v>174.2</v>
       </c>
       <c r="K37" t="n">
-        <v>227429.2</v>
+        <v>228672.4</v>
       </c>
     </row>
     <row r="38">
@@ -4334,7 +4337,7 @@
         <v>1990</v>
       </c>
       <c r="H38" t="n">
-        <v>7251.8</v>
+        <v>8406.799999999999</v>
       </c>
       <c r="I38" t="n">
         <v>17196</v>
@@ -4343,7 +4346,7 @@
         <v>174.2</v>
       </c>
       <c r="K38" t="n">
-        <v>228917.3</v>
+        <v>230072.2</v>
       </c>
     </row>
     <row r="39">
@@ -4369,7 +4372,7 @@
         <v>1990</v>
       </c>
       <c r="H39" t="n">
-        <v>7251.8</v>
+        <v>8318.5</v>
       </c>
       <c r="I39" t="n">
         <v>17198.5</v>
@@ -4378,7 +4381,7 @@
         <v>174.2</v>
       </c>
       <c r="K39" t="n">
-        <v>230639.9</v>
+        <v>231706.5</v>
       </c>
     </row>
     <row r="40">
@@ -4404,7 +4407,7 @@
         <v>1990</v>
       </c>
       <c r="H40" t="n">
-        <v>7251.8</v>
+        <v>8230.200000000001</v>
       </c>
       <c r="I40" t="n">
         <v>17199</v>
@@ -4413,7 +4416,7 @@
         <v>174.2</v>
       </c>
       <c r="K40" t="n">
-        <v>232399.7</v>
+        <v>233378</v>
       </c>
     </row>
     <row r="41">
@@ -4439,7 +4442,7 @@
         <v>1990</v>
       </c>
       <c r="H41" t="n">
-        <v>7251.8</v>
+        <v>8141.9</v>
       </c>
       <c r="I41" t="n">
         <v>17345.7</v>
@@ -4448,7 +4451,7 @@
         <v>174.2</v>
       </c>
       <c r="K41" t="n">
-        <v>234643.7</v>
+        <v>235533.8</v>
       </c>
     </row>
     <row r="42">
@@ -4474,7 +4477,7 @@
         <v>1990</v>
       </c>
       <c r="H42" t="n">
-        <v>7251.8</v>
+        <v>8053.7</v>
       </c>
       <c r="I42" t="n">
         <v>17346.2</v>
@@ -4483,7 +4486,7 @@
         <v>174.2</v>
       </c>
       <c r="K42" t="n">
-        <v>236129.9</v>
+        <v>236931.7</v>
       </c>
     </row>
     <row r="43">
@@ -4509,7 +4512,7 @@
         <v>1990</v>
       </c>
       <c r="H43" t="n">
-        <v>7281.8</v>
+        <v>7995.4</v>
       </c>
       <c r="I43" t="n">
         <v>17386.8</v>
@@ -4518,7 +4521,7 @@
         <v>174.2</v>
       </c>
       <c r="K43" t="n">
-        <v>237673</v>
+        <v>238386.5</v>
       </c>
     </row>
     <row r="44">
@@ -4544,7 +4547,7 @@
         <v>1990</v>
       </c>
       <c r="H44" t="n">
-        <v>7282.4</v>
+        <v>7907.7</v>
       </c>
       <c r="I44" t="n">
         <v>17388.1</v>
@@ -4553,7 +4556,7 @@
         <v>174.2</v>
       </c>
       <c r="K44" t="n">
-        <v>239595.4</v>
+        <v>240220.7</v>
       </c>
     </row>
     <row r="45">
@@ -4579,7 +4582,7 @@
         <v>1990</v>
       </c>
       <c r="H45" t="n">
-        <v>7282.4</v>
+        <v>7819.4</v>
       </c>
       <c r="I45" t="n">
         <v>17390.2</v>
@@ -4588,7 +4591,7 @@
         <v>174.2</v>
       </c>
       <c r="K45" t="n">
-        <v>241085.6</v>
+        <v>241622.6</v>
       </c>
     </row>
     <row r="46">
@@ -4614,7 +4617,7 @@
         <v>1990</v>
       </c>
       <c r="H46" t="n">
-        <v>7282.4</v>
+        <v>7731.1</v>
       </c>
       <c r="I46" t="n">
         <v>17460</v>
@@ -4623,7 +4626,7 @@
         <v>174.2</v>
       </c>
       <c r="K46" t="n">
-        <v>242640.2</v>
+        <v>243088.9</v>
       </c>
     </row>
     <row r="47">
@@ -4649,7 +4652,7 @@
         <v>1990</v>
       </c>
       <c r="H47" t="n">
-        <v>7572.3</v>
+        <v>7932.7</v>
       </c>
       <c r="I47" t="n">
         <v>17496.3</v>
@@ -4658,7 +4661,7 @@
         <v>174.2</v>
       </c>
       <c r="K47" t="n">
-        <v>244910.6</v>
+        <v>245271.1</v>
       </c>
     </row>
     <row r="48">
@@ -4684,7 +4687,7 @@
         <v>1990</v>
       </c>
       <c r="H48" t="n">
-        <v>7572.3</v>
+        <v>7844.4</v>
       </c>
       <c r="I48" t="n">
         <v>17496.3</v>
@@ -4693,7 +4696,7 @@
         <v>174.3</v>
       </c>
       <c r="K48" t="n">
-        <v>246673.9</v>
+        <v>246946</v>
       </c>
     </row>
     <row r="49">
@@ -4719,7 +4722,7 @@
         <v>1990</v>
       </c>
       <c r="H49" t="n">
-        <v>7572.3</v>
+        <v>7852.2</v>
       </c>
       <c r="I49" t="n">
         <v>17496.3</v>
@@ -4728,7 +4731,7 @@
         <v>174.3</v>
       </c>
       <c r="K49" t="n">
-        <v>248308.2</v>
+        <v>248588.1</v>
       </c>
     </row>
     <row r="50">
@@ -4754,7 +4757,7 @@
         <v>1990</v>
       </c>
       <c r="H50" t="n">
-        <v>7573.6</v>
+        <v>7859.7</v>
       </c>
       <c r="I50" t="n">
         <v>17881.9</v>
@@ -4763,7 +4766,7 @@
         <v>174.3</v>
       </c>
       <c r="K50" t="n">
-        <v>250595.7</v>
+        <v>250881.8</v>
       </c>
     </row>
     <row r="51">
@@ -4789,7 +4792,7 @@
         <v>1990</v>
       </c>
       <c r="H51" t="n">
-        <v>7573.6</v>
+        <v>7865.8</v>
       </c>
       <c r="I51" t="n">
         <v>17935.1</v>
@@ -4798,7 +4801,7 @@
         <v>174.3</v>
       </c>
       <c r="K51" t="n">
-        <v>251793.7</v>
+        <v>252085.9</v>
       </c>
     </row>
     <row r="52">
@@ -4824,7 +4827,7 @@
         <v>1990</v>
       </c>
       <c r="H52" t="n">
-        <v>7573.6</v>
+        <v>7872</v>
       </c>
       <c r="I52" t="n">
         <v>17966.3</v>
@@ -4833,7 +4836,7 @@
         <v>174.4</v>
       </c>
       <c r="K52" t="n">
-        <v>252977.9</v>
+        <v>253276.3</v>
       </c>
     </row>
     <row r="53">
@@ -4859,7 +4862,7 @@
         <v>1990</v>
       </c>
       <c r="H53" t="n">
-        <v>7573.6</v>
+        <v>7878.2</v>
       </c>
       <c r="I53" t="n">
         <v>18011.6</v>
@@ -4868,7 +4871,7 @@
         <v>174.4</v>
       </c>
       <c r="K53" t="n">
-        <v>254006.3</v>
+        <v>254310.9</v>
       </c>
     </row>
     <row r="54">
@@ -4894,7 +4897,7 @@
         <v>1990</v>
       </c>
       <c r="H54" t="n">
-        <v>7573.6</v>
+        <v>7884.4</v>
       </c>
       <c r="I54" t="n">
         <v>18059.6</v>
@@ -4903,7 +4906,7 @@
         <v>174.4</v>
       </c>
       <c r="K54" t="n">
-        <v>256534.9</v>
+        <v>256845.7</v>
       </c>
     </row>
     <row r="55">
@@ -4929,7 +4932,7 @@
         <v>1990</v>
       </c>
       <c r="H55" t="n">
-        <v>7573.6</v>
+        <v>7890.5</v>
       </c>
       <c r="I55" t="n">
         <v>18061.8</v>
@@ -4938,7 +4941,7 @@
         <v>174.4</v>
       </c>
       <c r="K55" t="n">
-        <v>257537.6</v>
+        <v>257854.6</v>
       </c>
     </row>
     <row r="56">
@@ -4964,7 +4967,7 @@
         <v>1990</v>
       </c>
       <c r="H56" t="n">
-        <v>7573.6</v>
+        <v>7896.7</v>
       </c>
       <c r="I56" t="n">
         <v>18064.6</v>
@@ -4973,7 +4976,7 @@
         <v>174.4</v>
       </c>
       <c r="K56" t="n">
-        <v>258448.2</v>
+        <v>258771.4</v>
       </c>
     </row>
     <row r="57">
@@ -4999,7 +5002,7 @@
         <v>1990</v>
       </c>
       <c r="H57" t="n">
-        <v>7573.6</v>
+        <v>7902.9</v>
       </c>
       <c r="I57" t="n">
         <v>18104.6</v>
@@ -5008,7 +5011,7 @@
         <v>174.5</v>
       </c>
       <c r="K57" t="n">
-        <v>259484.1</v>
+        <v>259813.4</v>
       </c>
     </row>
     <row r="58">
@@ -5034,7 +5037,7 @@
         <v>1990</v>
       </c>
       <c r="H58" t="n">
-        <v>7573.6</v>
+        <v>7909.1</v>
       </c>
       <c r="I58" t="n">
         <v>18106.7</v>
@@ -5043,7 +5046,7 @@
         <v>174.6</v>
       </c>
       <c r="K58" t="n">
-        <v>261483.5</v>
+        <v>261819</v>
       </c>
     </row>
     <row r="59">
@@ -5069,7 +5072,7 @@
         <v>1990</v>
       </c>
       <c r="H59" t="n">
-        <v>7573.6</v>
+        <v>7915.2</v>
       </c>
       <c r="I59" t="n">
         <v>18136.5</v>
@@ -5078,7 +5081,7 @@
         <v>174.9</v>
       </c>
       <c r="K59" t="n">
-        <v>262912.6</v>
+        <v>263254.2</v>
       </c>
     </row>
     <row r="60">
@@ -5104,7 +5107,7 @@
         <v>1990</v>
       </c>
       <c r="H60" t="n">
-        <v>7573.6</v>
+        <v>7921.4</v>
       </c>
       <c r="I60" t="n">
         <v>18136.5</v>
@@ -5113,7 +5116,7 @@
         <v>175.2</v>
       </c>
       <c r="K60" t="n">
-        <v>263820.9</v>
+        <v>264168.8</v>
       </c>
     </row>
     <row r="61">
@@ -5139,7 +5142,7 @@
         <v>1990</v>
       </c>
       <c r="H61" t="n">
-        <v>7573.6</v>
+        <v>7927.6</v>
       </c>
       <c r="I61" t="n">
         <v>18145</v>
@@ -5148,7 +5151,7 @@
         <v>175.4</v>
       </c>
       <c r="K61" t="n">
-        <v>265226.9</v>
+        <v>265581</v>
       </c>
     </row>
     <row r="62">
@@ -5174,7 +5177,7 @@
         <v>1990</v>
       </c>
       <c r="H62" t="n">
-        <v>7573.6</v>
+        <v>7888.3</v>
       </c>
       <c r="I62" t="n">
         <v>18145.1</v>
@@ -5183,7 +5186,7 @@
         <v>175.7</v>
       </c>
       <c r="K62" t="n">
-        <v>266496.4</v>
+        <v>266811.1</v>
       </c>
     </row>
     <row r="63">
@@ -5209,7 +5212,7 @@
         <v>1990</v>
       </c>
       <c r="H63" t="n">
-        <v>7573.6</v>
+        <v>7848.9</v>
       </c>
       <c r="I63" t="n">
         <v>18145.1</v>
@@ -5218,7 +5221,7 @@
         <v>175.8</v>
       </c>
       <c r="K63" t="n">
-        <v>267900.5</v>
+        <v>268175.8</v>
       </c>
     </row>
     <row r="64">
@@ -5244,7 +5247,7 @@
         <v>1990</v>
       </c>
       <c r="H64" t="n">
-        <v>7574.7</v>
+        <v>7810.7</v>
       </c>
       <c r="I64" t="n">
         <v>18171.5</v>
@@ -5253,7 +5256,7 @@
         <v>175.9</v>
       </c>
       <c r="K64" t="n">
-        <v>269765.7</v>
+        <v>270001.7</v>
       </c>
     </row>
     <row r="65">
@@ -5279,7 +5282,7 @@
         <v>1990</v>
       </c>
       <c r="H65" t="n">
-        <v>7574.7</v>
+        <v>7771.4</v>
       </c>
       <c r="I65" t="n">
         <v>18211.5</v>
@@ -5288,7 +5291,7 @@
         <v>179.4</v>
       </c>
       <c r="K65" t="n">
-        <v>270682.7</v>
+        <v>270879.3</v>
       </c>
     </row>
     <row r="66">
@@ -5314,7 +5317,7 @@
         <v>1990</v>
       </c>
       <c r="H66" t="n">
-        <v>7574.7</v>
+        <v>7732</v>
       </c>
       <c r="I66" t="n">
         <v>18211.5</v>
@@ -5323,7 +5326,7 @@
         <v>180.1</v>
       </c>
       <c r="K66" t="n">
-        <v>271384.4</v>
+        <v>271541.7</v>
       </c>
     </row>
     <row r="67">
@@ -5349,7 +5352,7 @@
         <v>1990</v>
       </c>
       <c r="H67" t="n">
-        <v>7574.7</v>
+        <v>7692.7</v>
       </c>
       <c r="I67" t="n">
         <v>18211.5</v>
@@ -5358,7 +5361,7 @@
         <v>180.5</v>
       </c>
       <c r="K67" t="n">
-        <v>272093.7</v>
+        <v>272211.7</v>
       </c>
     </row>
     <row r="68">
@@ -5384,7 +5387,7 @@
         <v>1990</v>
       </c>
       <c r="H68" t="n">
-        <v>7574.7</v>
+        <v>7653.4</v>
       </c>
       <c r="I68" t="n">
         <v>18215.7</v>
@@ -5393,7 +5396,7 @@
         <v>180.5</v>
       </c>
       <c r="K68" t="n">
-        <v>272528</v>
+        <v>272606.7</v>
       </c>
     </row>
     <row r="69">
@@ -5419,7 +5422,7 @@
         <v>1990</v>
       </c>
       <c r="H69" t="n">
-        <v>7579.6</v>
+        <v>7619</v>
       </c>
       <c r="I69" t="n">
         <v>18225.7</v>
@@ -5428,7 +5431,7 @@
         <v>180.5</v>
       </c>
       <c r="K69" t="n">
-        <v>274511.6</v>
+        <v>274550.9</v>
       </c>
     </row>
     <row r="70">
@@ -15205,13 +15208,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>7.252</v>
+        <v>8.494999999999999</v>
       </c>
       <c r="E8" t="n">
         <v>7.69</v>
       </c>
       <c r="F8" t="n">
-        <v>-5.7</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="9">
@@ -15271,13 +15274,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>227.429</v>
+        <v>228.672</v>
       </c>
       <c r="E11" t="n">
         <v>224.69</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="12">
@@ -15439,13 +15442,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>7.572</v>
+        <v>7.852</v>
       </c>
       <c r="E18" t="n">
         <v>8.01</v>
       </c>
       <c r="F18" t="n">
-        <v>-5.5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="19">
@@ -15505,13 +15508,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>248.308</v>
+        <v>248.588</v>
       </c>
       <c r="E21" t="n">
         <v>244.67</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="22">
@@ -15673,13 +15676,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>7.574</v>
+        <v>7.928</v>
       </c>
       <c r="E28" t="n">
         <v>8.01</v>
       </c>
       <c r="F28" t="n">
-        <v>-5.4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="29">
@@ -15739,13 +15742,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>265.227</v>
+        <v>265.581</v>
       </c>
       <c r="E31" t="n">
         <v>260.64</v>
       </c>
       <c r="F31" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/brazil_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/brazil_power_capacity.xlsx
@@ -161,6 +161,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Brazil installed generation capacity (ANEEL) (to Sep/26)</a:t>
             </a:r>
           </a:p>
@@ -294,7 +295,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E87BA4"/>
+              <a:srgbClr val="6E4B2A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -322,7 +323,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="008300"/>
+              <a:srgbClr val="8A9A2B"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -350,7 +351,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="4A3AA7"/>
+              <a:srgbClr val="E87BA4"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -378,7 +379,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E34948"/>
+              <a:srgbClr val="008300"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>

--- a/output/Data and Chart Outputs/brazil_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/brazil_power_capacity.xlsx
@@ -25,8 +25,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="mmm/yy"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -66,13 +66,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -824,6 +823,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -852,6 +852,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
@@ -866,6 +867,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
@@ -901,6 +903,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
@@ -980,26 +983,26 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
-        <v>109.2893</v>
+        <v>109.2892</v>
       </c>
       <c r="C2" t="n">
-        <v>13.982</v>
+        <v>13.9818</v>
       </c>
       <c r="D2" t="n">
         <v>17.3511</v>
       </c>
       <c r="E2" t="n">
-        <v>9.463200000000001</v>
+        <v>9.4305</v>
       </c>
       <c r="F2" t="n">
         <v>9.134399999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>15.4085</v>
+        <v>15.4084</v>
       </c>
       <c r="H2" t="n">
         <v>3.9137</v>
@@ -1009,26 +1012,26 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
-        <v>109.2992</v>
+        <v>109.2991</v>
       </c>
       <c r="C3" t="n">
-        <v>13.982</v>
+        <v>13.9818</v>
       </c>
       <c r="D3" t="n">
         <v>17.4718</v>
       </c>
       <c r="E3" t="n">
-        <v>9.786100000000001</v>
+        <v>9.743799999999998</v>
       </c>
       <c r="F3" t="n">
         <v>9.143799999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>15.426</v>
+        <v>15.4258</v>
       </c>
       <c r="H3" t="n">
         <v>3.9137</v>
@@ -1038,26 +1041,26 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
         <v>109.3056</v>
       </c>
       <c r="C4" t="n">
-        <v>13.982</v>
+        <v>13.9818</v>
       </c>
       <c r="D4" t="n">
         <v>17.8043</v>
       </c>
       <c r="E4" t="n">
-        <v>10.2781</v>
+        <v>10.2276</v>
       </c>
       <c r="F4" t="n">
         <v>9.172499999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>15.4351</v>
+        <v>15.4349</v>
       </c>
       <c r="H4" t="n">
         <v>3.9137</v>
@@ -1067,26 +1070,26 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
         <v>109.3056</v>
       </c>
       <c r="C5" t="n">
-        <v>13.982</v>
+        <v>13.9818</v>
       </c>
       <c r="D5" t="n">
         <v>18.0124</v>
       </c>
       <c r="E5" t="n">
-        <v>10.6506</v>
+        <v>10.5972</v>
       </c>
       <c r="F5" t="n">
         <v>9.2149</v>
       </c>
       <c r="G5" t="n">
-        <v>15.4904</v>
+        <v>15.4903</v>
       </c>
       <c r="H5" t="n">
         <v>3.9137</v>
@@ -1096,26 +1099,26 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
-        <v>109.315</v>
+        <v>109.3144</v>
       </c>
       <c r="C6" t="n">
-        <v>13.982</v>
+        <v>13.9818</v>
       </c>
       <c r="D6" t="n">
         <v>18.263</v>
       </c>
       <c r="E6" t="n">
-        <v>11.0853</v>
+        <v>11.0271</v>
       </c>
       <c r="F6" t="n">
         <v>9.2149</v>
       </c>
       <c r="G6" t="n">
-        <v>15.5156</v>
+        <v>15.5153</v>
       </c>
       <c r="H6" t="n">
         <v>3.9137</v>
@@ -1125,26 +1128,26 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
-        <v>109.3481</v>
+        <v>109.3475</v>
       </c>
       <c r="C7" t="n">
-        <v>13.982</v>
+        <v>13.9818</v>
       </c>
       <c r="D7" t="n">
         <v>18.6021</v>
       </c>
       <c r="E7" t="n">
-        <v>11.5629</v>
+        <v>11.4964</v>
       </c>
       <c r="F7" t="n">
         <v>9.2149</v>
       </c>
       <c r="G7" t="n">
-        <v>15.5595</v>
+        <v>15.5593</v>
       </c>
       <c r="H7" t="n">
         <v>3.9137</v>
@@ -1154,26 +1157,26 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
-        <v>109.3481</v>
+        <v>109.3475</v>
       </c>
       <c r="C8" t="n">
-        <v>14.1591</v>
+        <v>14.1589</v>
       </c>
       <c r="D8" t="n">
         <v>18.8737</v>
       </c>
       <c r="E8" t="n">
-        <v>12.0824</v>
+        <v>12.0088</v>
       </c>
       <c r="F8" t="n">
         <v>9.2149</v>
       </c>
       <c r="G8" t="n">
-        <v>15.5602</v>
+        <v>15.5599</v>
       </c>
       <c r="H8" t="n">
         <v>3.9137</v>
@@ -1183,26 +1186,26 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
-        <v>109.3628</v>
+        <v>109.3622</v>
       </c>
       <c r="C9" t="n">
-        <v>14.1591</v>
+        <v>14.1589</v>
       </c>
       <c r="D9" t="n">
         <v>19.3076</v>
       </c>
       <c r="E9" t="n">
-        <v>12.8917</v>
+        <v>12.8307</v>
       </c>
       <c r="F9" t="n">
         <v>9.216700000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>15.6108</v>
+        <v>15.6105</v>
       </c>
       <c r="H9" t="n">
         <v>3.9137</v>
@@ -1212,26 +1215,26 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
-        <v>109.3644</v>
+        <v>109.3639</v>
       </c>
       <c r="C10" t="n">
-        <v>15.4974</v>
+        <v>15.4972</v>
       </c>
       <c r="D10" t="n">
         <v>19.586</v>
       </c>
       <c r="E10" t="n">
-        <v>13.4677</v>
+        <v>13.398</v>
       </c>
       <c r="F10" t="n">
         <v>9.2195</v>
       </c>
       <c r="G10" t="n">
-        <v>15.6138</v>
+        <v>15.6136</v>
       </c>
       <c r="H10" t="n">
         <v>3.9137</v>
@@ -1241,26 +1244,26 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
-        <v>109.367</v>
+        <v>109.3665</v>
       </c>
       <c r="C11" t="n">
-        <v>15.5269</v>
+        <v>15.5267</v>
       </c>
       <c r="D11" t="n">
         <v>19.8684</v>
       </c>
       <c r="E11" t="n">
-        <v>14.5823</v>
+        <v>14.5133</v>
       </c>
       <c r="F11" t="n">
         <v>9.2218</v>
       </c>
       <c r="G11" t="n">
-        <v>15.6465</v>
+        <v>15.6462</v>
       </c>
       <c r="H11" t="n">
         <v>3.9137</v>
@@ -1270,26 +1273,26 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
-        <v>109.3766</v>
+        <v>109.3761</v>
       </c>
       <c r="C12" t="n">
-        <v>15.5269</v>
+        <v>15.5267</v>
       </c>
       <c r="D12" t="n">
         <v>20.2385</v>
       </c>
       <c r="E12" t="n">
-        <v>15.3061</v>
+        <v>15.2268</v>
       </c>
       <c r="F12" t="n">
         <v>9.2218</v>
       </c>
       <c r="G12" t="n">
-        <v>15.6605</v>
+        <v>15.6602</v>
       </c>
       <c r="H12" t="n">
         <v>3.9137</v>
@@ -1299,26 +1302,26 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
-        <v>109.4045</v>
+        <v>109.404</v>
       </c>
       <c r="C13" t="n">
-        <v>15.5269</v>
+        <v>15.5267</v>
       </c>
       <c r="D13" t="n">
         <v>20.9293</v>
       </c>
       <c r="E13" t="n">
-        <v>16.1104</v>
+        <v>16.0207</v>
       </c>
       <c r="F13" t="n">
         <v>9.2218</v>
       </c>
       <c r="G13" t="n">
-        <v>16.0793</v>
+        <v>16.0791</v>
       </c>
       <c r="H13" t="n">
         <v>3.9137</v>
@@ -1328,26 +1331,26 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
-        <v>109.4053</v>
+        <v>109.4047</v>
       </c>
       <c r="C14" t="n">
-        <v>15.5269</v>
+        <v>15.5267</v>
       </c>
       <c r="D14" t="n">
         <v>21.1966</v>
       </c>
       <c r="E14" t="n">
-        <v>16.594</v>
+        <v>16.5087</v>
       </c>
       <c r="F14" t="n">
         <v>9.1655</v>
       </c>
       <c r="G14" t="n">
-        <v>16.2173</v>
+        <v>16.2171</v>
       </c>
       <c r="H14" t="n">
         <v>3.9137</v>
@@ -1357,26 +1360,26 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
-        <v>109.4252</v>
+        <v>109.4246</v>
       </c>
       <c r="C15" t="n">
-        <v>15.6532</v>
+        <v>15.653</v>
       </c>
       <c r="D15" t="n">
         <v>21.5646</v>
       </c>
       <c r="E15" t="n">
-        <v>17.2675</v>
+        <v>17.1767</v>
       </c>
       <c r="F15" t="n">
         <v>9.106</v>
       </c>
       <c r="G15" t="n">
-        <v>16.2188</v>
+        <v>16.2185</v>
       </c>
       <c r="H15" t="n">
         <v>3.9137</v>
@@ -1386,26 +1389,26 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
-        <v>109.4733</v>
+        <v>109.4718</v>
       </c>
       <c r="C16" t="n">
-        <v>15.6532</v>
+        <v>15.653</v>
       </c>
       <c r="D16" t="n">
         <v>21.5995</v>
       </c>
       <c r="E16" t="n">
-        <v>18.0986</v>
+        <v>18.0139</v>
       </c>
       <c r="F16" t="n">
         <v>9.052700000000002</v>
       </c>
       <c r="G16" t="n">
-        <v>16.2954</v>
+        <v>16.2951</v>
       </c>
       <c r="H16" t="n">
         <v>3.9137</v>
@@ -1415,26 +1418,26 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
-        <v>109.4743</v>
+        <v>109.4728</v>
       </c>
       <c r="C17" t="n">
-        <v>15.6532</v>
+        <v>15.653</v>
       </c>
       <c r="D17" t="n">
         <v>21.6583</v>
       </c>
       <c r="E17" t="n">
-        <v>18.883</v>
+        <v>18.8035</v>
       </c>
       <c r="F17" t="n">
         <v>8.993600000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>16.3329</v>
+        <v>16.3327</v>
       </c>
       <c r="H17" t="n">
         <v>3.9137</v>
@@ -1444,26 +1447,26 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
-        <v>109.5038</v>
+        <v>109.5023</v>
       </c>
       <c r="C18" t="n">
-        <v>15.6532</v>
+        <v>15.653</v>
       </c>
       <c r="D18" t="n">
         <v>21.8023</v>
       </c>
       <c r="E18" t="n">
-        <v>19.765</v>
+        <v>19.6644</v>
       </c>
       <c r="F18" t="n">
         <v>8.934100000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>16.6857</v>
+        <v>16.6855</v>
       </c>
       <c r="H18" t="n">
         <v>3.9137</v>
@@ -1473,26 +1476,26 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
-        <v>109.505</v>
+        <v>109.5035</v>
       </c>
       <c r="C19" t="n">
-        <v>15.6769</v>
+        <v>15.6767</v>
       </c>
       <c r="D19" t="n">
         <v>21.9049</v>
       </c>
       <c r="E19" t="n">
-        <v>20.6052</v>
+        <v>20.4992</v>
       </c>
       <c r="F19" t="n">
         <v>8.879</v>
       </c>
       <c r="G19" t="n">
-        <v>16.7093</v>
+        <v>16.7091</v>
       </c>
       <c r="H19" t="n">
         <v>3.9137</v>
@@ -1502,26 +1505,26 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
-        <v>109.6489</v>
+        <v>109.6474</v>
       </c>
       <c r="C20" t="n">
-        <v>15.7895</v>
+        <v>15.7893</v>
       </c>
       <c r="D20" t="n">
         <v>22.2287</v>
       </c>
       <c r="E20" t="n">
-        <v>21.7337</v>
+        <v>21.6158</v>
       </c>
       <c r="F20" t="n">
         <v>8.8195</v>
       </c>
       <c r="G20" t="n">
-        <v>16.7208</v>
+        <v>16.7205</v>
       </c>
       <c r="H20" t="n">
         <v>3.9137</v>
@@ -1531,26 +1534,26 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
-        <v>109.6505</v>
+        <v>109.6489</v>
       </c>
       <c r="C21" t="n">
-        <v>15.8018</v>
+        <v>15.8016</v>
       </c>
       <c r="D21" t="n">
         <v>22.4249</v>
       </c>
       <c r="E21" t="n">
-        <v>22.8731</v>
+        <v>22.7397</v>
       </c>
       <c r="F21" t="n">
         <v>8.76</v>
       </c>
       <c r="G21" t="n">
-        <v>16.722</v>
+        <v>16.7217</v>
       </c>
       <c r="H21" t="n">
         <v>3.9137</v>
@@ -1560,26 +1563,26 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
-        <v>109.6827</v>
+        <v>109.6811</v>
       </c>
       <c r="C22" t="n">
-        <v>16.0337</v>
+        <v>16.0335</v>
       </c>
       <c r="D22" t="n">
         <v>22.6648</v>
       </c>
       <c r="E22" t="n">
-        <v>24.2095</v>
+        <v>24.0652</v>
       </c>
       <c r="F22" t="n">
         <v>8.702</v>
       </c>
       <c r="G22" t="n">
-        <v>16.9133</v>
+        <v>16.9131</v>
       </c>
       <c r="H22" t="n">
         <v>3.9137</v>
@@ -1589,26 +1592,26 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
-        <v>109.6929</v>
+        <v>109.6907</v>
       </c>
       <c r="C23" t="n">
-        <v>16.3706</v>
+        <v>16.3704</v>
       </c>
       <c r="D23" t="n">
         <v>23.3259</v>
       </c>
       <c r="E23" t="n">
-        <v>25.186</v>
+        <v>25.1335</v>
       </c>
       <c r="F23" t="n">
         <v>8.654399999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>16.9138</v>
+        <v>16.9136</v>
       </c>
       <c r="H23" t="n">
         <v>3.9137</v>
@@ -1618,26 +1621,26 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
-        <v>109.7486</v>
+        <v>109.7464</v>
       </c>
       <c r="C24" t="n">
-        <v>16.7359</v>
+        <v>16.7357</v>
       </c>
       <c r="D24" t="n">
         <v>23.6406</v>
       </c>
       <c r="E24" t="n">
-        <v>26.2962</v>
+        <v>26.2493</v>
       </c>
       <c r="F24" t="n">
         <v>8.601100000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>16.9314</v>
+        <v>16.9312</v>
       </c>
       <c r="H24" t="n">
         <v>3.9137</v>
@@ -1647,26 +1650,26 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
-        <v>109.7587</v>
+        <v>109.7565</v>
       </c>
       <c r="C25" t="n">
-        <v>16.7359</v>
+        <v>16.7357</v>
       </c>
       <c r="D25" t="n">
         <v>24.1145</v>
       </c>
       <c r="E25" t="n">
-        <v>27.7044</v>
+        <v>27.6579</v>
       </c>
       <c r="F25" t="n">
         <v>8.588799999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>16.957</v>
+        <v>16.9567</v>
       </c>
       <c r="H25" t="n">
         <v>3.9137</v>
@@ -1676,26 +1679,26 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
-        <v>109.7836</v>
+        <v>109.7814</v>
       </c>
       <c r="C26" t="n">
-        <v>16.7359</v>
+        <v>16.7357</v>
       </c>
       <c r="D26" t="n">
         <v>24.9878</v>
       </c>
       <c r="E26" t="n">
-        <v>29.1641</v>
+        <v>29.1371</v>
       </c>
       <c r="F26" t="n">
         <v>8.5733</v>
       </c>
       <c r="G26" t="n">
-        <v>16.957</v>
+        <v>16.9567</v>
       </c>
       <c r="H26" t="n">
         <v>3.9137</v>
@@ -1705,26 +1708,26 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
-        <v>109.7839</v>
+        <v>109.7817</v>
       </c>
       <c r="C27" t="n">
-        <v>16.7359</v>
+        <v>16.7357</v>
       </c>
       <c r="D27" t="n">
         <v>25.1758</v>
       </c>
       <c r="E27" t="n">
-        <v>30.3054</v>
+        <v>30.2569</v>
       </c>
       <c r="F27" t="n">
         <v>8.629</v>
       </c>
       <c r="G27" t="n">
-        <v>16.9983</v>
+        <v>16.9981</v>
       </c>
       <c r="H27" t="n">
         <v>3.9137</v>
@@ -1734,26 +1737,26 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
-        <v>109.8056</v>
+        <v>109.8034</v>
       </c>
       <c r="C28" t="n">
-        <v>16.7359</v>
+        <v>16.7357</v>
       </c>
       <c r="D28" t="n">
         <v>25.36</v>
       </c>
       <c r="E28" t="n">
-        <v>31.6648</v>
+        <v>31.6367</v>
       </c>
       <c r="F28" t="n">
         <v>8.6195</v>
       </c>
       <c r="G28" t="n">
-        <v>17.0024</v>
+        <v>17.0022</v>
       </c>
       <c r="H28" t="n">
         <v>3.9137</v>
@@ -1763,26 +1766,26 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
-        <v>109.836</v>
+        <v>109.8338</v>
       </c>
       <c r="C29" t="n">
-        <v>16.7359</v>
+        <v>16.7357</v>
       </c>
       <c r="D29" t="n">
         <v>25.6176</v>
       </c>
       <c r="E29" t="n">
-        <v>32.742</v>
+        <v>32.7132</v>
       </c>
       <c r="F29" t="n">
         <v>8.608499999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>17.0823</v>
+        <v>17.0821</v>
       </c>
       <c r="H29" t="n">
         <v>3.9137</v>
@@ -1792,26 +1795,26 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
-        <v>109.8373</v>
+        <v>109.8351</v>
       </c>
       <c r="C30" t="n">
-        <v>16.8387</v>
+        <v>16.8385</v>
       </c>
       <c r="D30" t="n">
         <v>25.9833</v>
       </c>
       <c r="E30" t="n">
-        <v>34.4225</v>
+        <v>34.385</v>
       </c>
       <c r="F30" t="n">
         <v>8.616</v>
       </c>
       <c r="G30" t="n">
-        <v>17.0864</v>
+        <v>17.0862</v>
       </c>
       <c r="H30" t="n">
         <v>3.9137</v>
@@ -1821,26 +1824,26 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
-        <v>109.8765</v>
+        <v>109.8744</v>
       </c>
       <c r="C31" t="n">
-        <v>16.8387</v>
+        <v>16.8385</v>
       </c>
       <c r="D31" t="n">
         <v>26.2352</v>
       </c>
       <c r="E31" t="n">
-        <v>35.1515</v>
+        <v>35.113</v>
       </c>
       <c r="F31" t="n">
         <v>8.612</v>
       </c>
       <c r="G31" t="n">
-        <v>17.1049</v>
+        <v>17.1047</v>
       </c>
       <c r="H31" t="n">
         <v>3.9137</v>
@@ -1850,26 +1853,26 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
-        <v>109.8827</v>
+        <v>109.8805</v>
       </c>
       <c r="C32" t="n">
-        <v>16.8387</v>
+        <v>16.8385</v>
       </c>
       <c r="D32" t="n">
         <v>26.6768</v>
       </c>
       <c r="E32" t="n">
-        <v>35.7495</v>
+        <v>35.7113</v>
       </c>
       <c r="F32" t="n">
         <v>8.5959</v>
       </c>
       <c r="G32" t="n">
-        <v>17.1107</v>
+        <v>17.1105</v>
       </c>
       <c r="H32" t="n">
         <v>3.9137</v>
@@ -1879,26 +1882,26 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
-        <v>109.9037</v>
+        <v>109.9015</v>
       </c>
       <c r="C33" t="n">
-        <v>16.8387</v>
+        <v>16.8385</v>
       </c>
       <c r="D33" t="n">
         <v>27.023</v>
       </c>
       <c r="E33" t="n">
-        <v>37.0375</v>
+        <v>37.01</v>
       </c>
       <c r="F33" t="n">
         <v>8.586600000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>17.1267</v>
+        <v>17.1265</v>
       </c>
       <c r="H33" t="n">
         <v>3.9137</v>
@@ -1908,26 +1911,26 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
-        <v>109.9052</v>
+        <v>109.903</v>
       </c>
       <c r="C34" t="n">
-        <v>16.8387</v>
+        <v>16.8385</v>
       </c>
       <c r="D34" t="n">
         <v>27.1876</v>
       </c>
       <c r="E34" t="n">
-        <v>37.5747</v>
+        <v>37.5428</v>
       </c>
       <c r="F34" t="n">
         <v>8.6089</v>
       </c>
       <c r="G34" t="n">
-        <v>17.1678</v>
+        <v>17.1676</v>
       </c>
       <c r="H34" t="n">
         <v>3.9137</v>
@@ -1937,26 +1940,26 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
-        <v>109.9082</v>
+        <v>109.906</v>
       </c>
       <c r="C35" t="n">
-        <v>16.8387</v>
+        <v>16.8385</v>
       </c>
       <c r="D35" t="n">
         <v>27.696</v>
       </c>
       <c r="E35" t="n">
-        <v>38.4571</v>
+        <v>38.4257</v>
       </c>
       <c r="F35" t="n">
         <v>8.601100000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>17.1918</v>
+        <v>17.1915</v>
       </c>
       <c r="H35" t="n">
         <v>3.9137</v>
@@ -1966,26 +1969,26 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
-        <v>109.9212</v>
+        <v>109.919</v>
       </c>
       <c r="C36" t="n">
-        <v>16.8387</v>
+        <v>16.8385</v>
       </c>
       <c r="D36" t="n">
         <v>27.9834</v>
       </c>
       <c r="E36" t="n">
-        <v>39.4366</v>
+        <v>39.40280000000001</v>
       </c>
       <c r="F36" t="n">
         <v>8.583299999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>17.1953</v>
+        <v>17.1951</v>
       </c>
       <c r="H36" t="n">
         <v>3.9137</v>
@@ -1995,26 +1998,26 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
-        <v>109.9314</v>
+        <v>109.9292</v>
       </c>
       <c r="C37" t="n">
-        <v>17.4042</v>
+        <v>17.404</v>
       </c>
       <c r="D37" t="n">
         <v>29.0403</v>
       </c>
       <c r="E37" t="n">
-        <v>40.5277</v>
+        <v>40.4929</v>
       </c>
       <c r="F37" t="n">
         <v>8.494999999999999</v>
       </c>
       <c r="G37" t="n">
-        <v>17.1959</v>
+        <v>17.1957</v>
       </c>
       <c r="H37" t="n">
         <v>3.9137</v>
@@ -2024,26 +2027,26 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
-        <v>109.9321</v>
+        <v>109.9299</v>
       </c>
       <c r="C38" t="n">
-        <v>17.4042</v>
+        <v>17.404</v>
       </c>
       <c r="D38" t="n">
         <v>29.5172</v>
       </c>
       <c r="E38" t="n">
-        <v>41.5382</v>
+        <v>41.5</v>
       </c>
       <c r="F38" t="n">
         <v>8.406799999999999</v>
       </c>
       <c r="G38" t="n">
-        <v>17.196</v>
+        <v>17.1958</v>
       </c>
       <c r="H38" t="n">
         <v>3.9137</v>
@@ -2053,26 +2056,26 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
-        <v>109.9321</v>
+        <v>109.9299</v>
       </c>
       <c r="C39" t="n">
-        <v>17.4042</v>
+        <v>17.404</v>
       </c>
       <c r="D39" t="n">
         <v>29.893</v>
       </c>
       <c r="E39" t="n">
-        <v>42.8823</v>
+        <v>42.8441</v>
       </c>
       <c r="F39" t="n">
         <v>8.3185</v>
       </c>
       <c r="G39" t="n">
-        <v>17.1985</v>
+        <v>17.1983</v>
       </c>
       <c r="H39" t="n">
         <v>3.9137</v>
@@ -2082,26 +2085,26 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
-        <v>109.9518</v>
+        <v>109.9496</v>
       </c>
       <c r="C40" t="n">
-        <v>17.4042</v>
+        <v>17.404</v>
       </c>
       <c r="D40" t="n">
         <v>30.2145</v>
       </c>
       <c r="E40" t="n">
-        <v>44.3004</v>
+        <v>44.2619</v>
       </c>
       <c r="F40" t="n">
         <v>8.2302</v>
       </c>
       <c r="G40" t="n">
-        <v>17.199</v>
+        <v>17.1988</v>
       </c>
       <c r="H40" t="n">
         <v>3.9137</v>
@@ -2111,26 +2114,26 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
-        <v>109.9548</v>
+        <v>109.9526</v>
       </c>
       <c r="C41" t="n">
-        <v>17.4042</v>
+        <v>17.404</v>
       </c>
       <c r="D41" t="n">
         <v>30.6802</v>
       </c>
       <c r="E41" t="n">
-        <v>45.929</v>
+        <v>45.8907</v>
       </c>
       <c r="F41" t="n">
         <v>8.1419</v>
       </c>
       <c r="G41" t="n">
-        <v>17.3457</v>
+        <v>17.3455</v>
       </c>
       <c r="H41" t="n">
         <v>3.9137</v>
@@ -2140,26 +2143,26 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
-        <v>109.9548</v>
+        <v>109.9526</v>
       </c>
       <c r="C42" t="n">
-        <v>17.4042</v>
+        <v>17.404</v>
       </c>
       <c r="D42" t="n">
         <v>30.9016</v>
       </c>
       <c r="E42" t="n">
-        <v>47.1933</v>
+        <v>47.1524</v>
       </c>
       <c r="F42" t="n">
         <v>8.053699999999999</v>
       </c>
       <c r="G42" t="n">
-        <v>17.3462</v>
+        <v>17.346</v>
       </c>
       <c r="H42" t="n">
         <v>3.9137</v>
@@ -2169,26 +2172,26 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
-        <v>109.9595</v>
+        <v>109.9573</v>
       </c>
       <c r="C43" t="n">
-        <v>17.4042</v>
+        <v>17.404</v>
       </c>
       <c r="D43" t="n">
         <v>31.1283</v>
       </c>
       <c r="E43" t="n">
-        <v>48.4345</v>
+        <v>48.40280000000001</v>
       </c>
       <c r="F43" t="n">
         <v>7.9954</v>
       </c>
       <c r="G43" t="n">
-        <v>17.3868</v>
+        <v>17.3865</v>
       </c>
       <c r="H43" t="n">
         <v>3.9137</v>
@@ -2198,26 +2201,26 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
-        <v>109.9595</v>
+        <v>109.9573</v>
       </c>
       <c r="C44" t="n">
-        <v>17.4042</v>
+        <v>17.404</v>
       </c>
       <c r="D44" t="n">
         <v>31.5212</v>
       </c>
       <c r="E44" t="n">
-        <v>49.962</v>
+        <v>49.93219999999999</v>
       </c>
       <c r="F44" t="n">
         <v>7.9077</v>
       </c>
       <c r="G44" t="n">
-        <v>17.3881</v>
+        <v>17.3879</v>
       </c>
       <c r="H44" t="n">
         <v>3.9137</v>
@@ -2227,26 +2230,26 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
-        <v>109.9764</v>
+        <v>109.9742</v>
       </c>
       <c r="C45" t="n">
-        <v>17.4042</v>
+        <v>17.404</v>
       </c>
       <c r="D45" t="n">
         <v>31.8485</v>
       </c>
       <c r="E45" t="n">
-        <v>51.1059</v>
+        <v>51.0808</v>
       </c>
       <c r="F45" t="n">
         <v>7.8194</v>
       </c>
       <c r="G45" t="n">
-        <v>17.3902</v>
+        <v>17.39</v>
       </c>
       <c r="H45" t="n">
         <v>3.9137</v>
@@ -2256,26 +2259,26 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
-        <v>109.9764</v>
+        <v>109.9742</v>
       </c>
       <c r="C46" t="n">
-        <v>17.4042</v>
+        <v>17.404</v>
       </c>
       <c r="D46" t="n">
         <v>32.0042</v>
       </c>
       <c r="E46" t="n">
-        <v>52.4351</v>
+        <v>52.4035</v>
       </c>
       <c r="F46" t="n">
         <v>7.731100000000001</v>
       </c>
       <c r="G46" t="n">
-        <v>17.46</v>
+        <v>17.4597</v>
       </c>
       <c r="H46" t="n">
         <v>3.9137</v>
@@ -2285,26 +2288,26 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
-        <v>109.9815</v>
+        <v>109.9793</v>
       </c>
       <c r="C47" t="n">
-        <v>17.4042</v>
+        <v>17.404</v>
       </c>
       <c r="D47" t="n">
         <v>32.4956</v>
       </c>
       <c r="E47" t="n">
-        <v>53.8829</v>
+        <v>53.8537</v>
       </c>
       <c r="F47" t="n">
         <v>7.9327</v>
       </c>
       <c r="G47" t="n">
-        <v>17.4963</v>
+        <v>17.496</v>
       </c>
       <c r="H47" t="n">
         <v>3.9137</v>
@@ -2314,26 +2317,26 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
-        <v>110.0103</v>
+        <v>110.0082</v>
       </c>
       <c r="C48" t="n">
-        <v>17.4042</v>
+        <v>17.404</v>
       </c>
       <c r="D48" t="n">
         <v>32.6441</v>
       </c>
       <c r="E48" t="n">
-        <v>55.4687</v>
+        <v>55.4372</v>
       </c>
       <c r="F48" t="n">
         <v>7.844399999999999</v>
       </c>
       <c r="G48" t="n">
-        <v>17.4963</v>
+        <v>17.496</v>
       </c>
       <c r="H48" t="n">
         <v>3.9137</v>
@@ -2343,26 +2346,26 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
-        <v>110.0133</v>
+        <v>110.0112</v>
       </c>
       <c r="C49" t="n">
-        <v>17.4042</v>
+        <v>17.404</v>
       </c>
       <c r="D49" t="n">
         <v>32.8931</v>
       </c>
       <c r="E49" t="n">
-        <v>56.851</v>
+        <v>56.8203</v>
       </c>
       <c r="F49" t="n">
         <v>7.8522</v>
       </c>
       <c r="G49" t="n">
-        <v>17.4963</v>
+        <v>17.496</v>
       </c>
       <c r="H49" t="n">
         <v>3.9137</v>
@@ -2372,26 +2375,26 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
-        <v>110.0133</v>
+        <v>110.0112</v>
       </c>
       <c r="C50" t="n">
-        <v>17.4042</v>
+        <v>17.404</v>
       </c>
       <c r="D50" t="n">
         <v>33.22069999999999</v>
       </c>
       <c r="E50" t="n">
-        <v>58.424</v>
+        <v>58.3891</v>
       </c>
       <c r="F50" t="n">
         <v>7.8597</v>
       </c>
       <c r="G50" t="n">
-        <v>17.8819</v>
+        <v>17.8817</v>
       </c>
       <c r="H50" t="n">
         <v>3.9137</v>
@@ -2401,26 +2404,26 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
-        <v>110.0607</v>
+        <v>110.0585</v>
       </c>
       <c r="C51" t="n">
-        <v>17.4042</v>
+        <v>17.404</v>
       </c>
       <c r="D51" t="n">
         <v>33.4106</v>
       </c>
       <c r="E51" t="n">
-        <v>59.3316</v>
+        <v>59.2991</v>
       </c>
       <c r="F51" t="n">
         <v>7.8658</v>
       </c>
       <c r="G51" t="n">
-        <v>17.9351</v>
+        <v>17.9348</v>
       </c>
       <c r="H51" t="n">
         <v>3.9137</v>
@@ -2430,142 +2433,142 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
-        <v>110.0923</v>
+        <v>110.0863</v>
       </c>
       <c r="C52" t="n">
-        <v>17.4042</v>
+        <v>17.404</v>
       </c>
       <c r="D52" t="n">
         <v>33.6086</v>
       </c>
       <c r="E52" t="n">
-        <v>60.2548</v>
+        <v>60.2257</v>
       </c>
       <c r="F52" t="n">
         <v>7.872</v>
       </c>
       <c r="G52" t="n">
-        <v>17.9663</v>
+        <v>17.9661</v>
       </c>
       <c r="H52" t="n">
         <v>3.9137</v>
       </c>
       <c r="I52" t="n">
-        <v>2.1644</v>
+        <v>2.1643</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
-        <v>110.1037</v>
+        <v>110.0977</v>
       </c>
       <c r="C53" t="n">
-        <v>17.4042</v>
+        <v>17.404</v>
       </c>
       <c r="D53" t="n">
         <v>33.6356</v>
       </c>
       <c r="E53" t="n">
-        <v>61.1996</v>
+        <v>61.175</v>
       </c>
       <c r="F53" t="n">
         <v>7.8782</v>
       </c>
       <c r="G53" t="n">
-        <v>18.0116</v>
+        <v>18.0114</v>
       </c>
       <c r="H53" t="n">
         <v>3.9137</v>
       </c>
       <c r="I53" t="n">
-        <v>2.1644</v>
+        <v>2.1643</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
-        <v>110.1082</v>
+        <v>110.1022</v>
       </c>
       <c r="C54" t="n">
-        <v>19.0768</v>
+        <v>19.0766</v>
       </c>
       <c r="D54" t="n">
         <v>33.6356</v>
       </c>
       <c r="E54" t="n">
-        <v>62.003</v>
+        <v>61.9807</v>
       </c>
       <c r="F54" t="n">
         <v>7.884399999999999</v>
       </c>
       <c r="G54" t="n">
-        <v>18.0596</v>
+        <v>18.0594</v>
       </c>
       <c r="H54" t="n">
         <v>3.9137</v>
       </c>
       <c r="I54" t="n">
-        <v>2.1644</v>
+        <v>2.1643</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
-        <v>110.1122</v>
+        <v>110.1062</v>
       </c>
       <c r="C55" t="n">
-        <v>19.0768</v>
+        <v>19.0766</v>
       </c>
       <c r="D55" t="n">
         <v>33.8471</v>
       </c>
       <c r="E55" t="n">
-        <v>62.788</v>
+        <v>62.76580000000001</v>
       </c>
       <c r="F55" t="n">
         <v>7.8905</v>
       </c>
       <c r="G55" t="n">
-        <v>18.0618</v>
+        <v>18.0616</v>
       </c>
       <c r="H55" t="n">
         <v>3.9137</v>
       </c>
       <c r="I55" t="n">
-        <v>2.1644</v>
+        <v>2.1643</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
-        <v>110.1122</v>
+        <v>110.1062</v>
       </c>
       <c r="C56" t="n">
-        <v>19.0768</v>
+        <v>19.0766</v>
       </c>
       <c r="D56" t="n">
         <v>33.8876</v>
       </c>
       <c r="E56" t="n">
-        <v>63.6554</v>
+        <v>63.63630000000001</v>
       </c>
       <c r="F56" t="n">
         <v>7.8967</v>
       </c>
       <c r="G56" t="n">
-        <v>18.0646</v>
+        <v>18.0644</v>
       </c>
       <c r="H56" t="n">
         <v>3.9137</v>
@@ -2575,55 +2578,55 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
-        <v>110.1662</v>
+        <v>110.1602</v>
       </c>
       <c r="C57" t="n">
-        <v>19.0768</v>
+        <v>19.0766</v>
       </c>
       <c r="D57" t="n">
-        <v>34.1037</v>
+        <v>34.1036</v>
       </c>
       <c r="E57" t="n">
-        <v>64.3811</v>
+        <v>64.37469999999999</v>
       </c>
       <c r="F57" t="n">
         <v>7.9029</v>
       </c>
       <c r="G57" t="n">
-        <v>18.1046</v>
+        <v>18.1044</v>
       </c>
       <c r="H57" t="n">
         <v>3.9137</v>
       </c>
       <c r="I57" t="n">
-        <v>2.1645</v>
+        <v>2.1644</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n">
+      <c r="A58" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
-        <v>110.2405</v>
+        <v>110.2342</v>
       </c>
       <c r="C58" t="n">
-        <v>19.0768</v>
+        <v>19.0766</v>
       </c>
       <c r="D58" t="n">
-        <v>34.41869999999999</v>
+        <v>34.4186</v>
       </c>
       <c r="E58" t="n">
-        <v>65.989</v>
+        <v>65.9658</v>
       </c>
       <c r="F58" t="n">
         <v>7.9091</v>
       </c>
       <c r="G58" t="n">
-        <v>18.1067</v>
+        <v>18.1065</v>
       </c>
       <c r="H58" t="n">
         <v>3.9137</v>
@@ -2633,26 +2636,26 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
-        <v>110.2734</v>
+        <v>110.2667</v>
       </c>
       <c r="C59" t="n">
-        <v>19.0768</v>
+        <v>19.0766</v>
       </c>
       <c r="D59" t="n">
-        <v>34.41869999999999</v>
+        <v>34.4186</v>
       </c>
       <c r="E59" t="n">
-        <v>67.35510000000001</v>
+        <v>67.33369999999999</v>
       </c>
       <c r="F59" t="n">
         <v>7.9152</v>
       </c>
       <c r="G59" t="n">
-        <v>18.1365</v>
+        <v>18.1363</v>
       </c>
       <c r="H59" t="n">
         <v>3.9137</v>
@@ -2662,26 +2665,26 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
-        <v>110.2734</v>
+        <v>110.2667</v>
       </c>
       <c r="C60" t="n">
-        <v>19.0768</v>
+        <v>19.0766</v>
       </c>
       <c r="D60" t="n">
-        <v>34.41869999999999</v>
+        <v>34.4186</v>
       </c>
       <c r="E60" t="n">
-        <v>68.26310000000001</v>
+        <v>68.23910000000001</v>
       </c>
       <c r="F60" t="n">
         <v>7.921399999999999</v>
       </c>
       <c r="G60" t="n">
-        <v>18.1365</v>
+        <v>18.1363</v>
       </c>
       <c r="H60" t="n">
         <v>3.9137</v>
@@ -2691,26 +2694,26 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
-        <v>110.2734</v>
+        <v>110.2667</v>
       </c>
       <c r="C61" t="n">
-        <v>19.0768</v>
+        <v>19.0766</v>
       </c>
       <c r="D61" t="n">
-        <v>34.7697</v>
+        <v>34.7696</v>
       </c>
       <c r="E61" t="n">
-        <v>69.3095</v>
+        <v>69.29219999999999</v>
       </c>
       <c r="F61" t="n">
         <v>7.9276</v>
       </c>
       <c r="G61" t="n">
-        <v>18.145</v>
+        <v>18.1447</v>
       </c>
       <c r="H61" t="n">
         <v>3.9137</v>
@@ -2720,84 +2723,84 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
+      <c r="A62" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
-        <v>110.2946</v>
+        <v>110.2879</v>
       </c>
       <c r="C62" t="n">
-        <v>19.0768</v>
+        <v>19.0766</v>
       </c>
       <c r="D62" t="n">
-        <v>34.7697</v>
+        <v>34.7696</v>
       </c>
       <c r="E62" t="n">
-        <v>70.5573</v>
+        <v>70.5325</v>
       </c>
       <c r="F62" t="n">
         <v>7.8883</v>
       </c>
       <c r="G62" t="n">
-        <v>18.1451</v>
+        <v>18.1449</v>
       </c>
       <c r="H62" t="n">
         <v>3.9137</v>
       </c>
       <c r="I62" t="n">
-        <v>2.1657</v>
+        <v>2.1656</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
-        <v>110.2946</v>
+        <v>110.2879</v>
       </c>
       <c r="C63" t="n">
-        <v>19.0768</v>
+        <v>19.0766</v>
       </c>
       <c r="D63" t="n">
         <v>34.8282</v>
       </c>
       <c r="E63" t="n">
-        <v>71.9028</v>
+        <v>71.877</v>
       </c>
       <c r="F63" t="n">
         <v>7.8489</v>
       </c>
       <c r="G63" t="n">
-        <v>18.1451</v>
+        <v>18.1449</v>
       </c>
       <c r="H63" t="n">
         <v>3.9137</v>
       </c>
       <c r="I63" t="n">
-        <v>2.1658</v>
+        <v>2.1657</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n">
+      <c r="A64" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
-        <v>110.2998</v>
+        <v>110.2931</v>
       </c>
       <c r="C64" t="n">
-        <v>19.0768</v>
+        <v>19.0766</v>
       </c>
       <c r="D64" t="n">
         <v>34.8282</v>
       </c>
       <c r="E64" t="n">
-        <v>73.7351</v>
+        <v>73.7119</v>
       </c>
       <c r="F64" t="n">
         <v>7.8107</v>
       </c>
       <c r="G64" t="n">
-        <v>18.1715</v>
+        <v>18.1713</v>
       </c>
       <c r="H64" t="n">
         <v>3.9137</v>
@@ -2807,26 +2810,26 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
-        <v>110.2999</v>
+        <v>110.2932</v>
       </c>
       <c r="C65" t="n">
-        <v>19.0768</v>
+        <v>19.0766</v>
       </c>
       <c r="D65" t="n">
         <v>34.8282</v>
       </c>
       <c r="E65" t="n">
-        <v>74.60850000000001</v>
+        <v>74.5898</v>
       </c>
       <c r="F65" t="n">
         <v>7.7714</v>
       </c>
       <c r="G65" t="n">
-        <v>18.2115</v>
+        <v>18.2113</v>
       </c>
       <c r="H65" t="n">
         <v>3.9137</v>
@@ -2836,55 +2839,55 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="n">
+      <c r="A66" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
-        <v>110.3043</v>
+        <v>110.2976</v>
       </c>
       <c r="C66" t="n">
-        <v>19.0768</v>
+        <v>19.0766</v>
       </c>
       <c r="D66" t="n">
         <v>34.8282</v>
       </c>
       <c r="E66" t="n">
-        <v>75.3052</v>
+        <v>75.36969999999999</v>
       </c>
       <c r="F66" t="n">
         <v>7.732</v>
       </c>
       <c r="G66" t="n">
-        <v>18.2115</v>
+        <v>18.2113</v>
       </c>
       <c r="H66" t="n">
         <v>3.9137</v>
       </c>
       <c r="I66" t="n">
-        <v>2.1701</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="n">
+      <c r="A67" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
-        <v>110.327</v>
+        <v>110.3203</v>
       </c>
       <c r="C67" t="n">
-        <v>19.0768</v>
+        <v>19.0766</v>
       </c>
       <c r="D67" t="n">
         <v>34.8282</v>
       </c>
       <c r="E67" t="n">
-        <v>75.9914</v>
+        <v>76.0908</v>
       </c>
       <c r="F67" t="n">
         <v>7.692699999999999</v>
       </c>
       <c r="G67" t="n">
-        <v>18.2115</v>
+        <v>18.2113</v>
       </c>
       <c r="H67" t="n">
         <v>3.9137</v>
@@ -2894,26 +2897,26 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="n">
+      <c r="A68" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
-        <v>110.334</v>
+        <v>110.3273</v>
       </c>
       <c r="C68" t="n">
-        <v>19.0768</v>
+        <v>19.0766</v>
       </c>
       <c r="D68" t="n">
         <v>34.8912</v>
       </c>
       <c r="E68" t="n">
-        <v>76.3515</v>
+        <v>76.4768</v>
       </c>
       <c r="F68" t="n">
         <v>7.6534</v>
       </c>
       <c r="G68" t="n">
-        <v>18.2157</v>
+        <v>18.2155</v>
       </c>
       <c r="H68" t="n">
         <v>3.9137</v>
@@ -2923,26 +2926,26 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="n">
+      <c r="A69" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B69" t="n">
-        <v>110.334</v>
+        <v>110.3273</v>
       </c>
       <c r="C69" t="n">
-        <v>20.0677</v>
+        <v>20.0675</v>
       </c>
       <c r="D69" t="n">
         <v>34.9542</v>
       </c>
       <c r="E69" t="n">
-        <v>77.2662</v>
+        <v>77.405</v>
       </c>
       <c r="F69" t="n">
         <v>7.619</v>
       </c>
       <c r="G69" t="n">
-        <v>18.2257</v>
+        <v>18.2255</v>
       </c>
       <c r="H69" t="n">
         <v>3.9137</v>
@@ -2952,26 +2955,26 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="n">
+      <c r="A70" s="3" t="n">
         <v>46266</v>
       </c>
       <c r="B70" t="n">
-        <v>110.334</v>
+        <v>110.3273</v>
       </c>
       <c r="C70" t="n">
-        <v>20.1825</v>
+        <v>20.1823</v>
       </c>
       <c r="D70" t="n">
         <v>34.9542</v>
       </c>
       <c r="E70" t="n">
-        <v>77.2662</v>
+        <v>77.405</v>
       </c>
       <c r="F70" t="n">
         <v>7.5796</v>
       </c>
       <c r="G70" t="n">
-        <v>18.2507</v>
+        <v>18.2505</v>
       </c>
       <c r="H70" t="n">
         <v>3.9137</v>
@@ -3057,16 +3060,16 @@
         <v>44197</v>
       </c>
       <c r="B2" t="n">
-        <v>109289.3</v>
+        <v>109289.2</v>
       </c>
       <c r="C2" t="n">
-        <v>13982</v>
+        <v>13981.8</v>
       </c>
       <c r="D2" t="n">
         <v>17351.1</v>
       </c>
       <c r="E2" t="n">
-        <v>9463.200000000001</v>
+        <v>9430.5</v>
       </c>
       <c r="F2" t="n">
         <v>3913.7</v>
@@ -3078,13 +3081,13 @@
         <v>9134.4</v>
       </c>
       <c r="I2" t="n">
-        <v>15408.5</v>
+        <v>15408.4</v>
       </c>
       <c r="J2" t="n">
         <v>166</v>
       </c>
       <c r="K2" t="n">
-        <v>180698.2</v>
+        <v>180665</v>
       </c>
     </row>
     <row r="3">
@@ -3092,16 +3095,16 @@
         <v>44228</v>
       </c>
       <c r="B3" t="n">
-        <v>109299.2</v>
+        <v>109299.1</v>
       </c>
       <c r="C3" t="n">
-        <v>13982</v>
+        <v>13981.8</v>
       </c>
       <c r="D3" t="n">
         <v>17471.8</v>
       </c>
       <c r="E3" t="n">
-        <v>9786.1</v>
+        <v>9743.799999999999</v>
       </c>
       <c r="F3" t="n">
         <v>3913.7</v>
@@ -3113,13 +3116,13 @@
         <v>9143.799999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>15426</v>
+        <v>15425.8</v>
       </c>
       <c r="J3" t="n">
         <v>166</v>
       </c>
       <c r="K3" t="n">
-        <v>181178.5</v>
+        <v>181135.8</v>
       </c>
     </row>
     <row r="4">
@@ -3130,13 +3133,13 @@
         <v>109305.6</v>
       </c>
       <c r="C4" t="n">
-        <v>13982</v>
+        <v>13981.8</v>
       </c>
       <c r="D4" t="n">
         <v>17804.3</v>
       </c>
       <c r="E4" t="n">
-        <v>10278.1</v>
+        <v>10227.6</v>
       </c>
       <c r="F4" t="n">
         <v>3913.7</v>
@@ -3148,13 +3151,13 @@
         <v>9172.5</v>
       </c>
       <c r="I4" t="n">
-        <v>15435.1</v>
+        <v>15434.9</v>
       </c>
       <c r="J4" t="n">
         <v>166</v>
       </c>
       <c r="K4" t="n">
-        <v>182047.3</v>
+        <v>181996.4</v>
       </c>
     </row>
     <row r="5">
@@ -3165,13 +3168,13 @@
         <v>109305.6</v>
       </c>
       <c r="C5" t="n">
-        <v>13982</v>
+        <v>13981.8</v>
       </c>
       <c r="D5" t="n">
         <v>18012.4</v>
       </c>
       <c r="E5" t="n">
-        <v>10650.6</v>
+        <v>10597.2</v>
       </c>
       <c r="F5" t="n">
         <v>3913.7</v>
@@ -3183,13 +3186,13 @@
         <v>9214.9</v>
       </c>
       <c r="I5" t="n">
-        <v>15490.4</v>
+        <v>15490.3</v>
       </c>
       <c r="J5" t="n">
         <v>166</v>
       </c>
       <c r="K5" t="n">
-        <v>182725.6</v>
+        <v>182671.8</v>
       </c>
     </row>
     <row r="6">
@@ -3197,16 +3200,16 @@
         <v>44317</v>
       </c>
       <c r="B6" t="n">
-        <v>109315</v>
+        <v>109314.4</v>
       </c>
       <c r="C6" t="n">
-        <v>13982</v>
+        <v>13981.8</v>
       </c>
       <c r="D6" t="n">
         <v>18263</v>
       </c>
       <c r="E6" t="n">
-        <v>11085.3</v>
+        <v>11027.1</v>
       </c>
       <c r="F6" t="n">
         <v>3913.7</v>
@@ -3218,13 +3221,13 @@
         <v>9214.9</v>
       </c>
       <c r="I6" t="n">
-        <v>15515.6</v>
+        <v>15515.3</v>
       </c>
       <c r="J6" t="n">
         <v>166</v>
       </c>
       <c r="K6" t="n">
-        <v>183445.5</v>
+        <v>183386.3</v>
       </c>
     </row>
     <row r="7">
@@ -3232,16 +3235,16 @@
         <v>44348</v>
       </c>
       <c r="B7" t="n">
-        <v>109348.1</v>
+        <v>109347.5</v>
       </c>
       <c r="C7" t="n">
-        <v>13982</v>
+        <v>13981.8</v>
       </c>
       <c r="D7" t="n">
         <v>18602.1</v>
       </c>
       <c r="E7" t="n">
-        <v>11562.9</v>
+        <v>11496.4</v>
       </c>
       <c r="F7" t="n">
         <v>3913.7</v>
@@ -3253,13 +3256,13 @@
         <v>9214.9</v>
       </c>
       <c r="I7" t="n">
-        <v>15559.5</v>
+        <v>15559.3</v>
       </c>
       <c r="J7" t="n">
         <v>168.9</v>
       </c>
       <c r="K7" t="n">
-        <v>184342</v>
+        <v>184274.5</v>
       </c>
     </row>
     <row r="8">
@@ -3267,16 +3270,16 @@
         <v>44378</v>
       </c>
       <c r="B8" t="n">
-        <v>109348.1</v>
+        <v>109347.5</v>
       </c>
       <c r="C8" t="n">
-        <v>14159.1</v>
+        <v>14158.9</v>
       </c>
       <c r="D8" t="n">
         <v>18873.7</v>
       </c>
       <c r="E8" t="n">
-        <v>12082.4</v>
+        <v>12008.8</v>
       </c>
       <c r="F8" t="n">
         <v>3913.7</v>
@@ -3288,13 +3291,13 @@
         <v>9214.9</v>
       </c>
       <c r="I8" t="n">
-        <v>15560.2</v>
+        <v>15559.9</v>
       </c>
       <c r="J8" t="n">
         <v>168.9</v>
       </c>
       <c r="K8" t="n">
-        <v>185310.9</v>
+        <v>185236.3</v>
       </c>
     </row>
     <row r="9">
@@ -3302,16 +3305,16 @@
         <v>44409</v>
       </c>
       <c r="B9" t="n">
-        <v>109362.8</v>
+        <v>109362.2</v>
       </c>
       <c r="C9" t="n">
-        <v>14159.1</v>
+        <v>14158.9</v>
       </c>
       <c r="D9" t="n">
         <v>19307.6</v>
       </c>
       <c r="E9" t="n">
-        <v>12891.7</v>
+        <v>12830.7</v>
       </c>
       <c r="F9" t="n">
         <v>3913.7</v>
@@ -3323,13 +3326,13 @@
         <v>9216.700000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>15610.8</v>
+        <v>15610.5</v>
       </c>
       <c r="J9" t="n">
         <v>168.9</v>
       </c>
       <c r="K9" t="n">
-        <v>186621.3</v>
+        <v>186559.2</v>
       </c>
     </row>
     <row r="10">
@@ -3337,16 +3340,16 @@
         <v>44440</v>
       </c>
       <c r="B10" t="n">
-        <v>109364.4</v>
+        <v>109363.9</v>
       </c>
       <c r="C10" t="n">
-        <v>15497.4</v>
+        <v>15497.2</v>
       </c>
       <c r="D10" t="n">
         <v>19586</v>
       </c>
       <c r="E10" t="n">
-        <v>13467.7</v>
+        <v>13398</v>
       </c>
       <c r="F10" t="n">
         <v>3913.7</v>
@@ -3358,13 +3361,13 @@
         <v>9219.5</v>
       </c>
       <c r="I10" t="n">
-        <v>15613.8</v>
+        <v>15613.6</v>
       </c>
       <c r="J10" t="n">
         <v>168.9</v>
       </c>
       <c r="K10" t="n">
-        <v>188821.5</v>
+        <v>188750.7</v>
       </c>
     </row>
     <row r="11">
@@ -3372,16 +3375,16 @@
         <v>44470</v>
       </c>
       <c r="B11" t="n">
-        <v>109367</v>
+        <v>109366.5</v>
       </c>
       <c r="C11" t="n">
-        <v>15526.9</v>
+        <v>15526.7</v>
       </c>
       <c r="D11" t="n">
         <v>19868.4</v>
       </c>
       <c r="E11" t="n">
-        <v>14582.3</v>
+        <v>14513.3</v>
       </c>
       <c r="F11" t="n">
         <v>3913.7</v>
@@ -3393,13 +3396,13 @@
         <v>9221.799999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>15646.5</v>
+        <v>15646.2</v>
       </c>
       <c r="J11" t="n">
         <v>170.5</v>
       </c>
       <c r="K11" t="n">
-        <v>190287.2</v>
+        <v>190217.1</v>
       </c>
     </row>
     <row r="12">
@@ -3407,16 +3410,16 @@
         <v>44501</v>
       </c>
       <c r="B12" t="n">
-        <v>109376.6</v>
+        <v>109376.1</v>
       </c>
       <c r="C12" t="n">
-        <v>15526.9</v>
+        <v>15526.7</v>
       </c>
       <c r="D12" t="n">
         <v>20238.5</v>
       </c>
       <c r="E12" t="n">
-        <v>15306.1</v>
+        <v>15226.8</v>
       </c>
       <c r="F12" t="n">
         <v>3913.7</v>
@@ -3428,13 +3431,13 @@
         <v>9221.799999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>15660.5</v>
+        <v>15660.2</v>
       </c>
       <c r="J12" t="n">
         <v>170.5</v>
       </c>
       <c r="K12" t="n">
-        <v>191404.6</v>
+        <v>191324.2</v>
       </c>
     </row>
     <row r="13">
@@ -3442,16 +3445,16 @@
         <v>44531</v>
       </c>
       <c r="B13" t="n">
-        <v>109404.5</v>
+        <v>109404</v>
       </c>
       <c r="C13" t="n">
-        <v>15526.9</v>
+        <v>15526.7</v>
       </c>
       <c r="D13" t="n">
         <v>20929.3</v>
       </c>
       <c r="E13" t="n">
-        <v>16110.4</v>
+        <v>16020.7</v>
       </c>
       <c r="F13" t="n">
         <v>3913.7</v>
@@ -3463,13 +3466,13 @@
         <v>9221.799999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>16079.3</v>
+        <v>16079.1</v>
       </c>
       <c r="J13" t="n">
         <v>170.5</v>
       </c>
       <c r="K13" t="n">
-        <v>193346.4</v>
+        <v>193255.7</v>
       </c>
     </row>
     <row r="14">
@@ -3477,16 +3480,16 @@
         <v>44562</v>
       </c>
       <c r="B14" t="n">
-        <v>109405.3</v>
+        <v>109404.7</v>
       </c>
       <c r="C14" t="n">
-        <v>15526.9</v>
+        <v>15526.7</v>
       </c>
       <c r="D14" t="n">
         <v>21196.6</v>
       </c>
       <c r="E14" t="n">
-        <v>16594</v>
+        <v>16508.7</v>
       </c>
       <c r="F14" t="n">
         <v>3913.7</v>
@@ -3498,13 +3501,13 @@
         <v>9165.5</v>
       </c>
       <c r="I14" t="n">
-        <v>16217.3</v>
+        <v>16217.1</v>
       </c>
       <c r="J14" t="n">
         <v>170.5</v>
       </c>
       <c r="K14" t="n">
-        <v>194179.8</v>
+        <v>194093.4</v>
       </c>
     </row>
     <row r="15">
@@ -3512,16 +3515,16 @@
         <v>44593</v>
       </c>
       <c r="B15" t="n">
-        <v>109425.2</v>
+        <v>109424.6</v>
       </c>
       <c r="C15" t="n">
-        <v>15653.2</v>
+        <v>15653</v>
       </c>
       <c r="D15" t="n">
         <v>21564.6</v>
       </c>
       <c r="E15" t="n">
-        <v>17267.5</v>
+        <v>17176.7</v>
       </c>
       <c r="F15" t="n">
         <v>3913.7</v>
@@ -3533,13 +3536,13 @@
         <v>9106</v>
       </c>
       <c r="I15" t="n">
-        <v>16218.8</v>
+        <v>16218.5</v>
       </c>
       <c r="J15" t="n">
         <v>172.2</v>
       </c>
       <c r="K15" t="n">
-        <v>195311.2</v>
+        <v>195219.4</v>
       </c>
     </row>
     <row r="16">
@@ -3547,16 +3550,16 @@
         <v>44621</v>
       </c>
       <c r="B16" t="n">
-        <v>109473.3</v>
+        <v>109471.8</v>
       </c>
       <c r="C16" t="n">
-        <v>15653.2</v>
+        <v>15653</v>
       </c>
       <c r="D16" t="n">
         <v>21599.5</v>
       </c>
       <c r="E16" t="n">
-        <v>18098.6</v>
+        <v>18013.9</v>
       </c>
       <c r="F16" t="n">
         <v>3913.7</v>
@@ -3568,13 +3571,13 @@
         <v>9052.700000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>16295.4</v>
+        <v>16295.1</v>
       </c>
       <c r="J16" t="n">
         <v>172.2</v>
       </c>
       <c r="K16" t="n">
-        <v>196248.6</v>
+        <v>196162</v>
       </c>
     </row>
     <row r="17">
@@ -3582,16 +3585,16 @@
         <v>44652</v>
       </c>
       <c r="B17" t="n">
-        <v>109474.3</v>
+        <v>109472.8</v>
       </c>
       <c r="C17" t="n">
-        <v>15653.2</v>
+        <v>15653</v>
       </c>
       <c r="D17" t="n">
         <v>21658.3</v>
       </c>
       <c r="E17" t="n">
-        <v>18883</v>
+        <v>18803.5</v>
       </c>
       <c r="F17" t="n">
         <v>3913.7</v>
@@ -3603,13 +3606,13 @@
         <v>8993.6</v>
       </c>
       <c r="I17" t="n">
-        <v>16332.9</v>
+        <v>16332.7</v>
       </c>
       <c r="J17" t="n">
         <v>173.1</v>
       </c>
       <c r="K17" t="n">
-        <v>197072.1</v>
+        <v>196990.6</v>
       </c>
     </row>
     <row r="18">
@@ -3617,16 +3620,16 @@
         <v>44682</v>
       </c>
       <c r="B18" t="n">
-        <v>109503.8</v>
+        <v>109502.3</v>
       </c>
       <c r="C18" t="n">
-        <v>15653.2</v>
+        <v>15653</v>
       </c>
       <c r="D18" t="n">
         <v>21802.3</v>
       </c>
       <c r="E18" t="n">
-        <v>19765</v>
+        <v>19664.4</v>
       </c>
       <c r="F18" t="n">
         <v>3913.7</v>
@@ -3638,13 +3641,13 @@
         <v>8934.1</v>
       </c>
       <c r="I18" t="n">
-        <v>16685.7</v>
+        <v>16685.5</v>
       </c>
       <c r="J18" t="n">
         <v>173.1</v>
       </c>
       <c r="K18" t="n">
-        <v>198420.9</v>
+        <v>198318.3</v>
       </c>
     </row>
     <row r="19">
@@ -3652,16 +3655,16 @@
         <v>44713</v>
       </c>
       <c r="B19" t="n">
-        <v>109505</v>
+        <v>109503.5</v>
       </c>
       <c r="C19" t="n">
-        <v>15676.9</v>
+        <v>15676.7</v>
       </c>
       <c r="D19" t="n">
         <v>21904.9</v>
       </c>
       <c r="E19" t="n">
-        <v>20605.2</v>
+        <v>20499.2</v>
       </c>
       <c r="F19" t="n">
         <v>3913.7</v>
@@ -3673,13 +3676,13 @@
         <v>8879</v>
       </c>
       <c r="I19" t="n">
-        <v>16709.3</v>
+        <v>16709.1</v>
       </c>
       <c r="J19" t="n">
         <v>173.1</v>
       </c>
       <c r="K19" t="n">
-        <v>199357</v>
+        <v>199249</v>
       </c>
     </row>
     <row r="20">
@@ -3687,16 +3690,16 @@
         <v>44743</v>
       </c>
       <c r="B20" t="n">
-        <v>109648.9</v>
+        <v>109647.4</v>
       </c>
       <c r="C20" t="n">
-        <v>15789.5</v>
+        <v>15789.3</v>
       </c>
       <c r="D20" t="n">
         <v>22228.7</v>
       </c>
       <c r="E20" t="n">
-        <v>21733.7</v>
+        <v>21615.8</v>
       </c>
       <c r="F20" t="n">
         <v>3913.7</v>
@@ -3708,13 +3711,13 @@
         <v>8819.5</v>
       </c>
       <c r="I20" t="n">
-        <v>16720.8</v>
+        <v>16720.5</v>
       </c>
       <c r="J20" t="n">
         <v>173.1</v>
       </c>
       <c r="K20" t="n">
-        <v>201017.9</v>
+        <v>200897.9</v>
       </c>
     </row>
     <row r="21">
@@ -3722,16 +3725,16 @@
         <v>44774</v>
       </c>
       <c r="B21" t="n">
-        <v>109650.5</v>
+        <v>109648.9</v>
       </c>
       <c r="C21" t="n">
-        <v>15801.8</v>
+        <v>15801.6</v>
       </c>
       <c r="D21" t="n">
         <v>22424.9</v>
       </c>
       <c r="E21" t="n">
-        <v>22873.1</v>
+        <v>22739.7</v>
       </c>
       <c r="F21" t="n">
         <v>3913.7</v>
@@ -3743,13 +3746,13 @@
         <v>8760</v>
       </c>
       <c r="I21" t="n">
-        <v>16722</v>
+        <v>16721.7</v>
       </c>
       <c r="J21" t="n">
         <v>173.1</v>
       </c>
       <c r="K21" t="n">
-        <v>202309</v>
+        <v>202173.6</v>
       </c>
     </row>
     <row r="22">
@@ -3757,16 +3760,16 @@
         <v>44805</v>
       </c>
       <c r="B22" t="n">
-        <v>109682.7</v>
+        <v>109681.1</v>
       </c>
       <c r="C22" t="n">
-        <v>16033.7</v>
+        <v>16033.5</v>
       </c>
       <c r="D22" t="n">
         <v>22664.8</v>
       </c>
       <c r="E22" t="n">
-        <v>24209.5</v>
+        <v>24065.2</v>
       </c>
       <c r="F22" t="n">
         <v>3913.7</v>
@@ -3778,13 +3781,13 @@
         <v>8702</v>
       </c>
       <c r="I22" t="n">
-        <v>16913.3</v>
+        <v>16913.1</v>
       </c>
       <c r="J22" t="n">
         <v>173.1</v>
       </c>
       <c r="K22" t="n">
-        <v>204282.6</v>
+        <v>204136.3</v>
       </c>
     </row>
     <row r="23">
@@ -3792,16 +3795,16 @@
         <v>44835</v>
       </c>
       <c r="B23" t="n">
-        <v>109692.9</v>
+        <v>109690.7</v>
       </c>
       <c r="C23" t="n">
-        <v>16370.6</v>
+        <v>16370.4</v>
       </c>
       <c r="D23" t="n">
         <v>23325.9</v>
       </c>
       <c r="E23" t="n">
-        <v>25186</v>
+        <v>25133.5</v>
       </c>
       <c r="F23" t="n">
         <v>3913.7</v>
@@ -3813,13 +3816,13 @@
         <v>8654.4</v>
       </c>
       <c r="I23" t="n">
-        <v>16913.8</v>
+        <v>16913.6</v>
       </c>
       <c r="J23" t="n">
         <v>173.1</v>
       </c>
       <c r="K23" t="n">
-        <v>206220.3</v>
+        <v>206165.2</v>
       </c>
     </row>
     <row r="24">
@@ -3827,16 +3830,16 @@
         <v>44866</v>
       </c>
       <c r="B24" t="n">
-        <v>109748.6</v>
+        <v>109746.4</v>
       </c>
       <c r="C24" t="n">
-        <v>16735.9</v>
+        <v>16735.7</v>
       </c>
       <c r="D24" t="n">
         <v>23640.6</v>
       </c>
       <c r="E24" t="n">
-        <v>26296.2</v>
+        <v>26249.3</v>
       </c>
       <c r="F24" t="n">
         <v>3913.7</v>
@@ -3848,13 +3851,13 @@
         <v>8601.1</v>
       </c>
       <c r="I24" t="n">
-        <v>16931.4</v>
+        <v>16931.2</v>
       </c>
       <c r="J24" t="n">
         <v>173.1</v>
       </c>
       <c r="K24" t="n">
-        <v>208030.6</v>
+        <v>207981.1</v>
       </c>
     </row>
     <row r="25">
@@ -3862,16 +3865,16 @@
         <v>44896</v>
       </c>
       <c r="B25" t="n">
-        <v>109758.7</v>
+        <v>109756.5</v>
       </c>
       <c r="C25" t="n">
-        <v>16735.9</v>
+        <v>16735.7</v>
       </c>
       <c r="D25" t="n">
         <v>24114.5</v>
       </c>
       <c r="E25" t="n">
-        <v>27704.4</v>
+        <v>27657.9</v>
       </c>
       <c r="F25" t="n">
         <v>3913.7</v>
@@ -3883,13 +3886,13 @@
         <v>8588.799999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>16957</v>
+        <v>16956.7</v>
       </c>
       <c r="J25" t="n">
         <v>173.1</v>
       </c>
       <c r="K25" t="n">
-        <v>209936</v>
+        <v>209886.9</v>
       </c>
     </row>
     <row r="26">
@@ -3897,16 +3900,16 @@
         <v>44927</v>
       </c>
       <c r="B26" t="n">
-        <v>109783.6</v>
+        <v>109781.4</v>
       </c>
       <c r="C26" t="n">
-        <v>16735.9</v>
+        <v>16735.7</v>
       </c>
       <c r="D26" t="n">
         <v>24987.8</v>
       </c>
       <c r="E26" t="n">
-        <v>29164.1</v>
+        <v>29137.1</v>
       </c>
       <c r="F26" t="n">
         <v>3913.7</v>
@@ -3918,13 +3921,13 @@
         <v>8573.299999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>16957</v>
+        <v>16956.7</v>
       </c>
       <c r="J26" t="n">
         <v>173.1</v>
       </c>
       <c r="K26" t="n">
-        <v>212278.5</v>
+        <v>212248.8</v>
       </c>
     </row>
     <row r="27">
@@ -3932,16 +3935,16 @@
         <v>44958</v>
       </c>
       <c r="B27" t="n">
-        <v>109783.9</v>
+        <v>109781.7</v>
       </c>
       <c r="C27" t="n">
-        <v>16735.9</v>
+        <v>16735.7</v>
       </c>
       <c r="D27" t="n">
         <v>25175.8</v>
       </c>
       <c r="E27" t="n">
-        <v>30305.4</v>
+        <v>30256.9</v>
       </c>
       <c r="F27" t="n">
         <v>3913.7</v>
@@ -3953,13 +3956,13 @@
         <v>8629</v>
       </c>
       <c r="I27" t="n">
-        <v>16998.3</v>
+        <v>16998.1</v>
       </c>
       <c r="J27" t="n">
         <v>173.1</v>
       </c>
       <c r="K27" t="n">
-        <v>213705.1</v>
+        <v>213654</v>
       </c>
     </row>
     <row r="28">
@@ -3967,16 +3970,16 @@
         <v>44986</v>
       </c>
       <c r="B28" t="n">
-        <v>109805.6</v>
+        <v>109803.4</v>
       </c>
       <c r="C28" t="n">
-        <v>16735.9</v>
+        <v>16735.7</v>
       </c>
       <c r="D28" t="n">
         <v>25360</v>
       </c>
       <c r="E28" t="n">
-        <v>31664.8</v>
+        <v>31636.7</v>
       </c>
       <c r="F28" t="n">
         <v>3913.7</v>
@@ -3988,13 +3991,13 @@
         <v>8619.5</v>
       </c>
       <c r="I28" t="n">
-        <v>17002.4</v>
+        <v>17002.2</v>
       </c>
       <c r="J28" t="n">
         <v>173.1</v>
       </c>
       <c r="K28" t="n">
-        <v>215265</v>
+        <v>215234.3</v>
       </c>
     </row>
     <row r="29">
@@ -4002,16 +4005,16 @@
         <v>45017</v>
       </c>
       <c r="B29" t="n">
-        <v>109836</v>
+        <v>109833.8</v>
       </c>
       <c r="C29" t="n">
-        <v>16735.9</v>
+        <v>16735.7</v>
       </c>
       <c r="D29" t="n">
         <v>25617.6</v>
       </c>
       <c r="E29" t="n">
-        <v>32742</v>
+        <v>32713.2</v>
       </c>
       <c r="F29" t="n">
         <v>3913.7</v>
@@ -4023,13 +4026,13 @@
         <v>8608.5</v>
       </c>
       <c r="I29" t="n">
-        <v>17082.3</v>
+        <v>17082.1</v>
       </c>
       <c r="J29" t="n">
         <v>173.1</v>
       </c>
       <c r="K29" t="n">
-        <v>216699.2</v>
+        <v>216667.7</v>
       </c>
     </row>
     <row r="30">
@@ -4037,16 +4040,16 @@
         <v>45047</v>
       </c>
       <c r="B30" t="n">
-        <v>109837.3</v>
+        <v>109835.1</v>
       </c>
       <c r="C30" t="n">
-        <v>16838.7</v>
+        <v>16838.5</v>
       </c>
       <c r="D30" t="n">
         <v>25983.3</v>
       </c>
       <c r="E30" t="n">
-        <v>34422.5</v>
+        <v>34385</v>
       </c>
       <c r="F30" t="n">
         <v>3913.7</v>
@@ -4058,13 +4061,13 @@
         <v>8616</v>
       </c>
       <c r="I30" t="n">
-        <v>17086.4</v>
+        <v>17086.2</v>
       </c>
       <c r="J30" t="n">
         <v>173.1</v>
       </c>
       <c r="K30" t="n">
-        <v>218861</v>
+        <v>218820.9</v>
       </c>
     </row>
     <row r="31">
@@ -4072,16 +4075,16 @@
         <v>45078</v>
       </c>
       <c r="B31" t="n">
-        <v>109876.5</v>
+        <v>109874.4</v>
       </c>
       <c r="C31" t="n">
-        <v>16838.7</v>
+        <v>16838.5</v>
       </c>
       <c r="D31" t="n">
         <v>26235.2</v>
       </c>
       <c r="E31" t="n">
-        <v>35151.5</v>
+        <v>35113</v>
       </c>
       <c r="F31" t="n">
         <v>3913.7</v>
@@ -4093,13 +4096,13 @@
         <v>8612</v>
       </c>
       <c r="I31" t="n">
-        <v>17104.9</v>
+        <v>17104.7</v>
       </c>
       <c r="J31" t="n">
         <v>173.1</v>
       </c>
       <c r="K31" t="n">
-        <v>219895.7</v>
+        <v>219854.5</v>
       </c>
     </row>
     <row r="32">
@@ -4107,16 +4110,16 @@
         <v>45108</v>
       </c>
       <c r="B32" t="n">
-        <v>109882.7</v>
+        <v>109880.5</v>
       </c>
       <c r="C32" t="n">
-        <v>16838.7</v>
+        <v>16838.5</v>
       </c>
       <c r="D32" t="n">
         <v>26676.8</v>
       </c>
       <c r="E32" t="n">
-        <v>35749.5</v>
+        <v>35711.3</v>
       </c>
       <c r="F32" t="n">
         <v>3913.7</v>
@@ -4128,13 +4131,13 @@
         <v>8595.9</v>
       </c>
       <c r="I32" t="n">
-        <v>17110.7</v>
+        <v>17110.5</v>
       </c>
       <c r="J32" t="n">
         <v>173.1</v>
       </c>
       <c r="K32" t="n">
-        <v>220931.1</v>
+        <v>220890.3</v>
       </c>
     </row>
     <row r="33">
@@ -4142,16 +4145,16 @@
         <v>45139</v>
       </c>
       <c r="B33" t="n">
-        <v>109903.7</v>
+        <v>109901.5</v>
       </c>
       <c r="C33" t="n">
-        <v>16838.7</v>
+        <v>16838.5</v>
       </c>
       <c r="D33" t="n">
         <v>27023</v>
       </c>
       <c r="E33" t="n">
-        <v>37037.5</v>
+        <v>37010</v>
       </c>
       <c r="F33" t="n">
         <v>3913.7</v>
@@ -4163,13 +4166,13 @@
         <v>8586.6</v>
       </c>
       <c r="I33" t="n">
-        <v>17126.7</v>
+        <v>17126.5</v>
       </c>
       <c r="J33" t="n">
         <v>173.1</v>
       </c>
       <c r="K33" t="n">
-        <v>222593</v>
+        <v>222562.9</v>
       </c>
     </row>
     <row r="34">
@@ -4177,16 +4180,16 @@
         <v>45170</v>
       </c>
       <c r="B34" t="n">
-        <v>109905.2</v>
+        <v>109903</v>
       </c>
       <c r="C34" t="n">
-        <v>16838.7</v>
+        <v>16838.5</v>
       </c>
       <c r="D34" t="n">
         <v>27187.6</v>
       </c>
       <c r="E34" t="n">
-        <v>37574.7</v>
+        <v>37542.8</v>
       </c>
       <c r="F34" t="n">
         <v>3913.7</v>
@@ -4198,13 +4201,13 @@
         <v>8608.9</v>
       </c>
       <c r="I34" t="n">
-        <v>17167.8</v>
+        <v>17167.6</v>
       </c>
       <c r="J34" t="n">
         <v>173.1</v>
       </c>
       <c r="K34" t="n">
-        <v>223359.7</v>
+        <v>223325.2</v>
       </c>
     </row>
     <row r="35">
@@ -4212,16 +4215,16 @@
         <v>45200</v>
       </c>
       <c r="B35" t="n">
-        <v>109908.2</v>
+        <v>109906</v>
       </c>
       <c r="C35" t="n">
-        <v>16838.7</v>
+        <v>16838.5</v>
       </c>
       <c r="D35" t="n">
         <v>27696</v>
       </c>
       <c r="E35" t="n">
-        <v>38457.1</v>
+        <v>38425.7</v>
       </c>
       <c r="F35" t="n">
         <v>3913.7</v>
@@ -4233,13 +4236,13 @@
         <v>8601.1</v>
       </c>
       <c r="I35" t="n">
-        <v>17191.8</v>
+        <v>17191.5</v>
       </c>
       <c r="J35" t="n">
         <v>174.2</v>
       </c>
       <c r="K35" t="n">
-        <v>224770.8</v>
+        <v>224736.7</v>
       </c>
     </row>
     <row r="36">
@@ -4247,16 +4250,16 @@
         <v>45231</v>
       </c>
       <c r="B36" t="n">
-        <v>109921.2</v>
+        <v>109919</v>
       </c>
       <c r="C36" t="n">
-        <v>16838.7</v>
+        <v>16838.5</v>
       </c>
       <c r="D36" t="n">
         <v>27983.4</v>
       </c>
       <c r="E36" t="n">
-        <v>39436.6</v>
+        <v>39402.8</v>
       </c>
       <c r="F36" t="n">
         <v>3913.7</v>
@@ -4268,13 +4271,13 @@
         <v>8583.299999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>17195.3</v>
+        <v>17195.1</v>
       </c>
       <c r="J36" t="n">
         <v>174.2</v>
       </c>
       <c r="K36" t="n">
-        <v>226036.4</v>
+        <v>226000</v>
       </c>
     </row>
     <row r="37">
@@ -4282,16 +4285,16 @@
         <v>45261</v>
       </c>
       <c r="B37" t="n">
-        <v>109931.4</v>
+        <v>109929.2</v>
       </c>
       <c r="C37" t="n">
-        <v>17404.2</v>
+        <v>17404</v>
       </c>
       <c r="D37" t="n">
         <v>29040.3</v>
       </c>
       <c r="E37" t="n">
-        <v>40527.7</v>
+        <v>40492.9</v>
       </c>
       <c r="F37" t="n">
         <v>3913.7</v>
@@ -4303,13 +4306,13 @@
         <v>8495</v>
       </c>
       <c r="I37" t="n">
-        <v>17195.9</v>
+        <v>17195.7</v>
       </c>
       <c r="J37" t="n">
         <v>174.2</v>
       </c>
       <c r="K37" t="n">
-        <v>228672.4</v>
+        <v>228635</v>
       </c>
     </row>
     <row r="38">
@@ -4317,16 +4320,16 @@
         <v>45292</v>
       </c>
       <c r="B38" t="n">
-        <v>109932.1</v>
+        <v>109929.9</v>
       </c>
       <c r="C38" t="n">
-        <v>17404.2</v>
+        <v>17404</v>
       </c>
       <c r="D38" t="n">
         <v>29517.2</v>
       </c>
       <c r="E38" t="n">
-        <v>41538.2</v>
+        <v>41500</v>
       </c>
       <c r="F38" t="n">
         <v>3913.7</v>
@@ -4338,13 +4341,13 @@
         <v>8406.799999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>17196</v>
+        <v>17195.8</v>
       </c>
       <c r="J38" t="n">
         <v>174.2</v>
       </c>
       <c r="K38" t="n">
-        <v>230072.2</v>
+        <v>230031.4</v>
       </c>
     </row>
     <row r="39">
@@ -4352,16 +4355,16 @@
         <v>45323</v>
       </c>
       <c r="B39" t="n">
-        <v>109932.1</v>
+        <v>109929.9</v>
       </c>
       <c r="C39" t="n">
-        <v>17404.2</v>
+        <v>17404</v>
       </c>
       <c r="D39" t="n">
         <v>29893</v>
       </c>
       <c r="E39" t="n">
-        <v>42882.3</v>
+        <v>42844.1</v>
       </c>
       <c r="F39" t="n">
         <v>3913.7</v>
@@ -4373,13 +4376,13 @@
         <v>8318.5</v>
       </c>
       <c r="I39" t="n">
-        <v>17198.5</v>
+        <v>17198.3</v>
       </c>
       <c r="J39" t="n">
         <v>174.2</v>
       </c>
       <c r="K39" t="n">
-        <v>231706.5</v>
+        <v>231665.6</v>
       </c>
     </row>
     <row r="40">
@@ -4387,16 +4390,16 @@
         <v>45352</v>
       </c>
       <c r="B40" t="n">
-        <v>109951.8</v>
+        <v>109949.6</v>
       </c>
       <c r="C40" t="n">
-        <v>17404.2</v>
+        <v>17404</v>
       </c>
       <c r="D40" t="n">
         <v>30214.5</v>
       </c>
       <c r="E40" t="n">
-        <v>44300.4</v>
+        <v>44261.9</v>
       </c>
       <c r="F40" t="n">
         <v>3913.7</v>
@@ -4408,13 +4411,13 @@
         <v>8230.200000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>17199</v>
+        <v>17198.8</v>
       </c>
       <c r="J40" t="n">
         <v>174.2</v>
       </c>
       <c r="K40" t="n">
-        <v>233378</v>
+        <v>233337</v>
       </c>
     </row>
     <row r="41">
@@ -4422,16 +4425,16 @@
         <v>45383</v>
       </c>
       <c r="B41" t="n">
-        <v>109954.8</v>
+        <v>109952.6</v>
       </c>
       <c r="C41" t="n">
-        <v>17404.2</v>
+        <v>17404</v>
       </c>
       <c r="D41" t="n">
         <v>30680.2</v>
       </c>
       <c r="E41" t="n">
-        <v>45929</v>
+        <v>45890.7</v>
       </c>
       <c r="F41" t="n">
         <v>3913.7</v>
@@ -4443,13 +4446,13 @@
         <v>8141.9</v>
       </c>
       <c r="I41" t="n">
-        <v>17345.7</v>
+        <v>17345.5</v>
       </c>
       <c r="J41" t="n">
         <v>174.2</v>
       </c>
       <c r="K41" t="n">
-        <v>235533.8</v>
+        <v>235492.8</v>
       </c>
     </row>
     <row r="42">
@@ -4457,16 +4460,16 @@
         <v>45413</v>
       </c>
       <c r="B42" t="n">
-        <v>109954.8</v>
+        <v>109952.6</v>
       </c>
       <c r="C42" t="n">
-        <v>17404.2</v>
+        <v>17404</v>
       </c>
       <c r="D42" t="n">
         <v>30901.6</v>
       </c>
       <c r="E42" t="n">
-        <v>47193.3</v>
+        <v>47152.4</v>
       </c>
       <c r="F42" t="n">
         <v>3913.7</v>
@@ -4478,13 +4481,13 @@
         <v>8053.7</v>
       </c>
       <c r="I42" t="n">
-        <v>17346.2</v>
+        <v>17346</v>
       </c>
       <c r="J42" t="n">
         <v>174.2</v>
       </c>
       <c r="K42" t="n">
-        <v>236931.7</v>
+        <v>236888.2</v>
       </c>
     </row>
     <row r="43">
@@ -4492,16 +4495,16 @@
         <v>45444</v>
       </c>
       <c r="B43" t="n">
-        <v>109959.5</v>
+        <v>109957.3</v>
       </c>
       <c r="C43" t="n">
-        <v>17404.2</v>
+        <v>17404</v>
       </c>
       <c r="D43" t="n">
         <v>31128.3</v>
       </c>
       <c r="E43" t="n">
-        <v>48434.5</v>
+        <v>48402.8</v>
       </c>
       <c r="F43" t="n">
         <v>3913.7</v>
@@ -4513,13 +4516,13 @@
         <v>7995.4</v>
       </c>
       <c r="I43" t="n">
-        <v>17386.8</v>
+        <v>17386.5</v>
       </c>
       <c r="J43" t="n">
         <v>174.2</v>
       </c>
       <c r="K43" t="n">
-        <v>238386.5</v>
+        <v>238352.3</v>
       </c>
     </row>
     <row r="44">
@@ -4527,16 +4530,16 @@
         <v>45474</v>
       </c>
       <c r="B44" t="n">
-        <v>109959.5</v>
+        <v>109957.3</v>
       </c>
       <c r="C44" t="n">
-        <v>17404.2</v>
+        <v>17404</v>
       </c>
       <c r="D44" t="n">
         <v>31521.2</v>
       </c>
       <c r="E44" t="n">
-        <v>49962</v>
+        <v>49932.2</v>
       </c>
       <c r="F44" t="n">
         <v>3913.7</v>
@@ -4548,13 +4551,13 @@
         <v>7907.7</v>
       </c>
       <c r="I44" t="n">
-        <v>17388.1</v>
+        <v>17387.9</v>
       </c>
       <c r="J44" t="n">
         <v>174.2</v>
       </c>
       <c r="K44" t="n">
-        <v>240220.7</v>
+        <v>240188.2</v>
       </c>
     </row>
     <row r="45">
@@ -4562,16 +4565,16 @@
         <v>45505</v>
       </c>
       <c r="B45" t="n">
-        <v>109976.4</v>
+        <v>109974.2</v>
       </c>
       <c r="C45" t="n">
-        <v>17404.2</v>
+        <v>17404</v>
       </c>
       <c r="D45" t="n">
         <v>31848.5</v>
       </c>
       <c r="E45" t="n">
-        <v>51105.9</v>
+        <v>51080.8</v>
       </c>
       <c r="F45" t="n">
         <v>3913.7</v>
@@ -4583,13 +4586,13 @@
         <v>7819.4</v>
       </c>
       <c r="I45" t="n">
-        <v>17390.2</v>
+        <v>17390</v>
       </c>
       <c r="J45" t="n">
         <v>174.2</v>
       </c>
       <c r="K45" t="n">
-        <v>241622.6</v>
+        <v>241594.8</v>
       </c>
     </row>
     <row r="46">
@@ -4597,16 +4600,16 @@
         <v>45536</v>
       </c>
       <c r="B46" t="n">
-        <v>109976.4</v>
+        <v>109974.2</v>
       </c>
       <c r="C46" t="n">
-        <v>17404.2</v>
+        <v>17404</v>
       </c>
       <c r="D46" t="n">
         <v>32004.2</v>
       </c>
       <c r="E46" t="n">
-        <v>52435.1</v>
+        <v>52403.5</v>
       </c>
       <c r="F46" t="n">
         <v>3913.7</v>
@@ -4618,13 +4621,13 @@
         <v>7731.1</v>
       </c>
       <c r="I46" t="n">
-        <v>17460</v>
+        <v>17459.7</v>
       </c>
       <c r="J46" t="n">
         <v>174.2</v>
       </c>
       <c r="K46" t="n">
-        <v>243088.9</v>
+        <v>243054.7</v>
       </c>
     </row>
     <row r="47">
@@ -4632,16 +4635,16 @@
         <v>45566</v>
       </c>
       <c r="B47" t="n">
-        <v>109981.5</v>
+        <v>109979.3</v>
       </c>
       <c r="C47" t="n">
-        <v>17404.2</v>
+        <v>17404</v>
       </c>
       <c r="D47" t="n">
         <v>32495.6</v>
       </c>
       <c r="E47" t="n">
-        <v>53882.9</v>
+        <v>53853.7</v>
       </c>
       <c r="F47" t="n">
         <v>3913.7</v>
@@ -4653,13 +4656,13 @@
         <v>7932.7</v>
       </c>
       <c r="I47" t="n">
-        <v>17496.3</v>
+        <v>17496</v>
       </c>
       <c r="J47" t="n">
         <v>174.2</v>
       </c>
       <c r="K47" t="n">
-        <v>245271.1</v>
+        <v>245239.3</v>
       </c>
     </row>
     <row r="48">
@@ -4667,16 +4670,16 @@
         <v>45597</v>
       </c>
       <c r="B48" t="n">
-        <v>110010.3</v>
+        <v>110008.2</v>
       </c>
       <c r="C48" t="n">
-        <v>17404.2</v>
+        <v>17404</v>
       </c>
       <c r="D48" t="n">
         <v>32644.1</v>
       </c>
       <c r="E48" t="n">
-        <v>55468.7</v>
+        <v>55437.2</v>
       </c>
       <c r="F48" t="n">
         <v>3913.7</v>
@@ -4688,13 +4691,13 @@
         <v>7844.4</v>
       </c>
       <c r="I48" t="n">
-        <v>17496.3</v>
+        <v>17496</v>
       </c>
       <c r="J48" t="n">
         <v>174.3</v>
       </c>
       <c r="K48" t="n">
-        <v>246946</v>
+        <v>246911.9</v>
       </c>
     </row>
     <row r="49">
@@ -4702,16 +4705,16 @@
         <v>45627</v>
       </c>
       <c r="B49" t="n">
-        <v>110013.3</v>
+        <v>110011.2</v>
       </c>
       <c r="C49" t="n">
-        <v>17404.2</v>
+        <v>17404</v>
       </c>
       <c r="D49" t="n">
         <v>32893.1</v>
       </c>
       <c r="E49" t="n">
-        <v>56851</v>
+        <v>56820.3</v>
       </c>
       <c r="F49" t="n">
         <v>3913.7</v>
@@ -4723,13 +4726,13 @@
         <v>7852.2</v>
       </c>
       <c r="I49" t="n">
-        <v>17496.3</v>
+        <v>17496</v>
       </c>
       <c r="J49" t="n">
         <v>174.3</v>
       </c>
       <c r="K49" t="n">
-        <v>248588.1</v>
+        <v>248554.7</v>
       </c>
     </row>
     <row r="50">
@@ -4737,16 +4740,16 @@
         <v>45658</v>
       </c>
       <c r="B50" t="n">
-        <v>110013.3</v>
+        <v>110011.2</v>
       </c>
       <c r="C50" t="n">
-        <v>17404.2</v>
+        <v>17404</v>
       </c>
       <c r="D50" t="n">
         <v>33220.7</v>
       </c>
       <c r="E50" t="n">
-        <v>58424</v>
+        <v>58389.1</v>
       </c>
       <c r="F50" t="n">
         <v>3913.7</v>
@@ -4758,13 +4761,13 @@
         <v>7859.7</v>
       </c>
       <c r="I50" t="n">
-        <v>17881.9</v>
+        <v>17881.7</v>
       </c>
       <c r="J50" t="n">
         <v>174.3</v>
       </c>
       <c r="K50" t="n">
-        <v>250881.8</v>
+        <v>250844.3</v>
       </c>
     </row>
     <row r="51">
@@ -4772,16 +4775,16 @@
         <v>45689</v>
       </c>
       <c r="B51" t="n">
-        <v>110060.7</v>
+        <v>110058.5</v>
       </c>
       <c r="C51" t="n">
-        <v>17404.2</v>
+        <v>17404</v>
       </c>
       <c r="D51" t="n">
         <v>33410.6</v>
       </c>
       <c r="E51" t="n">
-        <v>59331.6</v>
+        <v>59299.1</v>
       </c>
       <c r="F51" t="n">
         <v>3913.7</v>
@@ -4793,13 +4796,13 @@
         <v>7865.8</v>
       </c>
       <c r="I51" t="n">
-        <v>17935.1</v>
+        <v>17934.8</v>
       </c>
       <c r="J51" t="n">
         <v>174.3</v>
       </c>
       <c r="K51" t="n">
-        <v>252085.9</v>
+        <v>252050.8</v>
       </c>
     </row>
     <row r="52">
@@ -4807,16 +4810,16 @@
         <v>45717</v>
       </c>
       <c r="B52" t="n">
-        <v>110092.3</v>
+        <v>110086.3</v>
       </c>
       <c r="C52" t="n">
-        <v>17404.2</v>
+        <v>17404</v>
       </c>
       <c r="D52" t="n">
         <v>33608.6</v>
       </c>
       <c r="E52" t="n">
-        <v>60254.8</v>
+        <v>60225.7</v>
       </c>
       <c r="F52" t="n">
         <v>3913.7</v>
@@ -4828,13 +4831,13 @@
         <v>7872</v>
       </c>
       <c r="I52" t="n">
-        <v>17966.3</v>
+        <v>17966.1</v>
       </c>
       <c r="J52" t="n">
-        <v>174.4</v>
+        <v>174.3</v>
       </c>
       <c r="K52" t="n">
-        <v>253276.3</v>
+        <v>253240.7</v>
       </c>
     </row>
     <row r="53">
@@ -4842,16 +4845,16 @@
         <v>45748</v>
       </c>
       <c r="B53" t="n">
-        <v>110103.7</v>
+        <v>110097.7</v>
       </c>
       <c r="C53" t="n">
-        <v>17404.2</v>
+        <v>17404</v>
       </c>
       <c r="D53" t="n">
         <v>33635.6</v>
       </c>
       <c r="E53" t="n">
-        <v>61199.6</v>
+        <v>61175</v>
       </c>
       <c r="F53" t="n">
         <v>3913.7</v>
@@ -4863,13 +4866,13 @@
         <v>7878.2</v>
       </c>
       <c r="I53" t="n">
-        <v>18011.6</v>
+        <v>18011.4</v>
       </c>
       <c r="J53" t="n">
-        <v>174.4</v>
+        <v>174.3</v>
       </c>
       <c r="K53" t="n">
-        <v>254310.9</v>
+        <v>254279.8</v>
       </c>
     </row>
     <row r="54">
@@ -4877,16 +4880,16 @@
         <v>45778</v>
       </c>
       <c r="B54" t="n">
-        <v>110108.2</v>
+        <v>110102.2</v>
       </c>
       <c r="C54" t="n">
-        <v>19076.8</v>
+        <v>19076.6</v>
       </c>
       <c r="D54" t="n">
         <v>33635.6</v>
       </c>
       <c r="E54" t="n">
-        <v>62003</v>
+        <v>61980.7</v>
       </c>
       <c r="F54" t="n">
         <v>3913.7</v>
@@ -4898,13 +4901,13 @@
         <v>7884.4</v>
       </c>
       <c r="I54" t="n">
-        <v>18059.6</v>
+        <v>18059.4</v>
       </c>
       <c r="J54" t="n">
-        <v>174.4</v>
+        <v>174.3</v>
       </c>
       <c r="K54" t="n">
-        <v>256845.7</v>
+        <v>256816.9</v>
       </c>
     </row>
     <row r="55">
@@ -4912,16 +4915,16 @@
         <v>45809</v>
       </c>
       <c r="B55" t="n">
-        <v>110112.2</v>
+        <v>110106.2</v>
       </c>
       <c r="C55" t="n">
-        <v>19076.8</v>
+        <v>19076.6</v>
       </c>
       <c r="D55" t="n">
         <v>33847.1</v>
       </c>
       <c r="E55" t="n">
-        <v>62788</v>
+        <v>62765.8</v>
       </c>
       <c r="F55" t="n">
         <v>3913.7</v>
@@ -4933,13 +4936,13 @@
         <v>7890.5</v>
       </c>
       <c r="I55" t="n">
-        <v>18061.8</v>
+        <v>18061.6</v>
       </c>
       <c r="J55" t="n">
-        <v>174.4</v>
+        <v>174.3</v>
       </c>
       <c r="K55" t="n">
-        <v>257854.6</v>
+        <v>257825.9</v>
       </c>
     </row>
     <row r="56">
@@ -4947,16 +4950,16 @@
         <v>45839</v>
       </c>
       <c r="B56" t="n">
-        <v>110112.2</v>
+        <v>110106.2</v>
       </c>
       <c r="C56" t="n">
-        <v>19076.8</v>
+        <v>19076.6</v>
       </c>
       <c r="D56" t="n">
         <v>33887.6</v>
       </c>
       <c r="E56" t="n">
-        <v>63655.4</v>
+        <v>63636.3</v>
       </c>
       <c r="F56" t="n">
         <v>3913.7</v>
@@ -4968,13 +4971,13 @@
         <v>7896.7</v>
       </c>
       <c r="I56" t="n">
-        <v>18064.6</v>
+        <v>18064.4</v>
       </c>
       <c r="J56" t="n">
         <v>174.4</v>
       </c>
       <c r="K56" t="n">
-        <v>258771.4</v>
+        <v>258745.8</v>
       </c>
     </row>
     <row r="57">
@@ -4982,16 +4985,16 @@
         <v>45870</v>
       </c>
       <c r="B57" t="n">
-        <v>110166.2</v>
+        <v>110160.2</v>
       </c>
       <c r="C57" t="n">
-        <v>19076.8</v>
+        <v>19076.6</v>
       </c>
       <c r="D57" t="n">
-        <v>34103.7</v>
+        <v>34103.6</v>
       </c>
       <c r="E57" t="n">
-        <v>64381.1</v>
+        <v>64374.7</v>
       </c>
       <c r="F57" t="n">
         <v>3913.7</v>
@@ -5003,13 +5006,13 @@
         <v>7902.9</v>
       </c>
       <c r="I57" t="n">
-        <v>18104.6</v>
+        <v>18104.4</v>
       </c>
       <c r="J57" t="n">
-        <v>174.5</v>
+        <v>174.4</v>
       </c>
       <c r="K57" t="n">
-        <v>259813.4</v>
+        <v>259800.5</v>
       </c>
     </row>
     <row r="58">
@@ -5017,16 +5020,16 @@
         <v>45901</v>
       </c>
       <c r="B58" t="n">
-        <v>110240.5</v>
+        <v>110234.2</v>
       </c>
       <c r="C58" t="n">
-        <v>19076.8</v>
+        <v>19076.6</v>
       </c>
       <c r="D58" t="n">
-        <v>34418.7</v>
+        <v>34418.6</v>
       </c>
       <c r="E58" t="n">
-        <v>65989</v>
+        <v>65965.8</v>
       </c>
       <c r="F58" t="n">
         <v>3913.7</v>
@@ -5038,13 +5041,13 @@
         <v>7909.1</v>
       </c>
       <c r="I58" t="n">
-        <v>18106.7</v>
+        <v>18106.5</v>
       </c>
       <c r="J58" t="n">
         <v>174.6</v>
       </c>
       <c r="K58" t="n">
-        <v>261819</v>
+        <v>261789.1</v>
       </c>
     </row>
     <row r="59">
@@ -5052,16 +5055,16 @@
         <v>45931</v>
       </c>
       <c r="B59" t="n">
-        <v>110273.4</v>
+        <v>110266.7</v>
       </c>
       <c r="C59" t="n">
-        <v>19076.8</v>
+        <v>19076.6</v>
       </c>
       <c r="D59" t="n">
-        <v>34418.7</v>
+        <v>34418.6</v>
       </c>
       <c r="E59" t="n">
-        <v>67355.10000000001</v>
+        <v>67333.7</v>
       </c>
       <c r="F59" t="n">
         <v>3913.7</v>
@@ -5073,13 +5076,13 @@
         <v>7915.2</v>
       </c>
       <c r="I59" t="n">
-        <v>18136.5</v>
+        <v>18136.3</v>
       </c>
       <c r="J59" t="n">
         <v>174.9</v>
       </c>
       <c r="K59" t="n">
-        <v>263254.2</v>
+        <v>263225.7</v>
       </c>
     </row>
     <row r="60">
@@ -5087,16 +5090,16 @@
         <v>45962</v>
       </c>
       <c r="B60" t="n">
-        <v>110273.4</v>
+        <v>110266.7</v>
       </c>
       <c r="C60" t="n">
-        <v>19076.8</v>
+        <v>19076.6</v>
       </c>
       <c r="D60" t="n">
-        <v>34418.7</v>
+        <v>34418.6</v>
       </c>
       <c r="E60" t="n">
-        <v>68263.10000000001</v>
+        <v>68239.10000000001</v>
       </c>
       <c r="F60" t="n">
         <v>3913.7</v>
@@ -5108,13 +5111,13 @@
         <v>7921.4</v>
       </c>
       <c r="I60" t="n">
-        <v>18136.5</v>
+        <v>18136.3</v>
       </c>
       <c r="J60" t="n">
         <v>175.2</v>
       </c>
       <c r="K60" t="n">
-        <v>264168.8</v>
+        <v>264137.6</v>
       </c>
     </row>
     <row r="61">
@@ -5122,16 +5125,16 @@
         <v>45992</v>
       </c>
       <c r="B61" t="n">
-        <v>110273.4</v>
+        <v>110266.7</v>
       </c>
       <c r="C61" t="n">
-        <v>19076.8</v>
+        <v>19076.6</v>
       </c>
       <c r="D61" t="n">
-        <v>34769.7</v>
+        <v>34769.6</v>
       </c>
       <c r="E61" t="n">
-        <v>69309.5</v>
+        <v>69292.2</v>
       </c>
       <c r="F61" t="n">
         <v>3913.7</v>
@@ -5143,13 +5146,13 @@
         <v>7927.6</v>
       </c>
       <c r="I61" t="n">
-        <v>18145</v>
+        <v>18144.7</v>
       </c>
       <c r="J61" t="n">
         <v>175.4</v>
       </c>
       <c r="K61" t="n">
-        <v>265581</v>
+        <v>265556.5</v>
       </c>
     </row>
     <row r="62">
@@ -5157,16 +5160,16 @@
         <v>46023</v>
       </c>
       <c r="B62" t="n">
-        <v>110294.6</v>
+        <v>110287.9</v>
       </c>
       <c r="C62" t="n">
-        <v>19076.8</v>
+        <v>19076.6</v>
       </c>
       <c r="D62" t="n">
-        <v>34769.7</v>
+        <v>34769.6</v>
       </c>
       <c r="E62" t="n">
-        <v>70557.3</v>
+        <v>70532.5</v>
       </c>
       <c r="F62" t="n">
         <v>3913.7</v>
@@ -5178,13 +5181,13 @@
         <v>7888.3</v>
       </c>
       <c r="I62" t="n">
-        <v>18145.1</v>
+        <v>18144.9</v>
       </c>
       <c r="J62" t="n">
-        <v>175.7</v>
+        <v>175.6</v>
       </c>
       <c r="K62" t="n">
-        <v>266811.1</v>
+        <v>266779.1</v>
       </c>
     </row>
     <row r="63">
@@ -5192,16 +5195,16 @@
         <v>46054</v>
       </c>
       <c r="B63" t="n">
-        <v>110294.6</v>
+        <v>110287.9</v>
       </c>
       <c r="C63" t="n">
-        <v>19076.8</v>
+        <v>19076.6</v>
       </c>
       <c r="D63" t="n">
         <v>34828.2</v>
       </c>
       <c r="E63" t="n">
-        <v>71902.8</v>
+        <v>71877</v>
       </c>
       <c r="F63" t="n">
         <v>3913.7</v>
@@ -5213,13 +5216,13 @@
         <v>7848.9</v>
       </c>
       <c r="I63" t="n">
-        <v>18145.1</v>
+        <v>18144.9</v>
       </c>
       <c r="J63" t="n">
-        <v>175.8</v>
+        <v>175.7</v>
       </c>
       <c r="K63" t="n">
-        <v>268175.8</v>
+        <v>268143</v>
       </c>
     </row>
     <row r="64">
@@ -5227,16 +5230,16 @@
         <v>46082</v>
       </c>
       <c r="B64" t="n">
-        <v>110299.8</v>
+        <v>110293.1</v>
       </c>
       <c r="C64" t="n">
-        <v>19076.8</v>
+        <v>19076.6</v>
       </c>
       <c r="D64" t="n">
         <v>34828.2</v>
       </c>
       <c r="E64" t="n">
-        <v>73735.10000000001</v>
+        <v>73711.89999999999</v>
       </c>
       <c r="F64" t="n">
         <v>3913.7</v>
@@ -5248,13 +5251,13 @@
         <v>7810.7</v>
       </c>
       <c r="I64" t="n">
-        <v>18171.5</v>
+        <v>18171.3</v>
       </c>
       <c r="J64" t="n">
         <v>175.9</v>
       </c>
       <c r="K64" t="n">
-        <v>270001.7</v>
+        <v>269971.3</v>
       </c>
     </row>
     <row r="65">
@@ -5262,16 +5265,16 @@
         <v>46113</v>
       </c>
       <c r="B65" t="n">
-        <v>110299.9</v>
+        <v>110293.2</v>
       </c>
       <c r="C65" t="n">
-        <v>19076.8</v>
+        <v>19076.6</v>
       </c>
       <c r="D65" t="n">
         <v>34828.2</v>
       </c>
       <c r="E65" t="n">
-        <v>74608.5</v>
+        <v>74589.8</v>
       </c>
       <c r="F65" t="n">
         <v>3913.7</v>
@@ -5283,13 +5286,13 @@
         <v>7771.4</v>
       </c>
       <c r="I65" t="n">
-        <v>18211.5</v>
+        <v>18211.3</v>
       </c>
       <c r="J65" t="n">
         <v>179.4</v>
       </c>
       <c r="K65" t="n">
-        <v>270879.3</v>
+        <v>270853.5</v>
       </c>
     </row>
     <row r="66">
@@ -5297,16 +5300,16 @@
         <v>46143</v>
       </c>
       <c r="B66" t="n">
-        <v>110304.3</v>
+        <v>110297.6</v>
       </c>
       <c r="C66" t="n">
-        <v>19076.8</v>
+        <v>19076.6</v>
       </c>
       <c r="D66" t="n">
         <v>34828.2</v>
       </c>
       <c r="E66" t="n">
-        <v>75305.2</v>
+        <v>75369.7</v>
       </c>
       <c r="F66" t="n">
         <v>3913.7</v>
@@ -5318,13 +5321,13 @@
         <v>7732</v>
       </c>
       <c r="I66" t="n">
-        <v>18211.5</v>
+        <v>18211.3</v>
       </c>
       <c r="J66" t="n">
-        <v>180.1</v>
+        <v>180</v>
       </c>
       <c r="K66" t="n">
-        <v>271541.7</v>
+        <v>271599</v>
       </c>
     </row>
     <row r="67">
@@ -5332,16 +5335,16 @@
         <v>46174</v>
       </c>
       <c r="B67" t="n">
-        <v>110327</v>
+        <v>110320.3</v>
       </c>
       <c r="C67" t="n">
-        <v>19076.8</v>
+        <v>19076.6</v>
       </c>
       <c r="D67" t="n">
         <v>34828.2</v>
       </c>
       <c r="E67" t="n">
-        <v>75991.39999999999</v>
+        <v>76090.8</v>
       </c>
       <c r="F67" t="n">
         <v>3913.7</v>
@@ -5353,13 +5356,13 @@
         <v>7692.7</v>
       </c>
       <c r="I67" t="n">
-        <v>18211.5</v>
+        <v>18211.3</v>
       </c>
       <c r="J67" t="n">
         <v>180.5</v>
       </c>
       <c r="K67" t="n">
-        <v>272211.7</v>
+        <v>272304</v>
       </c>
     </row>
     <row r="68">
@@ -5367,16 +5370,16 @@
         <v>46204</v>
       </c>
       <c r="B68" t="n">
-        <v>110334</v>
+        <v>110327.3</v>
       </c>
       <c r="C68" t="n">
-        <v>19076.8</v>
+        <v>19076.6</v>
       </c>
       <c r="D68" t="n">
         <v>34891.2</v>
       </c>
       <c r="E68" t="n">
-        <v>76351.5</v>
+        <v>76476.8</v>
       </c>
       <c r="F68" t="n">
         <v>3913.7</v>
@@ -5388,13 +5391,13 @@
         <v>7653.4</v>
       </c>
       <c r="I68" t="n">
-        <v>18215.7</v>
+        <v>18215.5</v>
       </c>
       <c r="J68" t="n">
         <v>180.5</v>
       </c>
       <c r="K68" t="n">
-        <v>272606.7</v>
+        <v>272724.9</v>
       </c>
     </row>
     <row r="69">
@@ -5402,16 +5405,16 @@
         <v>46235</v>
       </c>
       <c r="B69" t="n">
-        <v>110334</v>
+        <v>110327.3</v>
       </c>
       <c r="C69" t="n">
-        <v>20067.7</v>
+        <v>20067.5</v>
       </c>
       <c r="D69" t="n">
         <v>34954.2</v>
       </c>
       <c r="E69" t="n">
-        <v>77266.2</v>
+        <v>77405</v>
       </c>
       <c r="F69" t="n">
         <v>3913.7</v>
@@ -5423,13 +5426,13 @@
         <v>7619</v>
       </c>
       <c r="I69" t="n">
-        <v>18225.7</v>
+        <v>18225.5</v>
       </c>
       <c r="J69" t="n">
         <v>180.5</v>
       </c>
       <c r="K69" t="n">
-        <v>274550.9</v>
+        <v>274682.6</v>
       </c>
     </row>
     <row r="70">
@@ -5437,16 +5440,16 @@
         <v>46266</v>
       </c>
       <c r="B70" t="n">
-        <v>110334</v>
+        <v>110327.3</v>
       </c>
       <c r="C70" t="n">
-        <v>20182.5</v>
+        <v>20182.3</v>
       </c>
       <c r="D70" t="n">
         <v>34954.2</v>
       </c>
       <c r="E70" t="n">
-        <v>77266.2</v>
+        <v>77405</v>
       </c>
       <c r="F70" t="n">
         <v>3913.7</v>
@@ -5458,13 +5461,13 @@
         <v>7579.6</v>
       </c>
       <c r="I70" t="n">
-        <v>18250.7</v>
+        <v>18250.5</v>
       </c>
       <c r="J70" t="n">
         <v>180.5</v>
       </c>
       <c r="K70" t="n">
-        <v>274651.4</v>
+        <v>274783</v>
       </c>
     </row>
   </sheetData>
@@ -5568,7 +5571,7 @@
         <v>44197</v>
       </c>
       <c r="B2" t="n">
-        <v>90.09999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="C2" t="n">
         <v>15318.5</v>
@@ -5577,13 +5580,13 @@
         <v>3913.7</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F2" t="n">
         <v>13979.5</v>
       </c>
       <c r="G2" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="H2" t="n">
         <v>109247.4</v>
@@ -5601,7 +5604,7 @@
         <v>166</v>
       </c>
       <c r="M2" t="n">
-        <v>6110.8</v>
+        <v>6078.1</v>
       </c>
       <c r="N2" t="n">
         <v>3352.4</v>
@@ -5618,7 +5621,7 @@
         <v>44228</v>
       </c>
       <c r="B3" t="n">
-        <v>93.2</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="C3" t="n">
         <v>15332.7</v>
@@ -5627,13 +5630,13 @@
         <v>3913.7</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F3" t="n">
         <v>13979.5</v>
       </c>
       <c r="G3" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="H3" t="n">
         <v>109257.3</v>
@@ -5651,7 +5654,7 @@
         <v>166</v>
       </c>
       <c r="M3" t="n">
-        <v>6428.5</v>
+        <v>6386.3</v>
       </c>
       <c r="N3" t="n">
         <v>3357.5</v>
@@ -5668,7 +5671,7 @@
         <v>44256</v>
       </c>
       <c r="B4" t="n">
-        <v>93.8</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="C4" t="n">
         <v>15341.3</v>
@@ -5677,13 +5680,13 @@
         <v>3913.7</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F4" t="n">
         <v>13979.5</v>
       </c>
       <c r="G4" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="H4" t="n">
         <v>109263.7</v>
@@ -5701,7 +5704,7 @@
         <v>166</v>
       </c>
       <c r="M4" t="n">
-        <v>6916.2</v>
+        <v>6865.8</v>
       </c>
       <c r="N4" t="n">
         <v>3361.8</v>
@@ -5718,7 +5721,7 @@
         <v>44287</v>
       </c>
       <c r="B5" t="n">
-        <v>94.5</v>
+        <v>94.3</v>
       </c>
       <c r="C5" t="n">
         <v>15396</v>
@@ -5727,13 +5730,13 @@
         <v>3913.7</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F5" t="n">
         <v>13979.5</v>
       </c>
       <c r="G5" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="H5" t="n">
         <v>109263.7</v>
@@ -5751,7 +5754,7 @@
         <v>166</v>
       </c>
       <c r="M5" t="n">
-        <v>7284.2</v>
+        <v>7230.9</v>
       </c>
       <c r="N5" t="n">
         <v>3366.4</v>
@@ -5768,7 +5771,7 @@
         <v>44317</v>
       </c>
       <c r="B6" t="n">
-        <v>96.59999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="C6" t="n">
         <v>15419</v>
@@ -5777,13 +5780,13 @@
         <v>3913.7</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F6" t="n">
         <v>13979.5</v>
       </c>
       <c r="G6" t="n">
-        <v>45.8</v>
+        <v>45.2</v>
       </c>
       <c r="H6" t="n">
         <v>109269.2</v>
@@ -5801,7 +5804,7 @@
         <v>166</v>
       </c>
       <c r="M6" t="n">
-        <v>7715.6</v>
+        <v>7657.4</v>
       </c>
       <c r="N6" t="n">
         <v>3369.8</v>
@@ -5818,7 +5821,7 @@
         <v>44348</v>
       </c>
       <c r="B7" t="n">
-        <v>104.5</v>
+        <v>104.3</v>
       </c>
       <c r="C7" t="n">
         <v>15455</v>
@@ -5827,13 +5830,13 @@
         <v>3913.7</v>
       </c>
       <c r="E7" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F7" t="n">
         <v>13979.5</v>
       </c>
       <c r="G7" t="n">
-        <v>45.8</v>
+        <v>45.2</v>
       </c>
       <c r="H7" t="n">
         <v>109302.3</v>
@@ -5851,7 +5854,7 @@
         <v>166</v>
       </c>
       <c r="M7" t="n">
-        <v>8126.8</v>
+        <v>8060.3</v>
       </c>
       <c r="N7" t="n">
         <v>3436.1</v>
@@ -5868,7 +5871,7 @@
         <v>44378</v>
       </c>
       <c r="B8" t="n">
-        <v>105.2</v>
+        <v>104.9</v>
       </c>
       <c r="C8" t="n">
         <v>15455</v>
@@ -5877,13 +5880,13 @@
         <v>3913.7</v>
       </c>
       <c r="E8" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F8" t="n">
         <v>14156.6</v>
       </c>
       <c r="G8" t="n">
-        <v>45.8</v>
+        <v>45.2</v>
       </c>
       <c r="H8" t="n">
         <v>109302.3</v>
@@ -5901,7 +5904,7 @@
         <v>166</v>
       </c>
       <c r="M8" t="n">
-        <v>8582.5</v>
+        <v>8508.9</v>
       </c>
       <c r="N8" t="n">
         <v>3499.9</v>
@@ -5918,7 +5921,7 @@
         <v>44409</v>
       </c>
       <c r="B9" t="n">
-        <v>105.8</v>
+        <v>105.5</v>
       </c>
       <c r="C9" t="n">
         <v>15505</v>
@@ -5927,13 +5930,13 @@
         <v>3913.7</v>
       </c>
       <c r="E9" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F9" t="n">
         <v>14156.6</v>
       </c>
       <c r="G9" t="n">
-        <v>47</v>
+        <v>46.4</v>
       </c>
       <c r="H9" t="n">
         <v>109315.8</v>
@@ -5951,7 +5954,7 @@
         <v>166</v>
       </c>
       <c r="M9" t="n">
-        <v>9075.4</v>
+        <v>9014.4</v>
       </c>
       <c r="N9" t="n">
         <v>3816.3</v>
@@ -5968,7 +5971,7 @@
         <v>44440</v>
       </c>
       <c r="B10" t="n">
-        <v>107.4</v>
+        <v>107.2</v>
       </c>
       <c r="C10" t="n">
         <v>15506.4</v>
@@ -5977,13 +5980,13 @@
         <v>3913.7</v>
       </c>
       <c r="E10" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F10" t="n">
         <v>15494.9</v>
       </c>
       <c r="G10" t="n">
-        <v>47</v>
+        <v>46.4</v>
       </c>
       <c r="H10" t="n">
         <v>109317.5</v>
@@ -6001,7 +6004,7 @@
         <v>166</v>
       </c>
       <c r="M10" t="n">
-        <v>9549</v>
+        <v>9479.200000000001</v>
       </c>
       <c r="N10" t="n">
         <v>3918.8</v>
@@ -6018,7 +6021,7 @@
         <v>44470</v>
       </c>
       <c r="B11" t="n">
-        <v>107.6</v>
+        <v>107.3</v>
       </c>
       <c r="C11" t="n">
         <v>15538.9</v>
@@ -6027,13 +6030,13 @@
         <v>3913.7</v>
       </c>
       <c r="E11" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F11" t="n">
         <v>15524.4</v>
       </c>
       <c r="G11" t="n">
-        <v>49.4</v>
+        <v>48.8</v>
       </c>
       <c r="H11" t="n">
         <v>109317.6</v>
@@ -6051,7 +6054,7 @@
         <v>166</v>
       </c>
       <c r="M11" t="n">
-        <v>10039.3</v>
+        <v>9970.299999999999</v>
       </c>
       <c r="N11" t="n">
         <v>4543</v>
@@ -6068,7 +6071,7 @@
         <v>44501</v>
       </c>
       <c r="B12" t="n">
-        <v>108.3</v>
+        <v>108</v>
       </c>
       <c r="C12" t="n">
         <v>15552.2</v>
@@ -6077,13 +6080,13 @@
         <v>3913.7</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F12" t="n">
         <v>15524.4</v>
       </c>
       <c r="G12" t="n">
-        <v>51</v>
+        <v>50.4</v>
       </c>
       <c r="H12" t="n">
         <v>109325.6</v>
@@ -6101,7 +6104,7 @@
         <v>166</v>
       </c>
       <c r="M12" t="n">
-        <v>10659.1</v>
+        <v>10579.8</v>
       </c>
       <c r="N12" t="n">
         <v>4647</v>
@@ -6118,7 +6121,7 @@
         <v>44531</v>
       </c>
       <c r="B13" t="n">
-        <v>115.8</v>
+        <v>115.6</v>
       </c>
       <c r="C13" t="n">
         <v>15963.5</v>
@@ -6127,13 +6130,13 @@
         <v>3913.7</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F13" t="n">
         <v>15524.4</v>
       </c>
       <c r="G13" t="n">
-        <v>51</v>
+        <v>50.4</v>
       </c>
       <c r="H13" t="n">
         <v>109353.5</v>
@@ -6151,7 +6154,7 @@
         <v>166</v>
       </c>
       <c r="M13" t="n">
-        <v>11410.1</v>
+        <v>11320.5</v>
       </c>
       <c r="N13" t="n">
         <v>4700.3</v>
@@ -6168,7 +6171,7 @@
         <v>44562</v>
       </c>
       <c r="B14" t="n">
-        <v>116.5</v>
+        <v>116.3</v>
       </c>
       <c r="C14" t="n">
         <v>16100.8</v>
@@ -6177,13 +6180,13 @@
         <v>3913.7</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F14" t="n">
         <v>15524.4</v>
       </c>
       <c r="G14" t="n">
-        <v>51</v>
+        <v>50.4</v>
       </c>
       <c r="H14" t="n">
         <v>109354.2</v>
@@ -6201,7 +6204,7 @@
         <v>166</v>
       </c>
       <c r="M14" t="n">
-        <v>11887.5</v>
+        <v>11802.2</v>
       </c>
       <c r="N14" t="n">
         <v>4706.5</v>
@@ -6218,7 +6221,7 @@
         <v>44593</v>
       </c>
       <c r="B15" t="n">
-        <v>117</v>
+        <v>116.7</v>
       </c>
       <c r="C15" t="n">
         <v>16101.8</v>
@@ -6227,13 +6230,13 @@
         <v>3913.7</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F15" t="n">
         <v>15650.7</v>
       </c>
       <c r="G15" t="n">
-        <v>51</v>
+        <v>50.4</v>
       </c>
       <c r="H15" t="n">
         <v>109374.2</v>
@@ -6251,7 +6254,7 @@
         <v>166</v>
       </c>
       <c r="M15" t="n">
-        <v>12455.9</v>
+        <v>12365.1</v>
       </c>
       <c r="N15" t="n">
         <v>4811.7</v>
@@ -6268,7 +6271,7 @@
         <v>44621</v>
       </c>
       <c r="B16" t="n">
-        <v>128.9</v>
+        <v>128.7</v>
       </c>
       <c r="C16" t="n">
         <v>16166.5</v>
@@ -6277,13 +6280,13 @@
         <v>3913.7</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F16" t="n">
         <v>15650.7</v>
       </c>
       <c r="G16" t="n">
-        <v>52.1</v>
+        <v>50.5</v>
       </c>
       <c r="H16" t="n">
         <v>109421.3</v>
@@ -6301,7 +6304,7 @@
         <v>166</v>
       </c>
       <c r="M16" t="n">
-        <v>13149.8</v>
+        <v>13065.1</v>
       </c>
       <c r="N16" t="n">
         <v>4948.8</v>
@@ -6318,7 +6321,7 @@
         <v>44652</v>
       </c>
       <c r="B17" t="n">
-        <v>132</v>
+        <v>131.8</v>
       </c>
       <c r="C17" t="n">
         <v>16201</v>
@@ -6327,13 +6330,13 @@
         <v>3913.7</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F17" t="n">
         <v>15650.7</v>
       </c>
       <c r="G17" t="n">
-        <v>53.1</v>
+        <v>51.5</v>
       </c>
       <c r="H17" t="n">
         <v>109421.3</v>
@@ -6351,7 +6354,7 @@
         <v>166</v>
       </c>
       <c r="M17" t="n">
-        <v>13777.5</v>
+        <v>13698.1</v>
       </c>
       <c r="N17" t="n">
         <v>5105.4</v>
@@ -6368,7 +6371,7 @@
         <v>44682</v>
       </c>
       <c r="B18" t="n">
-        <v>133.1</v>
+        <v>132.8</v>
       </c>
       <c r="C18" t="n">
         <v>16552.7</v>
@@ -6377,13 +6380,13 @@
         <v>3913.7</v>
       </c>
       <c r="E18" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F18" t="n">
         <v>15650.7</v>
       </c>
       <c r="G18" t="n">
-        <v>53.1</v>
+        <v>51.5</v>
       </c>
       <c r="H18" t="n">
         <v>109450.8</v>
@@ -6401,7 +6404,7 @@
         <v>166</v>
       </c>
       <c r="M18" t="n">
-        <v>14486.7</v>
+        <v>14386.1</v>
       </c>
       <c r="N18" t="n">
         <v>5278.3</v>
@@ -6418,7 +6421,7 @@
         <v>44713</v>
       </c>
       <c r="B19" t="n">
-        <v>138.2</v>
+        <v>137.9</v>
       </c>
       <c r="C19" t="n">
         <v>16571.2</v>
@@ -6427,13 +6430,13 @@
         <v>3913.7</v>
       </c>
       <c r="E19" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F19" t="n">
         <v>15674.4</v>
       </c>
       <c r="G19" t="n">
-        <v>53.1</v>
+        <v>51.5</v>
       </c>
       <c r="H19" t="n">
         <v>109452</v>
@@ -6451,7 +6454,7 @@
         <v>166</v>
       </c>
       <c r="M19" t="n">
-        <v>15207.4</v>
+        <v>15101.4</v>
       </c>
       <c r="N19" t="n">
         <v>5397.8</v>
@@ -6468,7 +6471,7 @@
         <v>44743</v>
       </c>
       <c r="B20" t="n">
-        <v>142.8</v>
+        <v>142.6</v>
       </c>
       <c r="C20" t="n">
         <v>16577.9</v>
@@ -6477,13 +6480,13 @@
         <v>3913.7</v>
       </c>
       <c r="E20" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F20" t="n">
         <v>15787</v>
       </c>
       <c r="G20" t="n">
-        <v>53.1</v>
+        <v>51.5</v>
       </c>
       <c r="H20" t="n">
         <v>109595.9</v>
@@ -6501,7 +6504,7 @@
         <v>166</v>
       </c>
       <c r="M20" t="n">
-        <v>15976.7</v>
+        <v>15858.8</v>
       </c>
       <c r="N20" t="n">
         <v>5757</v>
@@ -6518,7 +6521,7 @@
         <v>44774</v>
       </c>
       <c r="B21" t="n">
-        <v>144</v>
+        <v>143.8</v>
       </c>
       <c r="C21" t="n">
         <v>16577.9</v>
@@ -6527,13 +6530,13 @@
         <v>3913.7</v>
       </c>
       <c r="E21" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F21" t="n">
         <v>15799.3</v>
       </c>
       <c r="G21" t="n">
-        <v>54.6</v>
+        <v>53</v>
       </c>
       <c r="H21" t="n">
         <v>109595.9</v>
@@ -6551,13 +6554,13 @@
         <v>166</v>
       </c>
       <c r="M21" t="n">
-        <v>16766.1</v>
+        <v>16632.6</v>
       </c>
       <c r="N21" t="n">
         <v>6107.1</v>
       </c>
       <c r="O21" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="P21" t="n">
         <v>22408</v>
@@ -6568,7 +6571,7 @@
         <v>44805</v>
       </c>
       <c r="B22" t="n">
-        <v>144.2</v>
+        <v>144</v>
       </c>
       <c r="C22" t="n">
         <v>16769.1</v>
@@ -6577,13 +6580,13 @@
         <v>3913.7</v>
       </c>
       <c r="E22" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F22" t="n">
         <v>16031.1</v>
       </c>
       <c r="G22" t="n">
-        <v>56.6</v>
+        <v>55</v>
       </c>
       <c r="H22" t="n">
         <v>109626.1</v>
@@ -6601,7 +6604,7 @@
         <v>166</v>
       </c>
       <c r="M22" t="n">
-        <v>17551.7</v>
+        <v>17407.3</v>
       </c>
       <c r="N22" t="n">
         <v>6657.8</v>
@@ -6618,7 +6621,7 @@
         <v>44835</v>
       </c>
       <c r="B23" t="n">
-        <v>144.7</v>
+        <v>144.5</v>
       </c>
       <c r="C23" t="n">
         <v>16769.1</v>
@@ -6627,13 +6630,13 @@
         <v>3913.7</v>
       </c>
       <c r="E23" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F23" t="n">
         <v>16368.1</v>
       </c>
       <c r="G23" t="n">
-        <v>57.3</v>
+        <v>55.1</v>
       </c>
       <c r="H23" t="n">
         <v>109635.6</v>
@@ -6651,7 +6654,7 @@
         <v>166</v>
       </c>
       <c r="M23" t="n">
-        <v>18267.9</v>
+        <v>18215.4</v>
       </c>
       <c r="N23" t="n">
         <v>6918.1</v>
@@ -6668,7 +6671,7 @@
         <v>44866</v>
       </c>
       <c r="B24" t="n">
-        <v>150.8</v>
+        <v>150.5</v>
       </c>
       <c r="C24" t="n">
         <v>16780.6</v>
@@ -6677,13 +6680,13 @@
         <v>3913.7</v>
       </c>
       <c r="E24" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F24" t="n">
         <v>16733.4</v>
       </c>
       <c r="G24" t="n">
-        <v>57.3</v>
+        <v>55.1</v>
       </c>
       <c r="H24" t="n">
         <v>109691.3</v>
@@ -6701,7 +6704,7 @@
         <v>166</v>
       </c>
       <c r="M24" t="n">
-        <v>19140.5</v>
+        <v>19093.6</v>
       </c>
       <c r="N24" t="n">
         <v>7155.7</v>
@@ -6718,7 +6721,7 @@
         <v>44896</v>
       </c>
       <c r="B25" t="n">
-        <v>151.4</v>
+        <v>151.1</v>
       </c>
       <c r="C25" t="n">
         <v>16805.6</v>
@@ -6727,13 +6730,13 @@
         <v>3913.7</v>
       </c>
       <c r="E25" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F25" t="n">
         <v>16733.4</v>
       </c>
       <c r="G25" t="n">
-        <v>57.3</v>
+        <v>55.1</v>
       </c>
       <c r="H25" t="n">
         <v>109701.4</v>
@@ -6751,7 +6754,7 @@
         <v>166</v>
       </c>
       <c r="M25" t="n">
-        <v>20245.2</v>
+        <v>20198.8</v>
       </c>
       <c r="N25" t="n">
         <v>7459.1</v>
@@ -6768,7 +6771,7 @@
         <v>44927</v>
       </c>
       <c r="B26" t="n">
-        <v>151.4</v>
+        <v>151.1</v>
       </c>
       <c r="C26" t="n">
         <v>16805.6</v>
@@ -6777,13 +6780,13 @@
         <v>3913.7</v>
       </c>
       <c r="E26" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F26" t="n">
         <v>16733.4</v>
       </c>
       <c r="G26" t="n">
-        <v>58.1</v>
+        <v>56</v>
       </c>
       <c r="H26" t="n">
         <v>109725.4</v>
@@ -6801,7 +6804,7 @@
         <v>166</v>
       </c>
       <c r="M26" t="n">
-        <v>21320.1</v>
+        <v>21293.1</v>
       </c>
       <c r="N26" t="n">
         <v>7844</v>
@@ -6818,7 +6821,7 @@
         <v>44958</v>
       </c>
       <c r="B27" t="n">
-        <v>152.7</v>
+        <v>152.5</v>
       </c>
       <c r="C27" t="n">
         <v>16845.6</v>
@@ -6827,13 +6830,13 @@
         <v>3913.7</v>
       </c>
       <c r="E27" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F27" t="n">
         <v>16733.4</v>
       </c>
       <c r="G27" t="n">
-        <v>58.1</v>
+        <v>56</v>
       </c>
       <c r="H27" t="n">
         <v>109725.7</v>
@@ -6851,7 +6854,7 @@
         <v>166</v>
       </c>
       <c r="M27" t="n">
-        <v>22257.6</v>
+        <v>22209.1</v>
       </c>
       <c r="N27" t="n">
         <v>8047.9</v>
@@ -6868,7 +6871,7 @@
         <v>44986</v>
       </c>
       <c r="B28" t="n">
-        <v>154</v>
+        <v>153.8</v>
       </c>
       <c r="C28" t="n">
         <v>16848.4</v>
@@ -6877,13 +6880,13 @@
         <v>3913.7</v>
       </c>
       <c r="E28" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F28" t="n">
         <v>16733.4</v>
       </c>
       <c r="G28" t="n">
-        <v>58.2</v>
+        <v>56</v>
       </c>
       <c r="H28" t="n">
         <v>109747.4</v>
@@ -6901,7 +6904,7 @@
         <v>166</v>
       </c>
       <c r="M28" t="n">
-        <v>23276.7</v>
+        <v>23248.6</v>
       </c>
       <c r="N28" t="n">
         <v>8388.1</v>
@@ -6918,7 +6921,7 @@
         <v>45017</v>
       </c>
       <c r="B29" t="n">
-        <v>155.4</v>
+        <v>155.1</v>
       </c>
       <c r="C29" t="n">
         <v>16927</v>
@@ -6927,13 +6930,13 @@
         <v>3913.7</v>
       </c>
       <c r="E29" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F29" t="n">
         <v>16733.4</v>
       </c>
       <c r="G29" t="n">
-        <v>58.2</v>
+        <v>56</v>
       </c>
       <c r="H29" t="n">
         <v>109777.8</v>
@@ -6951,7 +6954,7 @@
         <v>166</v>
       </c>
       <c r="M29" t="n">
-        <v>24024.3</v>
+        <v>23995.5</v>
       </c>
       <c r="N29" t="n">
         <v>8717.700000000001</v>
@@ -6968,7 +6971,7 @@
         <v>45047</v>
       </c>
       <c r="B30" t="n">
-        <v>155.9</v>
+        <v>155.7</v>
       </c>
       <c r="C30" t="n">
         <v>16930.5</v>
@@ -6977,13 +6980,13 @@
         <v>3913.7</v>
       </c>
       <c r="E30" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F30" t="n">
         <v>16836.2</v>
       </c>
       <c r="G30" t="n">
-        <v>58.5</v>
+        <v>56.3</v>
       </c>
       <c r="H30" t="n">
         <v>109778.8</v>
@@ -7001,7 +7004,7 @@
         <v>166</v>
       </c>
       <c r="M30" t="n">
-        <v>24909.4</v>
+        <v>24871.9</v>
       </c>
       <c r="N30" t="n">
         <v>9513.1</v>
@@ -7018,7 +7021,7 @@
         <v>45078</v>
       </c>
       <c r="B31" t="n">
-        <v>156.5</v>
+        <v>156.3</v>
       </c>
       <c r="C31" t="n">
         <v>16948.4</v>
@@ -7027,13 +7030,13 @@
         <v>3913.7</v>
       </c>
       <c r="E31" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F31" t="n">
         <v>16836.2</v>
       </c>
       <c r="G31" t="n">
-        <v>58.5</v>
+        <v>56.3</v>
       </c>
       <c r="H31" t="n">
         <v>109818.1</v>
@@ -7051,13 +7054,13 @@
         <v>166</v>
       </c>
       <c r="M31" t="n">
-        <v>25465.9</v>
+        <v>25427.4</v>
       </c>
       <c r="N31" t="n">
         <v>9685.6</v>
       </c>
       <c r="O31" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P31" t="n">
         <v>26218.2</v>
@@ -7068,7 +7071,7 @@
         <v>45108</v>
       </c>
       <c r="B32" t="n">
-        <v>162.3</v>
+        <v>162.1</v>
       </c>
       <c r="C32" t="n">
         <v>16948.4</v>
@@ -7077,13 +7080,13 @@
         <v>3913.7</v>
       </c>
       <c r="E32" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F32" t="n">
         <v>16836.2</v>
       </c>
       <c r="G32" t="n">
-        <v>58.5</v>
+        <v>56.3</v>
       </c>
       <c r="H32" t="n">
         <v>109824.2</v>
@@ -7101,13 +7104,13 @@
         <v>166</v>
       </c>
       <c r="M32" t="n">
-        <v>25964.2</v>
+        <v>25926</v>
       </c>
       <c r="N32" t="n">
         <v>9785.299999999999</v>
       </c>
       <c r="O32" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P32" t="n">
         <v>26659.8</v>
@@ -7118,7 +7121,7 @@
         <v>45139</v>
       </c>
       <c r="B33" t="n">
-        <v>169.7</v>
+        <v>169.5</v>
       </c>
       <c r="C33" t="n">
         <v>16957</v>
@@ -7127,13 +7130,13 @@
         <v>3913.7</v>
       </c>
       <c r="E33" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F33" t="n">
         <v>16836.2</v>
       </c>
       <c r="G33" t="n">
-        <v>61.5</v>
+        <v>59.3</v>
       </c>
       <c r="H33" t="n">
         <v>109842.3</v>
@@ -7151,13 +7154,13 @@
         <v>166</v>
       </c>
       <c r="M33" t="n">
-        <v>26502.7</v>
+        <v>26475.2</v>
       </c>
       <c r="N33" t="n">
         <v>10534.8</v>
       </c>
       <c r="O33" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P33" t="n">
         <v>27006</v>
@@ -7168,7 +7171,7 @@
         <v>45170</v>
       </c>
       <c r="B34" t="n">
-        <v>174.1</v>
+        <v>173.9</v>
       </c>
       <c r="C34" t="n">
         <v>16993.7</v>
@@ -7177,13 +7180,13 @@
         <v>3913.7</v>
       </c>
       <c r="E34" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F34" t="n">
         <v>16836.2</v>
       </c>
       <c r="G34" t="n">
-        <v>61.5</v>
+        <v>59.3</v>
       </c>
       <c r="H34" t="n">
         <v>109843.8</v>
@@ -7201,13 +7204,13 @@
         <v>166</v>
       </c>
       <c r="M34" t="n">
-        <v>27036.3</v>
+        <v>27004.5</v>
       </c>
       <c r="N34" t="n">
         <v>10538.4</v>
       </c>
       <c r="O34" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P34" t="n">
         <v>27170.6</v>
@@ -7218,7 +7221,7 @@
         <v>45200</v>
       </c>
       <c r="B35" t="n">
-        <v>174.6</v>
+        <v>174.4</v>
       </c>
       <c r="C35" t="n">
         <v>17017.1</v>
@@ -7227,13 +7230,13 @@
         <v>3913.7</v>
       </c>
       <c r="E35" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F35" t="n">
         <v>16836.2</v>
       </c>
       <c r="G35" t="n">
-        <v>64.5</v>
+        <v>62.3</v>
       </c>
       <c r="H35" t="n">
         <v>109843.8</v>
@@ -7245,13 +7248,13 @@
         <v>7251.8</v>
       </c>
       <c r="K35" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L35" t="n">
         <v>166</v>
       </c>
       <c r="M35" t="n">
-        <v>27627.7</v>
+        <v>27596.2</v>
       </c>
       <c r="N35" t="n">
         <v>10829.5</v>
@@ -7268,7 +7271,7 @@
         <v>45231</v>
       </c>
       <c r="B36" t="n">
-        <v>177.9</v>
+        <v>177.6</v>
       </c>
       <c r="C36" t="n">
         <v>17017.5</v>
@@ -7277,13 +7280,13 @@
         <v>3913.7</v>
       </c>
       <c r="E36" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F36" t="n">
         <v>16836.2</v>
       </c>
       <c r="G36" t="n">
-        <v>64.5</v>
+        <v>62.3</v>
       </c>
       <c r="H36" t="n">
         <v>109856.8</v>
@@ -7301,7 +7304,7 @@
         <v>166</v>
       </c>
       <c r="M36" t="n">
-        <v>28242</v>
+        <v>28208.2</v>
       </c>
       <c r="N36" t="n">
         <v>11194.5</v>
@@ -7318,7 +7321,7 @@
         <v>45261</v>
       </c>
       <c r="B37" t="n">
-        <v>178.4</v>
+        <v>178.2</v>
       </c>
       <c r="C37" t="n">
         <v>17017.5</v>
@@ -7327,13 +7330,13 @@
         <v>3913.7</v>
       </c>
       <c r="E37" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F37" t="n">
         <v>17401.7</v>
       </c>
       <c r="G37" t="n">
-        <v>64.5</v>
+        <v>62.4</v>
       </c>
       <c r="H37" t="n">
         <v>109866.9</v>
@@ -7351,7 +7354,7 @@
         <v>166</v>
       </c>
       <c r="M37" t="n">
-        <v>28956.7</v>
+        <v>28921.8</v>
       </c>
       <c r="N37" t="n">
         <v>11571</v>
@@ -7368,7 +7371,7 @@
         <v>45292</v>
       </c>
       <c r="B38" t="n">
-        <v>178.5</v>
+        <v>178.3</v>
       </c>
       <c r="C38" t="n">
         <v>17017.5</v>
@@ -7377,13 +7380,13 @@
         <v>3913.7</v>
       </c>
       <c r="E38" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F38" t="n">
         <v>17401.7</v>
       </c>
       <c r="G38" t="n">
-        <v>64.5</v>
+        <v>62.4</v>
       </c>
       <c r="H38" t="n">
         <v>109867.5</v>
@@ -7401,7 +7404,7 @@
         <v>166</v>
       </c>
       <c r="M38" t="n">
-        <v>29766.1</v>
+        <v>29727.9</v>
       </c>
       <c r="N38" t="n">
         <v>11772.1</v>
@@ -7418,7 +7421,7 @@
         <v>45323</v>
       </c>
       <c r="B39" t="n">
-        <v>181.1</v>
+        <v>180.9</v>
       </c>
       <c r="C39" t="n">
         <v>17017.5</v>
@@ -7427,13 +7430,13 @@
         <v>3913.7</v>
       </c>
       <c r="E39" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F39" t="n">
         <v>17401.7</v>
       </c>
       <c r="G39" t="n">
-        <v>64.5</v>
+        <v>62.4</v>
       </c>
       <c r="H39" t="n">
         <v>109867.5</v>
@@ -7451,7 +7454,7 @@
         <v>166</v>
       </c>
       <c r="M39" t="n">
-        <v>30514</v>
+        <v>30475.7</v>
       </c>
       <c r="N39" t="n">
         <v>12368.4</v>
@@ -7468,7 +7471,7 @@
         <v>45352</v>
       </c>
       <c r="B40" t="n">
-        <v>181.6</v>
+        <v>181.3</v>
       </c>
       <c r="C40" t="n">
         <v>17017.5</v>
@@ -7477,13 +7480,13 @@
         <v>3913.7</v>
       </c>
       <c r="E40" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F40" t="n">
         <v>17401.7</v>
       </c>
       <c r="G40" t="n">
-        <v>64.5</v>
+        <v>62.4</v>
       </c>
       <c r="H40" t="n">
         <v>109887.3</v>
@@ -7501,7 +7504,7 @@
         <v>166</v>
       </c>
       <c r="M40" t="n">
-        <v>31387.7</v>
+        <v>31349.3</v>
       </c>
       <c r="N40" t="n">
         <v>12912.7</v>
@@ -7518,7 +7521,7 @@
         <v>45383</v>
       </c>
       <c r="B41" t="n">
-        <v>183.3</v>
+        <v>183.1</v>
       </c>
       <c r="C41" t="n">
         <v>17162.5</v>
@@ -7527,13 +7530,13 @@
         <v>3913.7</v>
       </c>
       <c r="E41" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F41" t="n">
         <v>17401.7</v>
       </c>
       <c r="G41" t="n">
-        <v>64.5</v>
+        <v>62.4</v>
       </c>
       <c r="H41" t="n">
         <v>109890.3</v>
@@ -7551,7 +7554,7 @@
         <v>166</v>
       </c>
       <c r="M41" t="n">
-        <v>32279.5</v>
+        <v>32241.2</v>
       </c>
       <c r="N41" t="n">
         <v>13649.5</v>
@@ -7568,7 +7571,7 @@
         <v>45413</v>
       </c>
       <c r="B42" t="n">
-        <v>183.8</v>
+        <v>183.6</v>
       </c>
       <c r="C42" t="n">
         <v>17162.5</v>
@@ -7577,13 +7580,13 @@
         <v>3913.7</v>
       </c>
       <c r="E42" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F42" t="n">
         <v>17401.7</v>
       </c>
       <c r="G42" t="n">
-        <v>64.5</v>
+        <v>62.4</v>
       </c>
       <c r="H42" t="n">
         <v>109890.3</v>
@@ -7601,7 +7604,7 @@
         <v>166</v>
       </c>
       <c r="M42" t="n">
-        <v>33154.3</v>
+        <v>33113.4</v>
       </c>
       <c r="N42" t="n">
         <v>14039</v>
@@ -7618,7 +7621,7 @@
         <v>45444</v>
       </c>
       <c r="B43" t="n">
-        <v>184.3</v>
+        <v>184.1</v>
       </c>
       <c r="C43" t="n">
         <v>17202.5</v>
@@ -7627,13 +7630,13 @@
         <v>3913.7</v>
       </c>
       <c r="E43" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F43" t="n">
         <v>17401.7</v>
       </c>
       <c r="G43" t="n">
-        <v>64.5</v>
+        <v>62.4</v>
       </c>
       <c r="H43" t="n">
         <v>109895</v>
@@ -7651,13 +7654,13 @@
         <v>166</v>
       </c>
       <c r="M43" t="n">
-        <v>34040.3</v>
+        <v>34008.7</v>
       </c>
       <c r="N43" t="n">
         <v>14394.2</v>
       </c>
       <c r="O43" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="P43" t="n">
         <v>31111.2</v>
@@ -7668,7 +7671,7 @@
         <v>45474</v>
       </c>
       <c r="B44" t="n">
-        <v>185.7</v>
+        <v>185.5</v>
       </c>
       <c r="C44" t="n">
         <v>17202.5</v>
@@ -7677,13 +7680,13 @@
         <v>3913.7</v>
       </c>
       <c r="E44" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F44" t="n">
         <v>17401.7</v>
       </c>
       <c r="G44" t="n">
-        <v>64.5</v>
+        <v>62.4</v>
       </c>
       <c r="H44" t="n">
         <v>109895</v>
@@ -7701,13 +7704,13 @@
         <v>166</v>
       </c>
       <c r="M44" t="n">
-        <v>35009.1</v>
+        <v>34979.2</v>
       </c>
       <c r="N44" t="n">
         <v>14953</v>
       </c>
       <c r="O44" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="P44" t="n">
         <v>31504.1</v>
@@ -7718,7 +7721,7 @@
         <v>45505</v>
       </c>
       <c r="B45" t="n">
-        <v>187.8</v>
+        <v>187.5</v>
       </c>
       <c r="C45" t="n">
         <v>17202.5</v>
@@ -7727,13 +7730,13 @@
         <v>3913.7</v>
       </c>
       <c r="E45" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F45" t="n">
         <v>17401.7</v>
       </c>
       <c r="G45" t="n">
-        <v>64.5</v>
+        <v>62.4</v>
       </c>
       <c r="H45" t="n">
         <v>109911.9</v>
@@ -7751,13 +7754,13 @@
         <v>166</v>
       </c>
       <c r="M45" t="n">
-        <v>35956.1</v>
+        <v>35931</v>
       </c>
       <c r="N45" t="n">
         <v>15149.8</v>
       </c>
       <c r="O45" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="P45" t="n">
         <v>31831.4</v>
@@ -7768,7 +7771,7 @@
         <v>45536</v>
       </c>
       <c r="B46" t="n">
-        <v>188</v>
+        <v>187.8</v>
       </c>
       <c r="C46" t="n">
         <v>17272</v>
@@ -7777,13 +7780,13 @@
         <v>3913.7</v>
       </c>
       <c r="E46" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F46" t="n">
         <v>17401.7</v>
       </c>
       <c r="G46" t="n">
-        <v>64.5</v>
+        <v>62.4</v>
       </c>
       <c r="H46" t="n">
         <v>109911.9</v>
@@ -7801,13 +7804,13 @@
         <v>166</v>
       </c>
       <c r="M46" t="n">
-        <v>36774.8</v>
+        <v>36743.1</v>
       </c>
       <c r="N46" t="n">
         <v>15660.3</v>
       </c>
       <c r="O46" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="P46" t="n">
         <v>31987.1</v>
@@ -7818,7 +7821,7 @@
         <v>45566</v>
       </c>
       <c r="B47" t="n">
-        <v>188.3</v>
+        <v>188.1</v>
       </c>
       <c r="C47" t="n">
         <v>17308</v>
@@ -7827,13 +7830,13 @@
         <v>3913.7</v>
       </c>
       <c r="E47" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F47" t="n">
         <v>17401.7</v>
       </c>
       <c r="G47" t="n">
-        <v>64.5</v>
+        <v>62.4</v>
       </c>
       <c r="H47" t="n">
         <v>109917</v>
@@ -7851,13 +7854,13 @@
         <v>166</v>
       </c>
       <c r="M47" t="n">
-        <v>37695.1</v>
+        <v>37665.9</v>
       </c>
       <c r="N47" t="n">
         <v>16187.8</v>
       </c>
       <c r="O47" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="P47" t="n">
         <v>32478.5</v>
@@ -7868,7 +7871,7 @@
         <v>45597</v>
       </c>
       <c r="B48" t="n">
-        <v>188.3</v>
+        <v>188.1</v>
       </c>
       <c r="C48" t="n">
         <v>17308</v>
@@ -7877,13 +7880,13 @@
         <v>3913.7</v>
       </c>
       <c r="E48" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F48" t="n">
         <v>17401.7</v>
       </c>
       <c r="G48" t="n">
-        <v>64.5</v>
+        <v>62.4</v>
       </c>
       <c r="H48" t="n">
         <v>109945.8</v>
@@ -7901,13 +7904,13 @@
         <v>166</v>
       </c>
       <c r="M48" t="n">
-        <v>38556.8</v>
+        <v>38525.3</v>
       </c>
       <c r="N48" t="n">
         <v>16911.9</v>
       </c>
       <c r="O48" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="P48" t="n">
         <v>32627</v>
@@ -7918,7 +7921,7 @@
         <v>45627</v>
       </c>
       <c r="B49" t="n">
-        <v>188.3</v>
+        <v>188.1</v>
       </c>
       <c r="C49" t="n">
         <v>17308</v>
@@ -7927,13 +7930,13 @@
         <v>3913.7</v>
       </c>
       <c r="E49" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F49" t="n">
         <v>17401.7</v>
       </c>
       <c r="G49" t="n">
-        <v>64.5</v>
+        <v>62.4</v>
       </c>
       <c r="H49" t="n">
         <v>109948.8</v>
@@ -7951,13 +7954,13 @@
         <v>166</v>
       </c>
       <c r="M49" t="n">
-        <v>39618.4</v>
+        <v>39587.7</v>
       </c>
       <c r="N49" t="n">
         <v>17232.6</v>
       </c>
       <c r="O49" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="P49" t="n">
         <v>32876</v>
@@ -7968,7 +7971,7 @@
         <v>45658</v>
       </c>
       <c r="B50" t="n">
-        <v>188.4</v>
+        <v>188.2</v>
       </c>
       <c r="C50" t="n">
         <v>17693.6</v>
@@ -7977,13 +7980,13 @@
         <v>3913.7</v>
       </c>
       <c r="E50" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F50" t="n">
         <v>17401.7</v>
       </c>
       <c r="G50" t="n">
-        <v>64.5</v>
+        <v>62.4</v>
       </c>
       <c r="H50" t="n">
         <v>109948.8</v>
@@ -8001,13 +8004,13 @@
         <v>166</v>
       </c>
       <c r="M50" t="n">
-        <v>40613.3</v>
+        <v>40578.4</v>
       </c>
       <c r="N50" t="n">
         <v>17810.7</v>
       </c>
       <c r="O50" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="P50" t="n">
         <v>33203.6</v>
@@ -8018,7 +8021,7 @@
         <v>45689</v>
       </c>
       <c r="B51" t="n">
-        <v>188.4</v>
+        <v>188.2</v>
       </c>
       <c r="C51" t="n">
         <v>17746.7</v>
@@ -8027,13 +8030,13 @@
         <v>3913.7</v>
       </c>
       <c r="E51" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F51" t="n">
         <v>17401.7</v>
       </c>
       <c r="G51" t="n">
-        <v>64.5</v>
+        <v>62.4</v>
       </c>
       <c r="H51" t="n">
         <v>109996.1</v>
@@ -8051,7 +8054,7 @@
         <v>166</v>
       </c>
       <c r="M51" t="n">
-        <v>41517.2</v>
+        <v>41484.7</v>
       </c>
       <c r="N51" t="n">
         <v>17814.4</v>
@@ -8068,7 +8071,7 @@
         <v>45717</v>
       </c>
       <c r="B52" t="n">
-        <v>193.4</v>
+        <v>193.2</v>
       </c>
       <c r="C52" t="n">
         <v>17772.9</v>
@@ -8077,13 +8080,13 @@
         <v>3913.7</v>
       </c>
       <c r="E52" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F52" t="n">
         <v>17401.7</v>
       </c>
       <c r="G52" t="n">
-        <v>68.90000000000001</v>
+        <v>62.9</v>
       </c>
       <c r="H52" t="n">
         <v>110023.4</v>
@@ -8101,13 +8104,13 @@
         <v>166</v>
       </c>
       <c r="M52" t="n">
-        <v>42426.7</v>
+        <v>42397.5</v>
       </c>
       <c r="N52" t="n">
         <v>17828.1</v>
       </c>
       <c r="O52" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="P52" t="n">
         <v>33591.2</v>
@@ -8118,7 +8121,7 @@
         <v>45748</v>
       </c>
       <c r="B53" t="n">
-        <v>193.7</v>
+        <v>193.5</v>
       </c>
       <c r="C53" t="n">
         <v>17817.9</v>
@@ -8127,13 +8130,13 @@
         <v>3913.7</v>
       </c>
       <c r="E53" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F53" t="n">
         <v>17401.7</v>
       </c>
       <c r="G53" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="H53" t="n">
         <v>110029.6</v>
@@ -8151,13 +8154,13 @@
         <v>166</v>
       </c>
       <c r="M53" t="n">
-        <v>43274.5</v>
+        <v>43249.9</v>
       </c>
       <c r="N53" t="n">
         <v>17925.1</v>
       </c>
       <c r="O53" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="P53" t="n">
         <v>33618.2</v>
@@ -8168,7 +8171,7 @@
         <v>45778</v>
       </c>
       <c r="B54" t="n">
-        <v>193.7</v>
+        <v>193.5</v>
       </c>
       <c r="C54" t="n">
         <v>17865.9</v>
@@ -8177,13 +8180,13 @@
         <v>3913.7</v>
       </c>
       <c r="E54" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F54" t="n">
         <v>19074.3</v>
       </c>
       <c r="G54" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="H54" t="n">
         <v>110034.1</v>
@@ -8201,7 +8204,7 @@
         <v>166</v>
       </c>
       <c r="M54" t="n">
-        <v>44073.3</v>
+        <v>44051</v>
       </c>
       <c r="N54" t="n">
         <v>17929.8</v>
@@ -8218,7 +8221,7 @@
         <v>45809</v>
       </c>
       <c r="B55" t="n">
-        <v>194.2</v>
+        <v>194</v>
       </c>
       <c r="C55" t="n">
         <v>17867.6</v>
@@ -8227,13 +8230,13 @@
         <v>3913.7</v>
       </c>
       <c r="E55" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F55" t="n">
         <v>19074.3</v>
       </c>
       <c r="G55" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="H55" t="n">
         <v>110038.1</v>
@@ -8251,7 +8254,7 @@
         <v>166</v>
       </c>
       <c r="M55" t="n">
-        <v>44811.9</v>
+        <v>44789.6</v>
       </c>
       <c r="N55" t="n">
         <v>17976.2</v>
@@ -8268,7 +8271,7 @@
         <v>45839</v>
       </c>
       <c r="B56" t="n">
-        <v>197</v>
+        <v>196.7</v>
       </c>
       <c r="C56" t="n">
         <v>17867.6</v>
@@ -8277,13 +8280,13 @@
         <v>3913.7</v>
       </c>
       <c r="E56" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F56" t="n">
         <v>19074.3</v>
       </c>
       <c r="G56" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="H56" t="n">
         <v>110038.1</v>
@@ -8301,7 +8304,7 @@
         <v>166</v>
       </c>
       <c r="M56" t="n">
-        <v>45633.4</v>
+        <v>45614.4</v>
       </c>
       <c r="N56" t="n">
         <v>18021.9</v>
@@ -8318,7 +8321,7 @@
         <v>45870</v>
       </c>
       <c r="B57" t="n">
-        <v>197</v>
+        <v>196.7</v>
       </c>
       <c r="C57" t="n">
         <v>17907.6</v>
@@ -8327,13 +8330,13 @@
         <v>3913.7</v>
       </c>
       <c r="E57" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F57" t="n">
         <v>19074.3</v>
       </c>
       <c r="G57" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="H57" t="n">
         <v>110092.1</v>
@@ -8351,7 +8354,7 @@
         <v>166</v>
       </c>
       <c r="M57" t="n">
-        <v>46353.1</v>
+        <v>46346.8</v>
       </c>
       <c r="N57" t="n">
         <v>18028</v>
@@ -8368,7 +8371,7 @@
         <v>45901</v>
       </c>
       <c r="B58" t="n">
-        <v>199.1</v>
+        <v>198.9</v>
       </c>
       <c r="C58" t="n">
         <v>17907.6</v>
@@ -8377,13 +8380,13 @@
         <v>3913.7</v>
       </c>
       <c r="E58" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F58" t="n">
         <v>19074.3</v>
       </c>
       <c r="G58" t="n">
-        <v>74.3</v>
+        <v>68</v>
       </c>
       <c r="H58" t="n">
         <v>110166.1</v>
@@ -8401,7 +8404,7 @@
         <v>166</v>
       </c>
       <c r="M58" t="n">
-        <v>47023.8</v>
+        <v>47000.6</v>
       </c>
       <c r="N58" t="n">
         <v>18965.2</v>
@@ -8418,7 +8421,7 @@
         <v>45931</v>
       </c>
       <c r="B59" t="n">
-        <v>199.6</v>
+        <v>199.4</v>
       </c>
       <c r="C59" t="n">
         <v>17936.9</v>
@@ -8427,13 +8430,13 @@
         <v>3913.7</v>
       </c>
       <c r="E59" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F59" t="n">
         <v>19074.3</v>
       </c>
       <c r="G59" t="n">
-        <v>80</v>
+        <v>73.3</v>
       </c>
       <c r="H59" t="n">
         <v>110193.4</v>
@@ -8451,7 +8454,7 @@
         <v>166</v>
       </c>
       <c r="M59" t="n">
-        <v>47805</v>
+        <v>47783.7</v>
       </c>
       <c r="N59" t="n">
         <v>19550.1</v>
@@ -8468,7 +8471,7 @@
         <v>45962</v>
       </c>
       <c r="B60" t="n">
-        <v>199.6</v>
+        <v>199.4</v>
       </c>
       <c r="C60" t="n">
         <v>17936.9</v>
@@ -8477,13 +8480,13 @@
         <v>3913.7</v>
       </c>
       <c r="E60" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F60" t="n">
         <v>19074.3</v>
       </c>
       <c r="G60" t="n">
-        <v>80</v>
+        <v>73.3</v>
       </c>
       <c r="H60" t="n">
         <v>110193.4</v>
@@ -8501,7 +8504,7 @@
         <v>166</v>
       </c>
       <c r="M60" t="n">
-        <v>48495.6</v>
+        <v>48471.6</v>
       </c>
       <c r="N60" t="n">
         <v>19767.5</v>
@@ -8518,7 +8521,7 @@
         <v>45992</v>
       </c>
       <c r="B61" t="n">
-        <v>199.6</v>
+        <v>199.4</v>
       </c>
       <c r="C61" t="n">
         <v>17945.4</v>
@@ -8527,13 +8530,13 @@
         <v>3913.7</v>
       </c>
       <c r="E61" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F61" t="n">
         <v>19074.3</v>
       </c>
       <c r="G61" t="n">
-        <v>80</v>
+        <v>73.3</v>
       </c>
       <c r="H61" t="n">
         <v>110193.4</v>
@@ -8551,7 +8554,7 @@
         <v>166</v>
       </c>
       <c r="M61" t="n">
-        <v>49223.8</v>
+        <v>49206.4</v>
       </c>
       <c r="N61" t="n">
         <v>20085.8</v>
@@ -8568,7 +8571,7 @@
         <v>46023</v>
       </c>
       <c r="B62" t="n">
-        <v>199.7</v>
+        <v>199.5</v>
       </c>
       <c r="C62" t="n">
         <v>17945.4</v>
@@ -8577,13 +8580,13 @@
         <v>3913.7</v>
       </c>
       <c r="E62" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F62" t="n">
         <v>19074.3</v>
       </c>
       <c r="G62" t="n">
-        <v>80.2</v>
+        <v>73.5</v>
       </c>
       <c r="H62" t="n">
         <v>110214.4</v>
@@ -8601,7 +8604,7 @@
         <v>166</v>
       </c>
       <c r="M62" t="n">
-        <v>49952.8</v>
+        <v>49928</v>
       </c>
       <c r="N62" t="n">
         <v>20604.5</v>
@@ -8618,7 +8621,7 @@
         <v>46054</v>
       </c>
       <c r="B63" t="n">
-        <v>199.7</v>
+        <v>199.5</v>
       </c>
       <c r="C63" t="n">
         <v>17945.4</v>
@@ -8627,13 +8630,13 @@
         <v>3913.7</v>
       </c>
       <c r="E63" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F63" t="n">
         <v>19074.3</v>
       </c>
       <c r="G63" t="n">
-        <v>80.2</v>
+        <v>73.5</v>
       </c>
       <c r="H63" t="n">
         <v>110214.4</v>
@@ -8651,7 +8654,7 @@
         <v>166</v>
       </c>
       <c r="M63" t="n">
-        <v>50619.1</v>
+        <v>50593.3</v>
       </c>
       <c r="N63" t="n">
         <v>21283.7</v>
@@ -8668,7 +8671,7 @@
         <v>46082</v>
       </c>
       <c r="B64" t="n">
-        <v>199.7</v>
+        <v>199.5</v>
       </c>
       <c r="C64" t="n">
         <v>17971.7</v>
@@ -8677,13 +8680,13 @@
         <v>3913.7</v>
       </c>
       <c r="E64" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F64" t="n">
         <v>19074.3</v>
       </c>
       <c r="G64" t="n">
-        <v>80.2</v>
+        <v>73.5</v>
       </c>
       <c r="H64" t="n">
         <v>110219.6</v>
@@ -8701,7 +8704,7 @@
         <v>166</v>
       </c>
       <c r="M64" t="n">
-        <v>51385.3</v>
+        <v>51362.1</v>
       </c>
       <c r="N64" t="n">
         <v>22349.8</v>
@@ -8718,7 +8721,7 @@
         <v>46113</v>
       </c>
       <c r="B65" t="n">
-        <v>199.7</v>
+        <v>199.5</v>
       </c>
       <c r="C65" t="n">
         <v>18011.7</v>
@@ -8727,13 +8730,13 @@
         <v>3913.7</v>
       </c>
       <c r="E65" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F65" t="n">
         <v>19074.3</v>
       </c>
       <c r="G65" t="n">
-        <v>80.3</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="H65" t="n">
         <v>110219.6</v>
@@ -8751,7 +8754,7 @@
         <v>166</v>
       </c>
       <c r="M65" t="n">
-        <v>52244.1</v>
+        <v>52225.4</v>
       </c>
       <c r="N65" t="n">
         <v>22364.4</v>
@@ -8768,7 +8771,7 @@
         <v>46143</v>
       </c>
       <c r="B66" t="n">
-        <v>199.7</v>
+        <v>199.5</v>
       </c>
       <c r="C66" t="n">
         <v>18011.7</v>
@@ -8777,13 +8780,13 @@
         <v>3913.7</v>
       </c>
       <c r="E66" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F66" t="n">
         <v>19074.3</v>
       </c>
       <c r="G66" t="n">
-        <v>80.3</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="H66" t="n">
         <v>110224</v>
@@ -8801,7 +8804,7 @@
         <v>166</v>
       </c>
       <c r="M66" t="n">
-        <v>52933.1</v>
+        <v>52997.5</v>
       </c>
       <c r="N66" t="n">
         <v>22372.2</v>
@@ -8818,7 +8821,7 @@
         <v>46174</v>
       </c>
       <c r="B67" t="n">
-        <v>199.7</v>
+        <v>199.5</v>
       </c>
       <c r="C67" t="n">
         <v>18011.7</v>
@@ -8827,13 +8830,13 @@
         <v>3913.7</v>
       </c>
       <c r="E67" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F67" t="n">
         <v>19074.3</v>
       </c>
       <c r="G67" t="n">
-        <v>80.3</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="H67" t="n">
         <v>110246.7</v>
@@ -8851,7 +8854,7 @@
         <v>166</v>
       </c>
       <c r="M67" t="n">
-        <v>53392.6</v>
+        <v>53492.1</v>
       </c>
       <c r="N67" t="n">
         <v>22598.8</v>
@@ -8868,7 +8871,7 @@
         <v>46204</v>
       </c>
       <c r="B68" t="n">
-        <v>199.8</v>
+        <v>199.6</v>
       </c>
       <c r="C68" t="n">
         <v>18015.9</v>
@@ -8877,13 +8880,13 @@
         <v>3913.7</v>
       </c>
       <c r="E68" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F68" t="n">
         <v>19074.3</v>
       </c>
       <c r="G68" t="n">
-        <v>80.3</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="H68" t="n">
         <v>110253.7</v>
@@ -8901,7 +8904,7 @@
         <v>166</v>
       </c>
       <c r="M68" t="n">
-        <v>53627.4</v>
+        <v>53752.8</v>
       </c>
       <c r="N68" t="n">
         <v>22724</v>
@@ -8918,7 +8921,7 @@
         <v>46235</v>
       </c>
       <c r="B69" t="n">
-        <v>199.8</v>
+        <v>199.6</v>
       </c>
       <c r="C69" t="n">
         <v>18025.9</v>
@@ -8927,13 +8930,13 @@
         <v>3913.7</v>
       </c>
       <c r="E69" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F69" t="n">
         <v>20065.2</v>
       </c>
       <c r="G69" t="n">
-        <v>80.3</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="H69" t="n">
         <v>110253.7</v>
@@ -8951,7 +8954,7 @@
         <v>166</v>
       </c>
       <c r="M69" t="n">
-        <v>53650.9</v>
+        <v>53789.7</v>
       </c>
       <c r="N69" t="n">
         <v>23615.3</v>
@@ -8968,7 +8971,7 @@
         <v>46266</v>
       </c>
       <c r="B70" t="n">
-        <v>199.8</v>
+        <v>199.6</v>
       </c>
       <c r="C70" t="n">
         <v>18050.9</v>
@@ -8977,13 +8980,13 @@
         <v>3913.7</v>
       </c>
       <c r="E70" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F70" t="n">
         <v>20180</v>
       </c>
       <c r="G70" t="n">
-        <v>80.3</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="H70" t="n">
         <v>110253.7</v>
@@ -9001,7 +9004,7 @@
         <v>166</v>
       </c>
       <c r="M70" t="n">
-        <v>53650.9</v>
+        <v>53789.7</v>
       </c>
       <c r="N70" t="n">
         <v>23615.3</v>
@@ -9145,16 +9148,16 @@
         <v>17336.3</v>
       </c>
       <c r="D2" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="E2" t="n">
         <v>14.7</v>
       </c>
       <c r="F2" t="n">
-        <v>6110.8</v>
+        <v>6078.1</v>
       </c>
       <c r="G2" t="n">
-        <v>92.59999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -9210,16 +9213,16 @@
         <v>17457.1</v>
       </c>
       <c r="D3" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="E3" t="n">
         <v>14.7</v>
       </c>
       <c r="F3" t="n">
-        <v>6428.5</v>
+        <v>6386.3</v>
       </c>
       <c r="G3" t="n">
-        <v>95.7</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -9275,16 +9278,16 @@
         <v>17789.5</v>
       </c>
       <c r="D4" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="E4" t="n">
         <v>14.8</v>
       </c>
       <c r="F4" t="n">
-        <v>6916.2</v>
+        <v>6865.8</v>
       </c>
       <c r="G4" t="n">
-        <v>96.3</v>
+        <v>96</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -9340,16 +9343,16 @@
         <v>17997.6</v>
       </c>
       <c r="D5" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="E5" t="n">
         <v>14.8</v>
       </c>
       <c r="F5" t="n">
-        <v>7284.2</v>
+        <v>7230.9</v>
       </c>
       <c r="G5" t="n">
-        <v>97</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -9405,16 +9408,16 @@
         <v>18248.2</v>
       </c>
       <c r="D6" t="n">
-        <v>45.8</v>
+        <v>45.2</v>
       </c>
       <c r="E6" t="n">
         <v>14.8</v>
       </c>
       <c r="F6" t="n">
-        <v>7715.6</v>
+        <v>7657.4</v>
       </c>
       <c r="G6" t="n">
-        <v>99.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -9470,16 +9473,16 @@
         <v>18587.3</v>
       </c>
       <c r="D7" t="n">
-        <v>45.8</v>
+        <v>45.2</v>
       </c>
       <c r="E7" t="n">
         <v>14.8</v>
       </c>
       <c r="F7" t="n">
-        <v>8126.8</v>
+        <v>8060.3</v>
       </c>
       <c r="G7" t="n">
-        <v>107</v>
+        <v>106.6</v>
       </c>
       <c r="H7" t="n">
         <v>2.9</v>
@@ -9535,16 +9538,16 @@
         <v>18858.9</v>
       </c>
       <c r="D8" t="n">
-        <v>45.8</v>
+        <v>45.2</v>
       </c>
       <c r="E8" t="n">
         <v>14.8</v>
       </c>
       <c r="F8" t="n">
-        <v>8582.5</v>
+        <v>8508.9</v>
       </c>
       <c r="G8" t="n">
-        <v>107.7</v>
+        <v>107.2</v>
       </c>
       <c r="H8" t="n">
         <v>2.9</v>
@@ -9600,16 +9603,16 @@
         <v>19292.8</v>
       </c>
       <c r="D9" t="n">
-        <v>47</v>
+        <v>46.4</v>
       </c>
       <c r="E9" t="n">
         <v>14.8</v>
       </c>
       <c r="F9" t="n">
-        <v>9075.4</v>
+        <v>9014.4</v>
       </c>
       <c r="G9" t="n">
-        <v>108.3</v>
+        <v>107.8</v>
       </c>
       <c r="H9" t="n">
         <v>2.9</v>
@@ -9665,16 +9668,16 @@
         <v>19571.1</v>
       </c>
       <c r="D10" t="n">
-        <v>47</v>
+        <v>46.4</v>
       </c>
       <c r="E10" t="n">
         <v>14.8</v>
       </c>
       <c r="F10" t="n">
-        <v>9549</v>
+        <v>9479.200000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>109.9</v>
+        <v>109.5</v>
       </c>
       <c r="H10" t="n">
         <v>2.9</v>
@@ -9730,16 +9733,16 @@
         <v>19853.6</v>
       </c>
       <c r="D11" t="n">
-        <v>49.4</v>
+        <v>48.8</v>
       </c>
       <c r="E11" t="n">
         <v>14.8</v>
       </c>
       <c r="F11" t="n">
-        <v>10039.3</v>
+        <v>9970.299999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>110.1</v>
+        <v>109.6</v>
       </c>
       <c r="H11" t="n">
         <v>4.6</v>
@@ -9795,16 +9798,16 @@
         <v>20223.6</v>
       </c>
       <c r="D12" t="n">
-        <v>51</v>
+        <v>50.4</v>
       </c>
       <c r="E12" t="n">
         <v>14.9</v>
       </c>
       <c r="F12" t="n">
-        <v>10659.1</v>
+        <v>10579.8</v>
       </c>
       <c r="G12" t="n">
-        <v>110.8</v>
+        <v>110.3</v>
       </c>
       <c r="H12" t="n">
         <v>4.6</v>
@@ -9860,16 +9863,16 @@
         <v>20914.4</v>
       </c>
       <c r="D13" t="n">
-        <v>51</v>
+        <v>50.4</v>
       </c>
       <c r="E13" t="n">
         <v>14.9</v>
       </c>
       <c r="F13" t="n">
-        <v>11410.1</v>
+        <v>11320.5</v>
       </c>
       <c r="G13" t="n">
-        <v>118.3</v>
+        <v>117.9</v>
       </c>
       <c r="H13" t="n">
         <v>4.6</v>
@@ -9925,16 +9928,16 @@
         <v>21180.2</v>
       </c>
       <c r="D14" t="n">
-        <v>51</v>
+        <v>50.4</v>
       </c>
       <c r="E14" t="n">
         <v>16.4</v>
       </c>
       <c r="F14" t="n">
-        <v>11887.5</v>
+        <v>11802.2</v>
       </c>
       <c r="G14" t="n">
-        <v>119</v>
+        <v>118.6</v>
       </c>
       <c r="H14" t="n">
         <v>4.6</v>
@@ -9990,16 +9993,16 @@
         <v>21547.7</v>
       </c>
       <c r="D15" t="n">
-        <v>51</v>
+        <v>50.4</v>
       </c>
       <c r="E15" t="n">
         <v>16.9</v>
       </c>
       <c r="F15" t="n">
-        <v>12455.9</v>
+        <v>12365.1</v>
       </c>
       <c r="G15" t="n">
-        <v>119.5</v>
+        <v>119</v>
       </c>
       <c r="H15" t="n">
         <v>6.3</v>
@@ -10055,16 +10058,16 @@
         <v>21582.6</v>
       </c>
       <c r="D16" t="n">
-        <v>52.1</v>
+        <v>50.5</v>
       </c>
       <c r="E16" t="n">
         <v>16.9</v>
       </c>
       <c r="F16" t="n">
-        <v>13149.8</v>
+        <v>13065.1</v>
       </c>
       <c r="G16" t="n">
-        <v>131.4</v>
+        <v>131</v>
       </c>
       <c r="H16" t="n">
         <v>6.3</v>
@@ -10120,16 +10123,16 @@
         <v>21641.4</v>
       </c>
       <c r="D17" t="n">
-        <v>53.1</v>
+        <v>51.5</v>
       </c>
       <c r="E17" t="n">
         <v>16.9</v>
       </c>
       <c r="F17" t="n">
-        <v>13777.5</v>
+        <v>13698.1</v>
       </c>
       <c r="G17" t="n">
-        <v>134.5</v>
+        <v>134.1</v>
       </c>
       <c r="H17" t="n">
         <v>7.1</v>
@@ -10185,16 +10188,16 @@
         <v>21785.4</v>
       </c>
       <c r="D18" t="n">
-        <v>53.1</v>
+        <v>51.5</v>
       </c>
       <c r="E18" t="n">
         <v>16.9</v>
       </c>
       <c r="F18" t="n">
-        <v>14486.7</v>
+        <v>14386.1</v>
       </c>
       <c r="G18" t="n">
-        <v>135.6</v>
+        <v>135.1</v>
       </c>
       <c r="H18" t="n">
         <v>7.1</v>
@@ -10250,16 +10253,16 @@
         <v>21888</v>
       </c>
       <c r="D19" t="n">
-        <v>53.1</v>
+        <v>51.5</v>
       </c>
       <c r="E19" t="n">
         <v>16.9</v>
       </c>
       <c r="F19" t="n">
-        <v>15207.4</v>
+        <v>15101.4</v>
       </c>
       <c r="G19" t="n">
-        <v>140.7</v>
+        <v>140.2</v>
       </c>
       <c r="H19" t="n">
         <v>7.1</v>
@@ -10315,16 +10318,16 @@
         <v>22211.8</v>
       </c>
       <c r="D20" t="n">
-        <v>53.1</v>
+        <v>51.5</v>
       </c>
       <c r="E20" t="n">
         <v>16.9</v>
       </c>
       <c r="F20" t="n">
-        <v>15976.7</v>
+        <v>15858.8</v>
       </c>
       <c r="G20" t="n">
-        <v>145.3</v>
+        <v>144.9</v>
       </c>
       <c r="H20" t="n">
         <v>7.1</v>
@@ -10380,16 +10383,16 @@
         <v>22408</v>
       </c>
       <c r="D21" t="n">
-        <v>54.6</v>
+        <v>53</v>
       </c>
       <c r="E21" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="F21" t="n">
-        <v>16766.1</v>
+        <v>16632.6</v>
       </c>
       <c r="G21" t="n">
-        <v>146.5</v>
+        <v>146.1</v>
       </c>
       <c r="H21" t="n">
         <v>7.1</v>
@@ -10445,16 +10448,16 @@
         <v>22647.8</v>
       </c>
       <c r="D22" t="n">
-        <v>56.6</v>
+        <v>55</v>
       </c>
       <c r="E22" t="n">
         <v>17</v>
       </c>
       <c r="F22" t="n">
-        <v>17551.7</v>
+        <v>17407.3</v>
       </c>
       <c r="G22" t="n">
-        <v>146.7</v>
+        <v>146.3</v>
       </c>
       <c r="H22" t="n">
         <v>7.1</v>
@@ -10510,16 +10513,16 @@
         <v>23308.9</v>
       </c>
       <c r="D23" t="n">
-        <v>57.3</v>
+        <v>55.1</v>
       </c>
       <c r="E23" t="n">
         <v>17</v>
       </c>
       <c r="F23" t="n">
-        <v>18267.9</v>
+        <v>18215.4</v>
       </c>
       <c r="G23" t="n">
-        <v>147.2</v>
+        <v>146.8</v>
       </c>
       <c r="H23" t="n">
         <v>7.1</v>
@@ -10575,16 +10578,16 @@
         <v>23623.7</v>
       </c>
       <c r="D24" t="n">
-        <v>57.3</v>
+        <v>55.1</v>
       </c>
       <c r="E24" t="n">
         <v>17</v>
       </c>
       <c r="F24" t="n">
-        <v>19140.5</v>
+        <v>19093.6</v>
       </c>
       <c r="G24" t="n">
-        <v>153.3</v>
+        <v>152.8</v>
       </c>
       <c r="H24" t="n">
         <v>7.1</v>
@@ -10640,16 +10643,16 @@
         <v>24097.6</v>
       </c>
       <c r="D25" t="n">
-        <v>57.3</v>
+        <v>55.1</v>
       </c>
       <c r="E25" t="n">
         <v>17</v>
       </c>
       <c r="F25" t="n">
-        <v>20245.2</v>
+        <v>20198.8</v>
       </c>
       <c r="G25" t="n">
-        <v>153.9</v>
+        <v>153.4</v>
       </c>
       <c r="H25" t="n">
         <v>7.1</v>
@@ -10705,16 +10708,16 @@
         <v>24970.9</v>
       </c>
       <c r="D26" t="n">
-        <v>58.1</v>
+        <v>56</v>
       </c>
       <c r="E26" t="n">
         <v>17</v>
       </c>
       <c r="F26" t="n">
-        <v>21320.1</v>
+        <v>21293.1</v>
       </c>
       <c r="G26" t="n">
-        <v>153.9</v>
+        <v>153.4</v>
       </c>
       <c r="H26" t="n">
         <v>7.1</v>
@@ -10770,16 +10773,16 @@
         <v>25158.9</v>
       </c>
       <c r="D27" t="n">
-        <v>58.1</v>
+        <v>56</v>
       </c>
       <c r="E27" t="n">
         <v>17</v>
       </c>
       <c r="F27" t="n">
-        <v>22257.6</v>
+        <v>22209.1</v>
       </c>
       <c r="G27" t="n">
-        <v>155.2</v>
+        <v>154.8</v>
       </c>
       <c r="H27" t="n">
         <v>7.1</v>
@@ -10835,16 +10838,16 @@
         <v>25343.1</v>
       </c>
       <c r="D28" t="n">
-        <v>58.2</v>
+        <v>56</v>
       </c>
       <c r="E28" t="n">
         <v>17</v>
       </c>
       <c r="F28" t="n">
-        <v>23276.7</v>
+        <v>23248.6</v>
       </c>
       <c r="G28" t="n">
-        <v>156.5</v>
+        <v>156.1</v>
       </c>
       <c r="H28" t="n">
         <v>7.1</v>
@@ -10900,16 +10903,16 @@
         <v>25600.7</v>
       </c>
       <c r="D29" t="n">
-        <v>58.2</v>
+        <v>56</v>
       </c>
       <c r="E29" t="n">
         <v>17</v>
       </c>
       <c r="F29" t="n">
-        <v>24024.3</v>
+        <v>23995.5</v>
       </c>
       <c r="G29" t="n">
-        <v>157.9</v>
+        <v>157.4</v>
       </c>
       <c r="H29" t="n">
         <v>7.1</v>
@@ -10965,16 +10968,16 @@
         <v>25966.4</v>
       </c>
       <c r="D30" t="n">
-        <v>58.5</v>
+        <v>56.3</v>
       </c>
       <c r="E30" t="n">
         <v>17</v>
       </c>
       <c r="F30" t="n">
-        <v>24909.4</v>
+        <v>24871.9</v>
       </c>
       <c r="G30" t="n">
-        <v>158.4</v>
+        <v>158</v>
       </c>
       <c r="H30" t="n">
         <v>7.1</v>
@@ -11030,16 +11033,16 @@
         <v>26218.2</v>
       </c>
       <c r="D31" t="n">
-        <v>58.5</v>
+        <v>56.3</v>
       </c>
       <c r="E31" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="F31" t="n">
-        <v>25465.9</v>
+        <v>25427.4</v>
       </c>
       <c r="G31" t="n">
-        <v>159</v>
+        <v>158.6</v>
       </c>
       <c r="H31" t="n">
         <v>7.1</v>
@@ -11095,16 +11098,16 @@
         <v>26659.8</v>
       </c>
       <c r="D32" t="n">
-        <v>58.5</v>
+        <v>56.3</v>
       </c>
       <c r="E32" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="F32" t="n">
-        <v>25964.2</v>
+        <v>25926</v>
       </c>
       <c r="G32" t="n">
-        <v>164.8</v>
+        <v>164.4</v>
       </c>
       <c r="H32" t="n">
         <v>7.1</v>
@@ -11160,16 +11163,16 @@
         <v>27006</v>
       </c>
       <c r="D33" t="n">
-        <v>61.5</v>
+        <v>59.3</v>
       </c>
       <c r="E33" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="F33" t="n">
-        <v>26502.7</v>
+        <v>26475.2</v>
       </c>
       <c r="G33" t="n">
-        <v>172.2</v>
+        <v>171.8</v>
       </c>
       <c r="H33" t="n">
         <v>7.1</v>
@@ -11225,16 +11228,16 @@
         <v>27170.6</v>
       </c>
       <c r="D34" t="n">
-        <v>61.5</v>
+        <v>59.3</v>
       </c>
       <c r="E34" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="F34" t="n">
-        <v>27036.3</v>
+        <v>27004.5</v>
       </c>
       <c r="G34" t="n">
-        <v>176.6</v>
+        <v>176.2</v>
       </c>
       <c r="H34" t="n">
         <v>7.1</v>
@@ -11290,19 +11293,19 @@
         <v>27678.9</v>
       </c>
       <c r="D35" t="n">
-        <v>64.5</v>
+        <v>62.3</v>
       </c>
       <c r="E35" t="n">
         <v>17.1</v>
       </c>
       <c r="F35" t="n">
-        <v>27627.7</v>
+        <v>27596.2</v>
       </c>
       <c r="G35" t="n">
-        <v>177.1</v>
+        <v>176.7</v>
       </c>
       <c r="H35" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I35" t="n">
         <v>5759.1</v>
@@ -11355,16 +11358,16 @@
         <v>27966.3</v>
       </c>
       <c r="D36" t="n">
-        <v>64.5</v>
+        <v>62.3</v>
       </c>
       <c r="E36" t="n">
         <v>17.1</v>
       </c>
       <c r="F36" t="n">
-        <v>28242</v>
+        <v>28208.2</v>
       </c>
       <c r="G36" t="n">
-        <v>180.4</v>
+        <v>179.9</v>
       </c>
       <c r="H36" t="n">
         <v>8.300000000000001</v>
@@ -11420,16 +11423,16 @@
         <v>29023.2</v>
       </c>
       <c r="D37" t="n">
-        <v>64.5</v>
+        <v>62.4</v>
       </c>
       <c r="E37" t="n">
         <v>17.1</v>
       </c>
       <c r="F37" t="n">
-        <v>28956.7</v>
+        <v>28921.8</v>
       </c>
       <c r="G37" t="n">
-        <v>180.9</v>
+        <v>180.5</v>
       </c>
       <c r="H37" t="n">
         <v>8.300000000000001</v>
@@ -11485,16 +11488,16 @@
         <v>29500.1</v>
       </c>
       <c r="D38" t="n">
-        <v>64.5</v>
+        <v>62.4</v>
       </c>
       <c r="E38" t="n">
         <v>17.1</v>
       </c>
       <c r="F38" t="n">
-        <v>29766.1</v>
+        <v>29727.9</v>
       </c>
       <c r="G38" t="n">
-        <v>181</v>
+        <v>180.6</v>
       </c>
       <c r="H38" t="n">
         <v>8.300000000000001</v>
@@ -11550,16 +11553,16 @@
         <v>29875.9</v>
       </c>
       <c r="D39" t="n">
-        <v>64.5</v>
+        <v>62.4</v>
       </c>
       <c r="E39" t="n">
         <v>17.1</v>
       </c>
       <c r="F39" t="n">
-        <v>30514</v>
+        <v>30475.7</v>
       </c>
       <c r="G39" t="n">
-        <v>183.6</v>
+        <v>183.2</v>
       </c>
       <c r="H39" t="n">
         <v>8.300000000000001</v>
@@ -11615,16 +11618,16 @@
         <v>30197.4</v>
       </c>
       <c r="D40" t="n">
-        <v>64.5</v>
+        <v>62.4</v>
       </c>
       <c r="E40" t="n">
         <v>17.1</v>
       </c>
       <c r="F40" t="n">
-        <v>31387.7</v>
+        <v>31349.3</v>
       </c>
       <c r="G40" t="n">
-        <v>184.1</v>
+        <v>183.6</v>
       </c>
       <c r="H40" t="n">
         <v>8.300000000000001</v>
@@ -11680,16 +11683,16 @@
         <v>30663.1</v>
       </c>
       <c r="D41" t="n">
-        <v>64.5</v>
+        <v>62.4</v>
       </c>
       <c r="E41" t="n">
         <v>17.1</v>
       </c>
       <c r="F41" t="n">
-        <v>32279.5</v>
+        <v>32241.2</v>
       </c>
       <c r="G41" t="n">
-        <v>185.8</v>
+        <v>185.4</v>
       </c>
       <c r="H41" t="n">
         <v>8.300000000000001</v>
@@ -11745,16 +11748,16 @@
         <v>30884.5</v>
       </c>
       <c r="D42" t="n">
-        <v>64.5</v>
+        <v>62.4</v>
       </c>
       <c r="E42" t="n">
         <v>17.1</v>
       </c>
       <c r="F42" t="n">
-        <v>33154.3</v>
+        <v>33113.4</v>
       </c>
       <c r="G42" t="n">
-        <v>186.3</v>
+        <v>185.9</v>
       </c>
       <c r="H42" t="n">
         <v>8.300000000000001</v>
@@ -11810,16 +11813,16 @@
         <v>31111.2</v>
       </c>
       <c r="D43" t="n">
-        <v>64.5</v>
+        <v>62.4</v>
       </c>
       <c r="E43" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="F43" t="n">
-        <v>34040.3</v>
+        <v>34008.7</v>
       </c>
       <c r="G43" t="n">
-        <v>186.8</v>
+        <v>186.4</v>
       </c>
       <c r="H43" t="n">
         <v>8.300000000000001</v>
@@ -11875,16 +11878,16 @@
         <v>31504.1</v>
       </c>
       <c r="D44" t="n">
-        <v>64.5</v>
+        <v>62.4</v>
       </c>
       <c r="E44" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="F44" t="n">
-        <v>35009.1</v>
+        <v>34979.2</v>
       </c>
       <c r="G44" t="n">
-        <v>188.2</v>
+        <v>187.8</v>
       </c>
       <c r="H44" t="n">
         <v>8.300000000000001</v>
@@ -11940,16 +11943,16 @@
         <v>31831.4</v>
       </c>
       <c r="D45" t="n">
-        <v>64.5</v>
+        <v>62.4</v>
       </c>
       <c r="E45" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="F45" t="n">
-        <v>35956.1</v>
+        <v>35931</v>
       </c>
       <c r="G45" t="n">
-        <v>190.3</v>
+        <v>189.8</v>
       </c>
       <c r="H45" t="n">
         <v>8.300000000000001</v>
@@ -12005,16 +12008,16 @@
         <v>31987.1</v>
       </c>
       <c r="D46" t="n">
-        <v>64.5</v>
+        <v>62.4</v>
       </c>
       <c r="E46" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="F46" t="n">
-        <v>36774.8</v>
+        <v>36743.1</v>
       </c>
       <c r="G46" t="n">
-        <v>190.5</v>
+        <v>190.1</v>
       </c>
       <c r="H46" t="n">
         <v>8.300000000000001</v>
@@ -12070,16 +12073,16 @@
         <v>32478.5</v>
       </c>
       <c r="D47" t="n">
-        <v>64.5</v>
+        <v>62.4</v>
       </c>
       <c r="E47" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="F47" t="n">
-        <v>37695.1</v>
+        <v>37665.9</v>
       </c>
       <c r="G47" t="n">
-        <v>190.8</v>
+        <v>190.4</v>
       </c>
       <c r="H47" t="n">
         <v>8.300000000000001</v>
@@ -12135,16 +12138,16 @@
         <v>32627</v>
       </c>
       <c r="D48" t="n">
-        <v>64.5</v>
+        <v>62.4</v>
       </c>
       <c r="E48" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="F48" t="n">
-        <v>38556.8</v>
+        <v>38525.3</v>
       </c>
       <c r="G48" t="n">
-        <v>190.8</v>
+        <v>190.4</v>
       </c>
       <c r="H48" t="n">
         <v>8.300000000000001</v>
@@ -12200,16 +12203,16 @@
         <v>32876</v>
       </c>
       <c r="D49" t="n">
-        <v>64.5</v>
+        <v>62.4</v>
       </c>
       <c r="E49" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="F49" t="n">
-        <v>39618.4</v>
+        <v>39587.7</v>
       </c>
       <c r="G49" t="n">
-        <v>190.8</v>
+        <v>190.4</v>
       </c>
       <c r="H49" t="n">
         <v>8.300000000000001</v>
@@ -12265,16 +12268,16 @@
         <v>33203.6</v>
       </c>
       <c r="D50" t="n">
-        <v>64.5</v>
+        <v>62.4</v>
       </c>
       <c r="E50" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="F50" t="n">
-        <v>40613.3</v>
+        <v>40578.4</v>
       </c>
       <c r="G50" t="n">
-        <v>190.9</v>
+        <v>190.5</v>
       </c>
       <c r="H50" t="n">
         <v>8.300000000000001</v>
@@ -12330,16 +12333,16 @@
         <v>33393.2</v>
       </c>
       <c r="D51" t="n">
-        <v>64.5</v>
+        <v>62.4</v>
       </c>
       <c r="E51" t="n">
         <v>17.4</v>
       </c>
       <c r="F51" t="n">
-        <v>41517.2</v>
+        <v>41484.7</v>
       </c>
       <c r="G51" t="n">
-        <v>190.9</v>
+        <v>190.5</v>
       </c>
       <c r="H51" t="n">
         <v>8.300000000000001</v>
@@ -12395,16 +12398,16 @@
         <v>33591.2</v>
       </c>
       <c r="D52" t="n">
-        <v>68.90000000000001</v>
+        <v>62.9</v>
       </c>
       <c r="E52" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="F52" t="n">
-        <v>42426.7</v>
+        <v>42397.5</v>
       </c>
       <c r="G52" t="n">
-        <v>195.9</v>
+        <v>195.5</v>
       </c>
       <c r="H52" t="n">
         <v>8.4</v>
@@ -12460,16 +12463,16 @@
         <v>33618.2</v>
       </c>
       <c r="D53" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E53" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="F53" t="n">
-        <v>43274.5</v>
+        <v>43249.9</v>
       </c>
       <c r="G53" t="n">
-        <v>196.2</v>
+        <v>195.8</v>
       </c>
       <c r="H53" t="n">
         <v>8.4</v>
@@ -12525,16 +12528,16 @@
         <v>33618.2</v>
       </c>
       <c r="D54" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E54" t="n">
         <v>17.5</v>
       </c>
       <c r="F54" t="n">
-        <v>44073.3</v>
+        <v>44051</v>
       </c>
       <c r="G54" t="n">
-        <v>196.2</v>
+        <v>195.8</v>
       </c>
       <c r="H54" t="n">
         <v>8.4</v>
@@ -12590,16 +12593,16 @@
         <v>33829.7</v>
       </c>
       <c r="D55" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E55" t="n">
         <v>17.5</v>
       </c>
       <c r="F55" t="n">
-        <v>44811.9</v>
+        <v>44789.6</v>
       </c>
       <c r="G55" t="n">
-        <v>196.7</v>
+        <v>196.3</v>
       </c>
       <c r="H55" t="n">
         <v>8.4</v>
@@ -12655,16 +12658,16 @@
         <v>33870.2</v>
       </c>
       <c r="D56" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E56" t="n">
         <v>17.5</v>
       </c>
       <c r="F56" t="n">
-        <v>45633.4</v>
+        <v>45614.4</v>
       </c>
       <c r="G56" t="n">
-        <v>199.5</v>
+        <v>199.1</v>
       </c>
       <c r="H56" t="n">
         <v>8.4</v>
@@ -12720,16 +12723,16 @@
         <v>34086.2</v>
       </c>
       <c r="D57" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E57" t="n">
         <v>17.5</v>
       </c>
       <c r="F57" t="n">
-        <v>46353.1</v>
+        <v>46346.8</v>
       </c>
       <c r="G57" t="n">
-        <v>199.5</v>
+        <v>199.1</v>
       </c>
       <c r="H57" t="n">
         <v>8.5</v>
@@ -12785,16 +12788,16 @@
         <v>34401.2</v>
       </c>
       <c r="D58" t="n">
-        <v>74.3</v>
+        <v>68</v>
       </c>
       <c r="E58" t="n">
         <v>17.5</v>
       </c>
       <c r="F58" t="n">
-        <v>47023.8</v>
+        <v>47000.6</v>
       </c>
       <c r="G58" t="n">
-        <v>201.6</v>
+        <v>201.2</v>
       </c>
       <c r="H58" t="n">
         <v>8.6</v>
@@ -12850,16 +12853,16 @@
         <v>34401.2</v>
       </c>
       <c r="D59" t="n">
-        <v>80</v>
+        <v>73.3</v>
       </c>
       <c r="E59" t="n">
         <v>17.5</v>
       </c>
       <c r="F59" t="n">
-        <v>47805</v>
+        <v>47783.7</v>
       </c>
       <c r="G59" t="n">
-        <v>202.1</v>
+        <v>201.7</v>
       </c>
       <c r="H59" t="n">
         <v>8.9</v>
@@ -12915,16 +12918,16 @@
         <v>34401.2</v>
       </c>
       <c r="D60" t="n">
-        <v>80</v>
+        <v>73.3</v>
       </c>
       <c r="E60" t="n">
         <v>17.5</v>
       </c>
       <c r="F60" t="n">
-        <v>48495.6</v>
+        <v>48471.6</v>
       </c>
       <c r="G60" t="n">
-        <v>202.1</v>
+        <v>201.7</v>
       </c>
       <c r="H60" t="n">
         <v>9.199999999999999</v>
@@ -12980,16 +12983,16 @@
         <v>34752.2</v>
       </c>
       <c r="D61" t="n">
-        <v>80</v>
+        <v>73.3</v>
       </c>
       <c r="E61" t="n">
         <v>17.5</v>
       </c>
       <c r="F61" t="n">
-        <v>49223.8</v>
+        <v>49206.4</v>
       </c>
       <c r="G61" t="n">
-        <v>202.1</v>
+        <v>201.7</v>
       </c>
       <c r="H61" t="n">
         <v>9.4</v>
@@ -13045,16 +13048,16 @@
         <v>34752.2</v>
       </c>
       <c r="D62" t="n">
-        <v>80.2</v>
+        <v>73.5</v>
       </c>
       <c r="E62" t="n">
         <v>17.5</v>
       </c>
       <c r="F62" t="n">
-        <v>49952.8</v>
+        <v>49928</v>
       </c>
       <c r="G62" t="n">
-        <v>202.2</v>
+        <v>201.8</v>
       </c>
       <c r="H62" t="n">
         <v>9.699999999999999</v>
@@ -13110,16 +13113,16 @@
         <v>34810.7</v>
       </c>
       <c r="D63" t="n">
-        <v>80.2</v>
+        <v>73.5</v>
       </c>
       <c r="E63" t="n">
         <v>17.5</v>
       </c>
       <c r="F63" t="n">
-        <v>50619.1</v>
+        <v>50593.3</v>
       </c>
       <c r="G63" t="n">
-        <v>202.2</v>
+        <v>201.8</v>
       </c>
       <c r="H63" t="n">
         <v>9.800000000000001</v>
@@ -13175,16 +13178,16 @@
         <v>34810.7</v>
       </c>
       <c r="D64" t="n">
-        <v>80.2</v>
+        <v>73.5</v>
       </c>
       <c r="E64" t="n">
         <v>17.5</v>
       </c>
       <c r="F64" t="n">
-        <v>51385.3</v>
+        <v>51362.1</v>
       </c>
       <c r="G64" t="n">
-        <v>202.2</v>
+        <v>201.8</v>
       </c>
       <c r="H64" t="n">
         <v>10</v>
@@ -13240,16 +13243,16 @@
         <v>34810.7</v>
       </c>
       <c r="D65" t="n">
-        <v>80.3</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="E65" t="n">
         <v>17.5</v>
       </c>
       <c r="F65" t="n">
-        <v>52244.1</v>
+        <v>52225.4</v>
       </c>
       <c r="G65" t="n">
-        <v>202.2</v>
+        <v>201.8</v>
       </c>
       <c r="H65" t="n">
         <v>13.5</v>
@@ -13305,16 +13308,16 @@
         <v>34810.7</v>
       </c>
       <c r="D66" t="n">
-        <v>80.3</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="E66" t="n">
         <v>17.5</v>
       </c>
       <c r="F66" t="n">
-        <v>52933.1</v>
+        <v>52997.5</v>
       </c>
       <c r="G66" t="n">
-        <v>202.2</v>
+        <v>201.8</v>
       </c>
       <c r="H66" t="n">
         <v>14.1</v>
@@ -13370,16 +13373,16 @@
         <v>34810.7</v>
       </c>
       <c r="D67" t="n">
-        <v>80.3</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="E67" t="n">
         <v>17.5</v>
       </c>
       <c r="F67" t="n">
-        <v>53392.6</v>
+        <v>53492.1</v>
       </c>
       <c r="G67" t="n">
-        <v>202.2</v>
+        <v>201.8</v>
       </c>
       <c r="H67" t="n">
         <v>14.5</v>
@@ -13435,16 +13438,16 @@
         <v>34873.7</v>
       </c>
       <c r="D68" t="n">
-        <v>80.3</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="E68" t="n">
         <v>17.5</v>
       </c>
       <c r="F68" t="n">
-        <v>53627.4</v>
+        <v>53752.8</v>
       </c>
       <c r="G68" t="n">
-        <v>202.3</v>
+        <v>201.9</v>
       </c>
       <c r="H68" t="n">
         <v>14.5</v>
@@ -13500,16 +13503,16 @@
         <v>34936.7</v>
       </c>
       <c r="D69" t="n">
-        <v>80.3</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="E69" t="n">
         <v>17.5</v>
       </c>
       <c r="F69" t="n">
-        <v>53650.9</v>
+        <v>53789.7</v>
       </c>
       <c r="G69" t="n">
-        <v>202.3</v>
+        <v>201.9</v>
       </c>
       <c r="H69" t="n">
         <v>14.5</v>
@@ -13565,16 +13568,16 @@
         <v>34936.7</v>
       </c>
       <c r="D70" t="n">
-        <v>80.3</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="E70" t="n">
         <v>17.5</v>
       </c>
       <c r="F70" t="n">
-        <v>53650.9</v>
+        <v>53789.7</v>
       </c>
       <c r="G70" t="n">
-        <v>202.3</v>
+        <v>201.9</v>
       </c>
       <c r="H70" t="n">
         <v>14.5</v>
@@ -13677,10 +13680,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E2" t="n">
-        <v>80.3</v>
+        <v>73.59999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -13700,7 +13703,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E3" t="n">
         <v>17.5</v>
@@ -13723,10 +13726,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4655916</v>
+        <v>4665874</v>
       </c>
       <c r="E4" t="n">
-        <v>53650.9</v>
+        <v>53789.7</v>
       </c>
     </row>
     <row r="5">
@@ -13746,10 +13749,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E5" t="n">
-        <v>199.8</v>
+        <v>199.6</v>
       </c>
     </row>
     <row r="6">
@@ -13769,10 +13772,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="7">
@@ -13792,7 +13795,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E7" t="n">
         <v>14.5</v>
@@ -15062,7 +15065,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>109.931</v>
+        <v>109.929</v>
       </c>
       <c r="E2" t="n">
         <v>109.92</v>
@@ -15134,13 +15137,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>40.528</v>
+        <v>40.493</v>
       </c>
       <c r="E5" t="n">
         <v>37.56</v>
       </c>
       <c r="F5" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="6">
@@ -15272,7 +15275,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>228.672</v>
+        <v>228.635</v>
       </c>
       <c r="E11" t="n">
         <v>224.69</v>
@@ -15296,7 +15299,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>110.013</v>
+        <v>110.011</v>
       </c>
       <c r="E12" t="n">
         <v>109.98</v>
@@ -15368,7 +15371,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>56.851</v>
+        <v>56.82</v>
       </c>
       <c r="E15" t="n">
         <v>53.11</v>
@@ -15506,7 +15509,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>248.588</v>
+        <v>248.555</v>
       </c>
       <c r="E21" t="n">
         <v>244.67</v>
@@ -15530,7 +15533,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>110.273</v>
+        <v>110.267</v>
       </c>
       <c r="E22" t="n">
         <v>110.27</v>
@@ -15602,7 +15605,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>69.309</v>
+        <v>69.292</v>
       </c>
       <c r="E25" t="n">
         <v>64.69</v>
@@ -15740,7 +15743,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>265.581</v>
+        <v>265.557</v>
       </c>
       <c r="E31" t="n">
         <v>260.64</v>
